--- a/wwwroot/template/TemplateExportHistoryNew.xlsx
+++ b/wwwroot/template/TemplateExportHistoryNew.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8C8A29-F4E7-4CC6-BCD6-1D774082A256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2E918D-C833-44BE-A860-CE277F8A2A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99E87B9-757D-492C-8DC2-9D6FEAFC762F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{D99E87B9-757D-492C-8DC2-9D6FEAFC762F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Lịch sử yêu cầu" sheetId="1" r:id="rId1"/>
+    <sheet name="Thời gian phê duyệt" sheetId="2" r:id="rId2"/>
+    <sheet name="Lịch sử quản lý theo Mã Nội Bộ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -403,8 +405,428 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Thuy, VuThiPhuong (BIVN-PUR PUR)</author>
+  </authors>
+  <commentList>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{510FF164-6C8C-446A-ACDF-34E6DA628B30}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Phòng ban nào cần mua về lắp thành 1 thiết bị thì ghi
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{67B99615-0101-4B99-9F2A-7C8E61F2C78F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Với mã hàng đã từng mua thì bắt buộc phải điền
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{17BA8675-2FB7-4492-88BB-965351BF42C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tương đương cột good code hiện tại</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Nếu là mã đã từng mua thì vlook up với master hàng hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{14A9A12F-8662-417F-A047-A0E69A7F4B7B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hàm &amp; của phần mô tả hàng hóa. Tên mở thủ tục hải quan thay đổi theo mục đích sử dụng. Cột này chỉ là tên dự thảo của phòng ban, sau Ship sẽ xác nhận lại trước khi phát hành đơn yêu cầu hàng hóa</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Thuy, VuThiPhuong (BIVN-PUR PUR)</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{866B77EC-1F7E-4F3E-8AFC-C9F7874B7D96}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Với mã hàng đã từng mua thì bắt buộc phải điền
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{DA9EF3F1-4107-4774-A091-ECC95FFCDFD5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Phòng ban nào cần mua về lắp thành 1 thiết bị thì ghi
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{14533181-8D93-4B63-9771-09475C056E57}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tương đương cột good code hiện tại</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Nếu là mã đã từng mua thì vlook up với master hàng hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{195977E4-DEAC-47BC-8B3B-F1D59F297EB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hàm &amp; của phần mô tả hàng hóa. Tên mở thủ tục hải quan thay đổi theo mục đích sử dụng. Cột này chỉ là tên dự thảo của phòng ban, sau Ship sẽ xác nhận lại trước khi phát hành đơn yêu cầu hàng hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{5821CCFB-50F0-42EF-9731-75CC1AA57AC3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mã đã mua: Vlookup theo master
+Mã mới: Lựa chọn trong chủng loại hàng hóa trong master, nếu không có phải liên lạc Pur tạo    </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{E23422DC-E5AB-4BFE-B3D1-EDC43EBE5002}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nếu là hàng tự thiết kế thì copy link bản vẽ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{773049F6-5B16-4BF9-B730-56519B8041FF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nếu là hàng tự thiết kế thì copy link bản vẽ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{A8C341F1-284D-4562-B492-E16749EFBD86}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mã đã mua: Vlook up từ master</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã mới: Tự điền</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{2BAEC063-6C80-4C49-83B5-2394B9D1A11D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Link từ cột chủng loại hàng+master</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{5D8AF123-FB69-4758-AF51-E2AF4C9B0173}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Link từ cột chủng loại hàng+master</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0" xr:uid="{13F1075B-342E-41AA-A04C-84AEE940C94C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>O: cần lấy báo giá
+X: Không cần</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Nếu Không muốn lấy báo gía NCC nào thì PIC tự đổi thành X dòng tương ứng tên NCC đó</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0" xr:uid="{17F1DE41-F1F8-4CED-ABA9-253C01C54B77}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Điền lý do hợp lý với các NCC chọn X ở cột số 14</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V2" authorId="0" shapeId="0" xr:uid="{80DED770-1755-482D-842C-6C438F879DCE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ngày này đã bao gồm kỳ hạn lấy xong giá và đến bước lựa chọn NCC rồi. Vì các phòng ban đã có bước đề xuất NCC từ lúc đầu nên Pur sau khi lấy giá sẽ tự đề xuất NCC phù hợp giá và kỳ hạn giao hàng trong số NCC đó</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X2" authorId="0" shapeId="0" xr:uid="{24A31E98-6333-4FBA-BC47-957F3B304681}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tên của người yêu cầu mặt hàng này
+(vì mỗi phòng có 1 đảm nhiệm làm đơn, ghi chú này để ghi chú nhận yêu cầu từ ai</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA2" authorId="0" shapeId="0" xr:uid="{BB919831-00DE-465B-BB1B-C1134183F4A7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tên của người yêu cầu mặt hàng này
+(vì mỗi phòng có 1 đảm nhiệm làm đơn, ghi chú này để ghi chú nhận yêu cầu từ ai</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB2" authorId="0" shapeId="0" xr:uid="{598BAA52-BD24-498A-B2C9-A2B5267009D9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tên của người yêu cầu mặt hàng này
+(vì mỗi phòng có 1 đảm nhiệm làm đơn, ghi chú này để ghi chú nhận yêu cầu từ ai</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC2" authorId="0" shapeId="0" xr:uid="{22EDF694-05E0-4DA6-A01E-0517AA030FA3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tên của người yêu cầu mặt hàng này
+(vì mỗi phòng có 1 đảm nhiệm làm đơn, ghi chú này để ghi chú nhận yêu cầu từ ai</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD2" authorId="0" shapeId="0" xr:uid="{1F08A1EC-2BEF-4D1E-B406-BA814EB79315}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tên của người yêu cầu mặt hàng này
+(vì mỗi phòng có 1 đảm nhiệm làm đơn, ghi chú này để ghi chú nhận yêu cầu từ ai</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
   <si>
     <t>Chủng loại hàng
 Part category</t>
@@ -562,6 +984,40 @@
   </si>
   <si>
     <t>Link báo giá</t>
+  </si>
+  <si>
+    <t>PIC phòng ban yêu cầu</t>
+  </si>
+  <si>
+    <t>QLSC Phê duyệt</t>
+  </si>
+  <si>
+    <t>Thời gian QLSC phê duyệt</t>
+  </si>
+  <si>
+    <t>QLTC Phê duyệt</t>
+  </si>
+  <si>
+    <t>Thời gian QLTC phê duyệt</t>
+  </si>
+  <si>
+    <t>PIC phòng PUR tiếp nhận</t>
+  </si>
+  <si>
+    <t>Thời gian PIC PUR tiếp nhận</t>
+  </si>
+  <si>
+    <t>QLSC phòng PUR tiếp nhân</t>
+  </si>
+  <si>
+    <t>Thời gian QLSC PUR phê duyệt</t>
+  </si>
+  <si>
+    <t>Thời gian tạo đơn phòng ban</t>
+  </si>
+  <si>
+    <t>Link file Box
+Design(*)</t>
   </si>
 </sst>
 </file>
@@ -753,7 +1209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -791,6 +1247,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -832,6 +1289,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1168,18 +1631,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC2F7D2-707F-4FAA-BAE9-54D056C0C3CB}">
   <dimension ref="A1:AN755"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" customWidth="1"/>
     <col min="15" max="26" width="0" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1222,15 +1685,15 @@
       <c r="N1" s="1">
         <v>12</v>
       </c>
-      <c r="O1" s="19">
+      <c r="O1" s="20">
         <f>N1+1</f>
         <v>13</v>
       </c>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="22"/>
       <c r="U1" s="2">
         <v>14</v>
       </c>
@@ -1311,133 +1774,133 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="17" t="s">
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="V2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="17" t="s">
+      <c r="W2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="17" t="s">
+      <c r="X2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="17" t="s">
+      <c r="Y2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="17" t="s">
+      <c r="Z2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="17" t="s">
+      <c r="AA2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="17" t="s">
+      <c r="AB2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="17" t="s">
+      <c r="AC2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="AD2" s="17" t="s">
+      <c r="AD2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="AE2" s="17" t="s">
+      <c r="AE2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="AF2" s="17" t="s">
+      <c r="AF2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AG2" s="16" t="s">
+      <c r="AG2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="AH2" s="16" t="s">
+      <c r="AH2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="AI2" s="14" t="s">
+      <c r="AI2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AJ2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AK2" s="16" t="s">
+      <c r="AK2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AL2" s="13" t="s">
+      <c r="AL2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AM2" s="13" t="s">
+      <c r="AM2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AN2" s="13" t="s">
+      <c r="AN2" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="132" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+    <row r="3" spans="1:40" ht="115" x14ac:dyDescent="0.35">
+      <c r="A3" s="27"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
       <c r="O3" s="5" t="s">
         <v>19</v>
       </c>
@@ -1456,28 +1919,28 @@
       <c r="T3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="18"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="18"/>
-      <c r="AB3" s="18"/>
-      <c r="AC3" s="18"/>
-      <c r="AD3" s="18"/>
-      <c r="AE3" s="18"/>
-      <c r="AF3" s="18"/>
-      <c r="AG3" s="16"/>
-      <c r="AH3" s="16"/>
-      <c r="AI3" s="15"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" s="16"/>
-      <c r="AL3" s="13"/>
-      <c r="AM3" s="13"/>
-      <c r="AN3" s="13"/>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="16"/>
+      <c r="AJ3" s="16"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1519,7 +1982,7 @@
       <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -1561,7 +2024,7 @@
       <c r="AM5" s="6"/>
       <c r="AN5" s="6"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1603,7 +2066,7 @@
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1645,7 +2108,7 @@
       <c r="AM7" s="6"/>
       <c r="AN7" s="6"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1687,7 +2150,7 @@
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1729,7 +2192,7 @@
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1771,7 +2234,7 @@
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1813,7 +2276,7 @@
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -1855,7 +2318,7 @@
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1897,7 +2360,7 @@
       <c r="AM13" s="6"/>
       <c r="AN13" s="6"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1939,7 +2402,7 @@
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1981,7 +2444,7 @@
       <c r="AM15" s="6"/>
       <c r="AN15" s="6"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -2023,7 +2486,7 @@
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -2065,7 +2528,7 @@
       <c r="AM17" s="6"/>
       <c r="AN17" s="6"/>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2107,7 +2570,7 @@
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -2149,7 +2612,7 @@
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -2191,7 +2654,7 @@
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2233,7 +2696,7 @@
       <c r="AM21" s="6"/>
       <c r="AN21" s="6"/>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2275,7 +2738,7 @@
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2317,7 +2780,7 @@
       <c r="AM23" s="6"/>
       <c r="AN23" s="6"/>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2359,7 +2822,7 @@
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2401,7 +2864,7 @@
       <c r="AM25" s="6"/>
       <c r="AN25" s="6"/>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2443,7 +2906,7 @@
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2485,7 +2948,7 @@
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2527,7 +2990,7 @@
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2569,7 +3032,7 @@
       <c r="AM29" s="6"/>
       <c r="AN29" s="6"/>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2611,7 +3074,7 @@
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2653,7 +3116,7 @@
       <c r="AM31" s="6"/>
       <c r="AN31" s="6"/>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -2695,7 +3158,7 @@
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -2737,7 +3200,7 @@
       <c r="AM33" s="6"/>
       <c r="AN33" s="6"/>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2779,7 +3242,7 @@
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2821,7 +3284,7 @@
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -2863,7 +3326,7 @@
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -2905,7 +3368,7 @@
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -2947,7 +3410,7 @@
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -2989,7 +3452,7 @@
       <c r="AM39" s="6"/>
       <c r="AN39" s="6"/>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -3031,7 +3494,7 @@
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -3073,7 +3536,7 @@
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -3115,7 +3578,7 @@
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -3157,7 +3620,7 @@
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -3199,7 +3662,7 @@
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -3241,7 +3704,7 @@
       <c r="AM45" s="6"/>
       <c r="AN45" s="6"/>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -3283,7 +3746,7 @@
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -3325,7 +3788,7 @@
       <c r="AM47" s="6"/>
       <c r="AN47" s="6"/>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -3367,7 +3830,7 @@
       <c r="AM48" s="6"/>
       <c r="AN48" s="6"/>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -3409,7 +3872,7 @@
       <c r="AM49" s="6"/>
       <c r="AN49" s="6"/>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -3451,7 +3914,7 @@
       <c r="AM50" s="6"/>
       <c r="AN50" s="6"/>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -3493,7 +3956,7 @@
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -3535,7 +3998,7 @@
       <c r="AM52" s="6"/>
       <c r="AN52" s="6"/>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -3577,7 +4040,7 @@
       <c r="AM53" s="6"/>
       <c r="AN53" s="6"/>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -3619,7 +4082,7 @@
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -3661,7 +4124,7 @@
       <c r="AM55" s="6"/>
       <c r="AN55" s="6"/>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -3703,7 +4166,7 @@
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -3745,7 +4208,7 @@
       <c r="AM57" s="6"/>
       <c r="AN57" s="6"/>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3787,7 +4250,7 @@
       <c r="AM58" s="6"/>
       <c r="AN58" s="6"/>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3829,7 +4292,7 @@
       <c r="AM59" s="6"/>
       <c r="AN59" s="6"/>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3871,7 +4334,7 @@
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3913,7 +4376,7 @@
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -3955,7 +4418,7 @@
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -3997,7 +4460,7 @@
       <c r="AM63" s="6"/>
       <c r="AN63" s="6"/>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -4039,7 +4502,7 @@
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -4081,7 +4544,7 @@
       <c r="AM65" s="6"/>
       <c r="AN65" s="6"/>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -4123,7 +4586,7 @@
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -4165,7 +4628,7 @@
       <c r="AM67" s="6"/>
       <c r="AN67" s="6"/>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -4207,7 +4670,7 @@
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -4249,7 +4712,7 @@
       <c r="AM69" s="6"/>
       <c r="AN69" s="6"/>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -4291,7 +4754,7 @@
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -4333,7 +4796,7 @@
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -4375,7 +4838,7 @@
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
@@ -4417,7 +4880,7 @@
       <c r="AM73" s="6"/>
       <c r="AN73" s="6"/>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -4459,7 +4922,7 @@
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
@@ -4501,7 +4964,7 @@
       <c r="AM75" s="6"/>
       <c r="AN75" s="6"/>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -4543,7 +5006,7 @@
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
@@ -4585,7 +5048,7 @@
       <c r="AM77" s="6"/>
       <c r="AN77" s="6"/>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -4627,7 +5090,7 @@
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
     </row>
-    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
@@ -4669,7 +5132,7 @@
       <c r="AM79" s="6"/>
       <c r="AN79" s="6"/>
     </row>
-    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
@@ -4711,7 +5174,7 @@
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
     </row>
-    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
@@ -4753,7 +5216,7 @@
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
     </row>
-    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -4795,7 +5258,7 @@
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
     </row>
-    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
@@ -4837,7 +5300,7 @@
       <c r="AM83" s="6"/>
       <c r="AN83" s="6"/>
     </row>
-    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
@@ -4879,7 +5342,7 @@
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
     </row>
-    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -4921,7 +5384,7 @@
       <c r="AM85" s="6"/>
       <c r="AN85" s="6"/>
     </row>
-    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
@@ -4963,7 +5426,7 @@
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
     </row>
-    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
@@ -5005,7 +5468,7 @@
       <c r="AM87" s="6"/>
       <c r="AN87" s="6"/>
     </row>
-    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
@@ -5047,7 +5510,7 @@
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
     </row>
-    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -5089,7 +5552,7 @@
       <c r="AM89" s="6"/>
       <c r="AN89" s="6"/>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
@@ -5131,7 +5594,7 @@
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
     </row>
-    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
@@ -5173,7 +5636,7 @@
       <c r="AM91" s="6"/>
       <c r="AN91" s="6"/>
     </row>
-    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -5215,7 +5678,7 @@
       <c r="AM92" s="6"/>
       <c r="AN92" s="6"/>
     </row>
-    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -5257,7 +5720,7 @@
       <c r="AM93" s="6"/>
       <c r="AN93" s="6"/>
     </row>
-    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
@@ -5299,7 +5762,7 @@
       <c r="AM94" s="6"/>
       <c r="AN94" s="6"/>
     </row>
-    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -5341,7 +5804,7 @@
       <c r="AM95" s="6"/>
       <c r="AN95" s="6"/>
     </row>
-    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -5383,7 +5846,7 @@
       <c r="AM96" s="6"/>
       <c r="AN96" s="6"/>
     </row>
-    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -5425,7 +5888,7 @@
       <c r="AM97" s="6"/>
       <c r="AN97" s="6"/>
     </row>
-    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
@@ -5467,7 +5930,7 @@
       <c r="AM98" s="6"/>
       <c r="AN98" s="6"/>
     </row>
-    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
@@ -5509,7 +5972,7 @@
       <c r="AM99" s="6"/>
       <c r="AN99" s="6"/>
     </row>
-    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -5551,7 +6014,7 @@
       <c r="AM100" s="6"/>
       <c r="AN100" s="6"/>
     </row>
-    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -5593,7 +6056,7 @@
       <c r="AM101" s="6"/>
       <c r="AN101" s="6"/>
     </row>
-    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -5635,7 +6098,7 @@
       <c r="AM102" s="6"/>
       <c r="AN102" s="6"/>
     </row>
-    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -5677,7 +6140,7 @@
       <c r="AM103" s="6"/>
       <c r="AN103" s="6"/>
     </row>
-    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -5719,7 +6182,7 @@
       <c r="AM104" s="6"/>
       <c r="AN104" s="6"/>
     </row>
-    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -5761,7 +6224,7 @@
       <c r="AM105" s="6"/>
       <c r="AN105" s="6"/>
     </row>
-    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -5803,7 +6266,7 @@
       <c r="AM106" s="6"/>
       <c r="AN106" s="6"/>
     </row>
-    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -5845,7 +6308,7 @@
       <c r="AM107" s="6"/>
       <c r="AN107" s="6"/>
     </row>
-    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -5887,7 +6350,7 @@
       <c r="AM108" s="6"/>
       <c r="AN108" s="6"/>
     </row>
-    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -5929,7 +6392,7 @@
       <c r="AM109" s="6"/>
       <c r="AN109" s="6"/>
     </row>
-    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -5971,7 +6434,7 @@
       <c r="AM110" s="6"/>
       <c r="AN110" s="6"/>
     </row>
-    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -6013,7 +6476,7 @@
       <c r="AM111" s="6"/>
       <c r="AN111" s="6"/>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -6055,7 +6518,7 @@
       <c r="AM112" s="6"/>
       <c r="AN112" s="6"/>
     </row>
-    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -6097,7 +6560,7 @@
       <c r="AM113" s="6"/>
       <c r="AN113" s="6"/>
     </row>
-    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -6139,7 +6602,7 @@
       <c r="AM114" s="6"/>
       <c r="AN114" s="6"/>
     </row>
-    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -6181,7 +6644,7 @@
       <c r="AM115" s="6"/>
       <c r="AN115" s="6"/>
     </row>
-    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -6223,7 +6686,7 @@
       <c r="AM116" s="6"/>
       <c r="AN116" s="6"/>
     </row>
-    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -6265,7 +6728,7 @@
       <c r="AM117" s="6"/>
       <c r="AN117" s="6"/>
     </row>
-    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -6307,7 +6770,7 @@
       <c r="AM118" s="6"/>
       <c r="AN118" s="6"/>
     </row>
-    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -6349,7 +6812,7 @@
       <c r="AM119" s="6"/>
       <c r="AN119" s="6"/>
     </row>
-    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -6391,7 +6854,7 @@
       <c r="AM120" s="6"/>
       <c r="AN120" s="6"/>
     </row>
-    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -6433,7 +6896,7 @@
       <c r="AM121" s="6"/>
       <c r="AN121" s="6"/>
     </row>
-    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -6475,7 +6938,7 @@
       <c r="AM122" s="6"/>
       <c r="AN122" s="6"/>
     </row>
-    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -6517,7 +6980,7 @@
       <c r="AM123" s="6"/>
       <c r="AN123" s="6"/>
     </row>
-    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -6559,7 +7022,7 @@
       <c r="AM124" s="6"/>
       <c r="AN124" s="6"/>
     </row>
-    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -6601,7 +7064,7 @@
       <c r="AM125" s="6"/>
       <c r="AN125" s="6"/>
     </row>
-    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -6643,7 +7106,7 @@
       <c r="AM126" s="6"/>
       <c r="AN126" s="6"/>
     </row>
-    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -6685,7 +7148,7 @@
       <c r="AM127" s="6"/>
       <c r="AN127" s="6"/>
     </row>
-    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
@@ -6727,7 +7190,7 @@
       <c r="AM128" s="6"/>
       <c r="AN128" s="6"/>
     </row>
-    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -6769,7 +7232,7 @@
       <c r="AM129" s="6"/>
       <c r="AN129" s="6"/>
     </row>
-    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -6811,7 +7274,7 @@
       <c r="AM130" s="6"/>
       <c r="AN130" s="6"/>
     </row>
-    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -6853,7 +7316,7 @@
       <c r="AM131" s="6"/>
       <c r="AN131" s="6"/>
     </row>
-    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -6895,7 +7358,7 @@
       <c r="AM132" s="6"/>
       <c r="AN132" s="6"/>
     </row>
-    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -6937,7 +7400,7 @@
       <c r="AM133" s="6"/>
       <c r="AN133" s="6"/>
     </row>
-    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -6979,7 +7442,7 @@
       <c r="AM134" s="6"/>
       <c r="AN134" s="6"/>
     </row>
-    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -7021,7 +7484,7 @@
       <c r="AM135" s="6"/>
       <c r="AN135" s="6"/>
     </row>
-    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -7063,7 +7526,7 @@
       <c r="AM136" s="6"/>
       <c r="AN136" s="6"/>
     </row>
-    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -7105,7 +7568,7 @@
       <c r="AM137" s="6"/>
       <c r="AN137" s="6"/>
     </row>
-    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
@@ -7147,7 +7610,7 @@
       <c r="AM138" s="6"/>
       <c r="AN138" s="6"/>
     </row>
-    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -7189,7 +7652,7 @@
       <c r="AM139" s="6"/>
       <c r="AN139" s="6"/>
     </row>
-    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -7231,7 +7694,7 @@
       <c r="AM140" s="6"/>
       <c r="AN140" s="6"/>
     </row>
-    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -7273,7 +7736,7 @@
       <c r="AM141" s="6"/>
       <c r="AN141" s="6"/>
     </row>
-    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
@@ -7315,7 +7778,7 @@
       <c r="AM142" s="6"/>
       <c r="AN142" s="6"/>
     </row>
-    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
@@ -7357,7 +7820,7 @@
       <c r="AM143" s="6"/>
       <c r="AN143" s="6"/>
     </row>
-    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
@@ -7399,7 +7862,7 @@
       <c r="AM144" s="6"/>
       <c r="AN144" s="6"/>
     </row>
-    <row r="145" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
@@ -7441,7 +7904,7 @@
       <c r="AM145" s="6"/>
       <c r="AN145" s="6"/>
     </row>
-    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -7483,7 +7946,7 @@
       <c r="AM146" s="6"/>
       <c r="AN146" s="6"/>
     </row>
-    <row r="147" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12"/>
@@ -7525,7 +7988,7 @@
       <c r="AM147" s="6"/>
       <c r="AN147" s="6"/>
     </row>
-    <row r="148" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -7567,7 +8030,7 @@
       <c r="AM148" s="6"/>
       <c r="AN148" s="6"/>
     </row>
-    <row r="149" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
@@ -7609,7 +8072,7 @@
       <c r="AM149" s="6"/>
       <c r="AN149" s="6"/>
     </row>
-    <row r="150" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -7651,7 +8114,7 @@
       <c r="AM150" s="6"/>
       <c r="AN150" s="6"/>
     </row>
-    <row r="151" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
@@ -7693,7 +8156,7 @@
       <c r="AM151" s="6"/>
       <c r="AN151" s="6"/>
     </row>
-    <row r="152" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="12"/>
@@ -7735,7 +8198,7 @@
       <c r="AM152" s="6"/>
       <c r="AN152" s="6"/>
     </row>
-    <row r="153" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
@@ -7777,7 +8240,7 @@
       <c r="AM153" s="6"/>
       <c r="AN153" s="6"/>
     </row>
-    <row r="154" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -7819,7 +8282,7 @@
       <c r="AM154" s="6"/>
       <c r="AN154" s="6"/>
     </row>
-    <row r="155" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -7861,7 +8324,7 @@
       <c r="AM155" s="6"/>
       <c r="AN155" s="6"/>
     </row>
-    <row r="156" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -7903,7 +8366,7 @@
       <c r="AM156" s="6"/>
       <c r="AN156" s="6"/>
     </row>
-    <row r="157" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
@@ -7945,7 +8408,7 @@
       <c r="AM157" s="6"/>
       <c r="AN157" s="6"/>
     </row>
-    <row r="158" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12"/>
@@ -7987,7 +8450,7 @@
       <c r="AM158" s="6"/>
       <c r="AN158" s="6"/>
     </row>
-    <row r="159" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12"/>
@@ -8029,7 +8492,7 @@
       <c r="AM159" s="6"/>
       <c r="AN159" s="6"/>
     </row>
-    <row r="160" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12"/>
@@ -8071,7 +8534,7 @@
       <c r="AM160" s="6"/>
       <c r="AN160" s="6"/>
     </row>
-    <row r="161" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -8113,7 +8576,7 @@
       <c r="AM161" s="6"/>
       <c r="AN161" s="6"/>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
@@ -8155,7 +8618,7 @@
       <c r="AM162" s="6"/>
       <c r="AN162" s="6"/>
     </row>
-    <row r="163" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
@@ -8197,7 +8660,7 @@
       <c r="AM163" s="6"/>
       <c r="AN163" s="6"/>
     </row>
-    <row r="164" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12"/>
@@ -8239,7 +8702,7 @@
       <c r="AM164" s="6"/>
       <c r="AN164" s="6"/>
     </row>
-    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
@@ -8281,7 +8744,7 @@
       <c r="AM165" s="6"/>
       <c r="AN165" s="6"/>
     </row>
-    <row r="166" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
@@ -8323,7 +8786,7 @@
       <c r="AM166" s="6"/>
       <c r="AN166" s="6"/>
     </row>
-    <row r="167" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
@@ -8365,7 +8828,7 @@
       <c r="AM167" s="6"/>
       <c r="AN167" s="6"/>
     </row>
-    <row r="168" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -8407,7 +8870,7 @@
       <c r="AM168" s="6"/>
       <c r="AN168" s="6"/>
     </row>
-    <row r="169" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
@@ -8449,7 +8912,7 @@
       <c r="AM169" s="6"/>
       <c r="AN169" s="6"/>
     </row>
-    <row r="170" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
@@ -8491,7 +8954,7 @@
       <c r="AM170" s="6"/>
       <c r="AN170" s="6"/>
     </row>
-    <row r="171" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
@@ -8533,7 +8996,7 @@
       <c r="AM171" s="6"/>
       <c r="AN171" s="6"/>
     </row>
-    <row r="172" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -8575,7 +9038,7 @@
       <c r="AM172" s="6"/>
       <c r="AN172" s="6"/>
     </row>
-    <row r="173" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
@@ -8617,7 +9080,7 @@
       <c r="AM173" s="6"/>
       <c r="AN173" s="6"/>
     </row>
-    <row r="174" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
@@ -8659,7 +9122,7 @@
       <c r="AM174" s="6"/>
       <c r="AN174" s="6"/>
     </row>
-    <row r="175" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
@@ -8701,7 +9164,7 @@
       <c r="AM175" s="6"/>
       <c r="AN175" s="6"/>
     </row>
-    <row r="176" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
@@ -8743,7 +9206,7 @@
       <c r="AM176" s="6"/>
       <c r="AN176" s="6"/>
     </row>
-    <row r="177" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
@@ -8785,7 +9248,7 @@
       <c r="AM177" s="6"/>
       <c r="AN177" s="6"/>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
@@ -8827,7 +9290,7 @@
       <c r="AM178" s="6"/>
       <c r="AN178" s="6"/>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="12"/>
@@ -8869,7 +9332,7 @@
       <c r="AM179" s="6"/>
       <c r="AN179" s="6"/>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="12"/>
@@ -8911,7 +9374,7 @@
       <c r="AM180" s="6"/>
       <c r="AN180" s="6"/>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="12"/>
@@ -8953,7 +9416,7 @@
       <c r="AM181" s="6"/>
       <c r="AN181" s="6"/>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="12"/>
@@ -8995,7 +9458,7 @@
       <c r="AM182" s="6"/>
       <c r="AN182" s="6"/>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="12"/>
@@ -9037,7 +9500,7 @@
       <c r="AM183" s="6"/>
       <c r="AN183" s="6"/>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="12"/>
@@ -9079,7 +9542,7 @@
       <c r="AM184" s="6"/>
       <c r="AN184" s="6"/>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="12"/>
@@ -9121,7 +9584,7 @@
       <c r="AM185" s="6"/>
       <c r="AN185" s="6"/>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="12"/>
@@ -9163,7 +9626,7 @@
       <c r="AM186" s="6"/>
       <c r="AN186" s="6"/>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="12"/>
@@ -9205,7 +9668,7 @@
       <c r="AM187" s="6"/>
       <c r="AN187" s="6"/>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
@@ -9247,7 +9710,7 @@
       <c r="AM188" s="6"/>
       <c r="AN188" s="6"/>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="12"/>
@@ -9289,7 +9752,7 @@
       <c r="AM189" s="6"/>
       <c r="AN189" s="6"/>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="12"/>
@@ -9331,7 +9794,7 @@
       <c r="AM190" s="6"/>
       <c r="AN190" s="6"/>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="12"/>
@@ -9373,7 +9836,7 @@
       <c r="AM191" s="6"/>
       <c r="AN191" s="6"/>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
@@ -9415,7 +9878,7 @@
       <c r="AM192" s="6"/>
       <c r="AN192" s="6"/>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="12"/>
@@ -9457,7 +9920,7 @@
       <c r="AM193" s="6"/>
       <c r="AN193" s="6"/>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="12"/>
@@ -9499,7 +9962,7 @@
       <c r="AM194" s="6"/>
       <c r="AN194" s="6"/>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="12"/>
@@ -9541,7 +10004,7 @@
       <c r="AM195" s="6"/>
       <c r="AN195" s="6"/>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="12"/>
@@ -9583,7 +10046,7 @@
       <c r="AM196" s="6"/>
       <c r="AN196" s="6"/>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="12"/>
@@ -9625,7 +10088,7 @@
       <c r="AM197" s="6"/>
       <c r="AN197" s="6"/>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="12"/>
@@ -9667,7 +10130,7 @@
       <c r="AM198" s="6"/>
       <c r="AN198" s="6"/>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="12"/>
@@ -9709,7 +10172,7 @@
       <c r="AM199" s="6"/>
       <c r="AN199" s="6"/>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="12"/>
@@ -9751,7 +10214,7 @@
       <c r="AM200" s="6"/>
       <c r="AN200" s="6"/>
     </row>
-    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="12"/>
@@ -9793,7 +10256,7 @@
       <c r="AM201" s="6"/>
       <c r="AN201" s="6"/>
     </row>
-    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="12"/>
@@ -9835,7 +10298,7 @@
       <c r="AM202" s="6"/>
       <c r="AN202" s="6"/>
     </row>
-    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="12"/>
@@ -9877,7 +10340,7 @@
       <c r="AM203" s="6"/>
       <c r="AN203" s="6"/>
     </row>
-    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="12"/>
@@ -9919,7 +10382,7 @@
       <c r="AM204" s="6"/>
       <c r="AN204" s="6"/>
     </row>
-    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="12"/>
@@ -9961,7 +10424,7 @@
       <c r="AM205" s="6"/>
       <c r="AN205" s="6"/>
     </row>
-    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="12"/>
@@ -10003,7 +10466,7 @@
       <c r="AM206" s="6"/>
       <c r="AN206" s="6"/>
     </row>
-    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12"/>
@@ -10045,7 +10508,7 @@
       <c r="AM207" s="6"/>
       <c r="AN207" s="6"/>
     </row>
-    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12"/>
@@ -10087,7 +10550,7 @@
       <c r="AM208" s="6"/>
       <c r="AN208" s="6"/>
     </row>
-    <row r="209" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12"/>
@@ -10129,7 +10592,7 @@
       <c r="AM209" s="6"/>
       <c r="AN209" s="6"/>
     </row>
-    <row r="210" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12"/>
@@ -10171,7 +10634,7 @@
       <c r="AM210" s="6"/>
       <c r="AN210" s="6"/>
     </row>
-    <row r="211" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12"/>
@@ -10213,7 +10676,7 @@
       <c r="AM211" s="6"/>
       <c r="AN211" s="6"/>
     </row>
-    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12"/>
@@ -10255,7 +10718,7 @@
       <c r="AM212" s="6"/>
       <c r="AN212" s="6"/>
     </row>
-    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12"/>
@@ -10297,7 +10760,7 @@
       <c r="AM213" s="6"/>
       <c r="AN213" s="6"/>
     </row>
-    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -10339,7 +10802,7 @@
       <c r="AM214" s="6"/>
       <c r="AN214" s="6"/>
     </row>
-    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="12"/>
@@ -10381,7 +10844,7 @@
       <c r="AM215" s="6"/>
       <c r="AN215" s="6"/>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="12"/>
@@ -10423,7 +10886,7 @@
       <c r="AM216" s="6"/>
       <c r="AN216" s="6"/>
     </row>
-    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="12"/>
@@ -10465,7 +10928,7 @@
       <c r="AM217" s="6"/>
       <c r="AN217" s="6"/>
     </row>
-    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="12"/>
@@ -10507,7 +10970,7 @@
       <c r="AM218" s="6"/>
       <c r="AN218" s="6"/>
     </row>
-    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="12"/>
@@ -10549,7 +11012,7 @@
       <c r="AM219" s="6"/>
       <c r="AN219" s="6"/>
     </row>
-    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="12"/>
@@ -10591,7 +11054,7 @@
       <c r="AM220" s="6"/>
       <c r="AN220" s="6"/>
     </row>
-    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="12"/>
@@ -10633,7 +11096,7 @@
       <c r="AM221" s="6"/>
       <c r="AN221" s="6"/>
     </row>
-    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="12"/>
@@ -10675,7 +11138,7 @@
       <c r="AM222" s="6"/>
       <c r="AN222" s="6"/>
     </row>
-    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="12"/>
@@ -10717,7 +11180,7 @@
       <c r="AM223" s="6"/>
       <c r="AN223" s="6"/>
     </row>
-    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="12"/>
@@ -10759,7 +11222,7 @@
       <c r="AM224" s="6"/>
       <c r="AN224" s="6"/>
     </row>
-    <row r="225" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="12"/>
@@ -10801,7 +11264,7 @@
       <c r="AM225" s="6"/>
       <c r="AN225" s="6"/>
     </row>
-    <row r="226" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="12"/>
@@ -10843,7 +11306,7 @@
       <c r="AM226" s="6"/>
       <c r="AN226" s="6"/>
     </row>
-    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="12"/>
@@ -10885,7 +11348,7 @@
       <c r="AM227" s="6"/>
       <c r="AN227" s="6"/>
     </row>
-    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="12"/>
@@ -10927,7 +11390,7 @@
       <c r="AM228" s="6"/>
       <c r="AN228" s="6"/>
     </row>
-    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="12"/>
@@ -10969,7 +11432,7 @@
       <c r="AM229" s="6"/>
       <c r="AN229" s="6"/>
     </row>
-    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="12"/>
@@ -11011,7 +11474,7 @@
       <c r="AM230" s="6"/>
       <c r="AN230" s="6"/>
     </row>
-    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="12"/>
@@ -11053,7 +11516,7 @@
       <c r="AM231" s="6"/>
       <c r="AN231" s="6"/>
     </row>
-    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="12"/>
@@ -11095,7 +11558,7 @@
       <c r="AM232" s="6"/>
       <c r="AN232" s="6"/>
     </row>
-    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="12"/>
@@ -11137,7 +11600,7 @@
       <c r="AM233" s="6"/>
       <c r="AN233" s="6"/>
     </row>
-    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="12"/>
@@ -11179,7 +11642,7 @@
       <c r="AM234" s="6"/>
       <c r="AN234" s="6"/>
     </row>
-    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="12"/>
@@ -11221,7 +11684,7 @@
       <c r="AM235" s="6"/>
       <c r="AN235" s="6"/>
     </row>
-    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="12"/>
@@ -11263,7 +11726,7 @@
       <c r="AM236" s="6"/>
       <c r="AN236" s="6"/>
     </row>
-    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="12"/>
@@ -11305,7 +11768,7 @@
       <c r="AM237" s="6"/>
       <c r="AN237" s="6"/>
     </row>
-    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="12"/>
@@ -11347,7 +11810,7 @@
       <c r="AM238" s="6"/>
       <c r="AN238" s="6"/>
     </row>
-    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="12"/>
@@ -11389,7 +11852,7 @@
       <c r="AM239" s="6"/>
       <c r="AN239" s="6"/>
     </row>
-    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="12"/>
@@ -11431,7 +11894,7 @@
       <c r="AM240" s="6"/>
       <c r="AN240" s="6"/>
     </row>
-    <row r="241" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
@@ -11473,7 +11936,7 @@
       <c r="AM241" s="6"/>
       <c r="AN241" s="6"/>
     </row>
-    <row r="242" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="12"/>
@@ -11515,7 +11978,7 @@
       <c r="AM242" s="6"/>
       <c r="AN242" s="6"/>
     </row>
-    <row r="243" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="12"/>
@@ -11557,7 +12020,7 @@
       <c r="AM243" s="6"/>
       <c r="AN243" s="6"/>
     </row>
-    <row r="244" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="12"/>
@@ -11599,7 +12062,7 @@
       <c r="AM244" s="6"/>
       <c r="AN244" s="6"/>
     </row>
-    <row r="245" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="12"/>
@@ -11641,7 +12104,7 @@
       <c r="AM245" s="6"/>
       <c r="AN245" s="6"/>
     </row>
-    <row r="246" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="12"/>
@@ -11683,7 +12146,7 @@
       <c r="AM246" s="6"/>
       <c r="AN246" s="6"/>
     </row>
-    <row r="247" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="12"/>
@@ -11725,7 +12188,7 @@
       <c r="AM247" s="6"/>
       <c r="AN247" s="6"/>
     </row>
-    <row r="248" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="12"/>
@@ -11767,7 +12230,7 @@
       <c r="AM248" s="6"/>
       <c r="AN248" s="6"/>
     </row>
-    <row r="249" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="12"/>
@@ -11809,7 +12272,7 @@
       <c r="AM249" s="6"/>
       <c r="AN249" s="6"/>
     </row>
-    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="12"/>
@@ -11851,7 +12314,7 @@
       <c r="AM250" s="6"/>
       <c r="AN250" s="6"/>
     </row>
-    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="12"/>
@@ -11893,7 +12356,7 @@
       <c r="AM251" s="6"/>
       <c r="AN251" s="6"/>
     </row>
-    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="12"/>
@@ -11935,7 +12398,7 @@
       <c r="AM252" s="6"/>
       <c r="AN252" s="6"/>
     </row>
-    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="12"/>
@@ -11977,7 +12440,7 @@
       <c r="AM253" s="6"/>
       <c r="AN253" s="6"/>
     </row>
-    <row r="254" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="12"/>
@@ -12019,7 +12482,7 @@
       <c r="AM254" s="6"/>
       <c r="AN254" s="6"/>
     </row>
-    <row r="255" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -12061,7 +12524,7 @@
       <c r="AM255" s="6"/>
       <c r="AN255" s="6"/>
     </row>
-    <row r="256" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="12"/>
@@ -12103,7 +12566,7 @@
       <c r="AM256" s="6"/>
       <c r="AN256" s="6"/>
     </row>
-    <row r="257" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="12"/>
@@ -12145,7 +12608,7 @@
       <c r="AM257" s="6"/>
       <c r="AN257" s="6"/>
     </row>
-    <row r="258" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
@@ -12187,7 +12650,7 @@
       <c r="AM258" s="6"/>
       <c r="AN258" s="6"/>
     </row>
-    <row r="259" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
@@ -12229,7 +12692,7 @@
       <c r="AM259" s="6"/>
       <c r="AN259" s="6"/>
     </row>
-    <row r="260" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
@@ -12271,7 +12734,7 @@
       <c r="AM260" s="6"/>
       <c r="AN260" s="6"/>
     </row>
-    <row r="261" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
@@ -12313,7 +12776,7 @@
       <c r="AM261" s="6"/>
       <c r="AN261" s="6"/>
     </row>
-    <row r="262" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
@@ -12355,7 +12818,7 @@
       <c r="AM262" s="6"/>
       <c r="AN262" s="6"/>
     </row>
-    <row r="263" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -12397,7 +12860,7 @@
       <c r="AM263" s="6"/>
       <c r="AN263" s="6"/>
     </row>
-    <row r="264" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="12"/>
@@ -12439,7 +12902,7 @@
       <c r="AM264" s="6"/>
       <c r="AN264" s="6"/>
     </row>
-    <row r="265" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="12"/>
@@ -12481,7 +12944,7 @@
       <c r="AM265" s="6"/>
       <c r="AN265" s="6"/>
     </row>
-    <row r="266" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="12"/>
@@ -12523,7 +12986,7 @@
       <c r="AM266" s="6"/>
       <c r="AN266" s="6"/>
     </row>
-    <row r="267" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="12"/>
@@ -12565,7 +13028,7 @@
       <c r="AM267" s="6"/>
       <c r="AN267" s="6"/>
     </row>
-    <row r="268" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
@@ -12607,7 +13070,7 @@
       <c r="AM268" s="6"/>
       <c r="AN268" s="6"/>
     </row>
-    <row r="269" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="12"/>
@@ -12649,7 +13112,7 @@
       <c r="AM269" s="6"/>
       <c r="AN269" s="6"/>
     </row>
-    <row r="270" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A270" s="12"/>
       <c r="B270" s="12"/>
       <c r="C270" s="12"/>
@@ -12691,7 +13154,7 @@
       <c r="AM270" s="6"/>
       <c r="AN270" s="6"/>
     </row>
-    <row r="271" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A271" s="12"/>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
@@ -12733,7 +13196,7 @@
       <c r="AM271" s="6"/>
       <c r="AN271" s="6"/>
     </row>
-    <row r="272" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A272" s="12"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
@@ -12775,7 +13238,7 @@
       <c r="AM272" s="6"/>
       <c r="AN272" s="6"/>
     </row>
-    <row r="273" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A273" s="12"/>
       <c r="B273" s="12"/>
       <c r="C273" s="12"/>
@@ -12817,7 +13280,7 @@
       <c r="AM273" s="6"/>
       <c r="AN273" s="6"/>
     </row>
-    <row r="274" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -12859,7 +13322,7 @@
       <c r="AM274" s="6"/>
       <c r="AN274" s="6"/>
     </row>
-    <row r="275" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -12901,7 +13364,7 @@
       <c r="AM275" s="6"/>
       <c r="AN275" s="6"/>
     </row>
-    <row r="276" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -12943,7 +13406,7 @@
       <c r="AM276" s="6"/>
       <c r="AN276" s="6"/>
     </row>
-    <row r="277" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -12985,7 +13448,7 @@
       <c r="AM277" s="6"/>
       <c r="AN277" s="6"/>
     </row>
-    <row r="278" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -13027,7 +13490,7 @@
       <c r="AM278" s="6"/>
       <c r="AN278" s="6"/>
     </row>
-    <row r="279" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12"/>
@@ -13069,7 +13532,7 @@
       <c r="AM279" s="6"/>
       <c r="AN279" s="6"/>
     </row>
-    <row r="280" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -13111,7 +13574,7 @@
       <c r="AM280" s="6"/>
       <c r="AN280" s="6"/>
     </row>
-    <row r="281" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -13153,7 +13616,7 @@
       <c r="AM281" s="6"/>
       <c r="AN281" s="6"/>
     </row>
-    <row r="282" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -13195,7 +13658,7 @@
       <c r="AM282" s="6"/>
       <c r="AN282" s="6"/>
     </row>
-    <row r="283" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -13237,7 +13700,7 @@
       <c r="AM283" s="6"/>
       <c r="AN283" s="6"/>
     </row>
-    <row r="284" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -13279,7 +13742,7 @@
       <c r="AM284" s="6"/>
       <c r="AN284" s="6"/>
     </row>
-    <row r="285" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A285" s="12"/>
       <c r="B285" s="12"/>
       <c r="C285" s="12"/>
@@ -13321,7 +13784,7 @@
       <c r="AM285" s="6"/>
       <c r="AN285" s="6"/>
     </row>
-    <row r="286" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A286" s="12"/>
       <c r="B286" s="12"/>
       <c r="C286" s="12"/>
@@ -13363,7 +13826,7 @@
       <c r="AM286" s="6"/>
       <c r="AN286" s="6"/>
     </row>
-    <row r="287" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A287" s="12"/>
       <c r="B287" s="12"/>
       <c r="C287" s="12"/>
@@ -13405,7 +13868,7 @@
       <c r="AM287" s="6"/>
       <c r="AN287" s="6"/>
     </row>
-    <row r="288" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A288" s="12"/>
       <c r="B288" s="12"/>
       <c r="C288" s="12"/>
@@ -13447,7 +13910,7 @@
       <c r="AM288" s="6"/>
       <c r="AN288" s="6"/>
     </row>
-    <row r="289" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A289" s="12"/>
       <c r="B289" s="12"/>
       <c r="C289" s="12"/>
@@ -13489,7 +13952,7 @@
       <c r="AM289" s="6"/>
       <c r="AN289" s="6"/>
     </row>
-    <row r="290" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A290" s="12"/>
       <c r="B290" s="12"/>
       <c r="C290" s="12"/>
@@ -13531,7 +13994,7 @@
       <c r="AM290" s="6"/>
       <c r="AN290" s="6"/>
     </row>
-    <row r="291" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A291" s="12"/>
       <c r="B291" s="12"/>
       <c r="C291" s="12"/>
@@ -13573,7 +14036,7 @@
       <c r="AM291" s="6"/>
       <c r="AN291" s="6"/>
     </row>
-    <row r="292" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A292" s="12"/>
       <c r="B292" s="12"/>
       <c r="C292" s="12"/>
@@ -13615,7 +14078,7 @@
       <c r="AM292" s="6"/>
       <c r="AN292" s="6"/>
     </row>
-    <row r="293" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A293" s="12"/>
       <c r="B293" s="12"/>
       <c r="C293" s="12"/>
@@ -13657,7 +14120,7 @@
       <c r="AM293" s="6"/>
       <c r="AN293" s="6"/>
     </row>
-    <row r="294" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A294" s="12"/>
       <c r="B294" s="12"/>
       <c r="C294" s="12"/>
@@ -13699,7 +14162,7 @@
       <c r="AM294" s="6"/>
       <c r="AN294" s="6"/>
     </row>
-    <row r="295" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A295" s="12"/>
       <c r="B295" s="12"/>
       <c r="C295" s="12"/>
@@ -13741,7 +14204,7 @@
       <c r="AM295" s="6"/>
       <c r="AN295" s="6"/>
     </row>
-    <row r="296" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12"/>
@@ -13783,7 +14246,7 @@
       <c r="AM296" s="6"/>
       <c r="AN296" s="6"/>
     </row>
-    <row r="297" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12"/>
@@ -13825,7 +14288,7 @@
       <c r="AM297" s="6"/>
       <c r="AN297" s="6"/>
     </row>
-    <row r="298" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A298" s="12"/>
       <c r="B298" s="12"/>
       <c r="C298" s="12"/>
@@ -13867,7 +14330,7 @@
       <c r="AM298" s="6"/>
       <c r="AN298" s="6"/>
     </row>
-    <row r="299" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12"/>
@@ -13909,7 +14372,7 @@
       <c r="AM299" s="6"/>
       <c r="AN299" s="6"/>
     </row>
-    <row r="300" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12"/>
@@ -13951,7 +14414,7 @@
       <c r="AM300" s="6"/>
       <c r="AN300" s="6"/>
     </row>
-    <row r="301" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A301" s="12"/>
       <c r="B301" s="12"/>
       <c r="C301" s="12"/>
@@ -13993,7 +14456,7 @@
       <c r="AM301" s="6"/>
       <c r="AN301" s="6"/>
     </row>
-    <row r="302" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A302" s="12"/>
       <c r="B302" s="12"/>
       <c r="C302" s="12"/>
@@ -14035,7 +14498,7 @@
       <c r="AM302" s="6"/>
       <c r="AN302" s="6"/>
     </row>
-    <row r="303" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A303" s="12"/>
       <c r="B303" s="12"/>
       <c r="C303" s="12"/>
@@ -14077,7 +14540,7 @@
       <c r="AM303" s="6"/>
       <c r="AN303" s="6"/>
     </row>
-    <row r="304" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A304" s="12"/>
       <c r="B304" s="12"/>
       <c r="C304" s="12"/>
@@ -14119,7 +14582,7 @@
       <c r="AM304" s="6"/>
       <c r="AN304" s="6"/>
     </row>
-    <row r="305" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A305" s="12"/>
       <c r="B305" s="12"/>
       <c r="C305" s="12"/>
@@ -14161,7 +14624,7 @@
       <c r="AM305" s="6"/>
       <c r="AN305" s="6"/>
     </row>
-    <row r="306" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A306" s="12"/>
       <c r="B306" s="12"/>
       <c r="C306" s="12"/>
@@ -14203,7 +14666,7 @@
       <c r="AM306" s="6"/>
       <c r="AN306" s="6"/>
     </row>
-    <row r="307" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A307" s="12"/>
       <c r="B307" s="12"/>
       <c r="C307" s="12"/>
@@ -14245,7 +14708,7 @@
       <c r="AM307" s="6"/>
       <c r="AN307" s="6"/>
     </row>
-    <row r="308" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A308" s="12"/>
       <c r="B308" s="12"/>
       <c r="C308" s="12"/>
@@ -14287,7 +14750,7 @@
       <c r="AM308" s="6"/>
       <c r="AN308" s="6"/>
     </row>
-    <row r="309" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A309" s="12"/>
       <c r="B309" s="12"/>
       <c r="C309" s="12"/>
@@ -14329,7 +14792,7 @@
       <c r="AM309" s="6"/>
       <c r="AN309" s="6"/>
     </row>
-    <row r="310" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A310" s="12"/>
       <c r="B310" s="12"/>
       <c r="C310" s="12"/>
@@ -14371,7 +14834,7 @@
       <c r="AM310" s="6"/>
       <c r="AN310" s="6"/>
     </row>
-    <row r="311" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -14413,7 +14876,7 @@
       <c r="AM311" s="6"/>
       <c r="AN311" s="6"/>
     </row>
-    <row r="312" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A312" s="12"/>
       <c r="B312" s="12"/>
       <c r="C312" s="12"/>
@@ -14455,7 +14918,7 @@
       <c r="AM312" s="6"/>
       <c r="AN312" s="6"/>
     </row>
-    <row r="313" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A313" s="12"/>
       <c r="B313" s="12"/>
       <c r="C313" s="12"/>
@@ -14497,7 +14960,7 @@
       <c r="AM313" s="6"/>
       <c r="AN313" s="6"/>
     </row>
-    <row r="314" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A314" s="12"/>
       <c r="B314" s="12"/>
       <c r="C314" s="12"/>
@@ -14539,7 +15002,7 @@
       <c r="AM314" s="6"/>
       <c r="AN314" s="6"/>
     </row>
-    <row r="315" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A315" s="12"/>
       <c r="B315" s="12"/>
       <c r="C315" s="12"/>
@@ -14581,7 +15044,7 @@
       <c r="AM315" s="6"/>
       <c r="AN315" s="6"/>
     </row>
-    <row r="316" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A316" s="12"/>
       <c r="B316" s="12"/>
       <c r="C316" s="12"/>
@@ -14623,7 +15086,7 @@
       <c r="AM316" s="6"/>
       <c r="AN316" s="6"/>
     </row>
-    <row r="317" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A317" s="12"/>
       <c r="B317" s="12"/>
       <c r="C317" s="12"/>
@@ -14665,7 +15128,7 @@
       <c r="AM317" s="6"/>
       <c r="AN317" s="6"/>
     </row>
-    <row r="318" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A318" s="12"/>
       <c r="B318" s="12"/>
       <c r="C318" s="12"/>
@@ -14707,7 +15170,7 @@
       <c r="AM318" s="6"/>
       <c r="AN318" s="6"/>
     </row>
-    <row r="319" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A319" s="12"/>
       <c r="B319" s="12"/>
       <c r="C319" s="12"/>
@@ -14749,7 +15212,7 @@
       <c r="AM319" s="6"/>
       <c r="AN319" s="6"/>
     </row>
-    <row r="320" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A320" s="12"/>
       <c r="B320" s="12"/>
       <c r="C320" s="12"/>
@@ -14791,7 +15254,7 @@
       <c r="AM320" s="6"/>
       <c r="AN320" s="6"/>
     </row>
-    <row r="321" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A321" s="12"/>
       <c r="B321" s="12"/>
       <c r="C321" s="12"/>
@@ -14833,7 +15296,7 @@
       <c r="AM321" s="6"/>
       <c r="AN321" s="6"/>
     </row>
-    <row r="322" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A322" s="12"/>
       <c r="B322" s="12"/>
       <c r="C322" s="12"/>
@@ -14875,7 +15338,7 @@
       <c r="AM322" s="6"/>
       <c r="AN322" s="6"/>
     </row>
-    <row r="323" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
@@ -14917,7 +15380,7 @@
       <c r="AM323" s="6"/>
       <c r="AN323" s="6"/>
     </row>
-    <row r="324" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A324" s="12"/>
       <c r="B324" s="12"/>
       <c r="C324" s="12"/>
@@ -14959,7 +15422,7 @@
       <c r="AM324" s="6"/>
       <c r="AN324" s="6"/>
     </row>
-    <row r="325" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A325" s="12"/>
       <c r="B325" s="12"/>
       <c r="C325" s="12"/>
@@ -15001,7 +15464,7 @@
       <c r="AM325" s="6"/>
       <c r="AN325" s="6"/>
     </row>
-    <row r="326" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A326" s="12"/>
       <c r="B326" s="12"/>
       <c r="C326" s="12"/>
@@ -15043,7 +15506,7 @@
       <c r="AM326" s="6"/>
       <c r="AN326" s="6"/>
     </row>
-    <row r="327" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A327" s="12"/>
       <c r="B327" s="12"/>
       <c r="C327" s="12"/>
@@ -15085,7 +15548,7 @@
       <c r="AM327" s="6"/>
       <c r="AN327" s="6"/>
     </row>
-    <row r="328" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A328" s="12"/>
       <c r="B328" s="12"/>
       <c r="C328" s="12"/>
@@ -15127,7 +15590,7 @@
       <c r="AM328" s="6"/>
       <c r="AN328" s="6"/>
     </row>
-    <row r="329" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A329" s="12"/>
       <c r="B329" s="12"/>
       <c r="C329" s="12"/>
@@ -15169,7 +15632,7 @@
       <c r="AM329" s="6"/>
       <c r="AN329" s="6"/>
     </row>
-    <row r="330" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A330" s="12"/>
       <c r="B330" s="12"/>
       <c r="C330" s="12"/>
@@ -15211,7 +15674,7 @@
       <c r="AM330" s="6"/>
       <c r="AN330" s="6"/>
     </row>
-    <row r="331" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A331" s="12"/>
       <c r="B331" s="12"/>
       <c r="C331" s="12"/>
@@ -15253,7 +15716,7 @@
       <c r="AM331" s="6"/>
       <c r="AN331" s="6"/>
     </row>
-    <row r="332" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A332" s="12"/>
       <c r="B332" s="12"/>
       <c r="C332" s="12"/>
@@ -15295,7 +15758,7 @@
       <c r="AM332" s="6"/>
       <c r="AN332" s="6"/>
     </row>
-    <row r="333" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A333" s="12"/>
       <c r="B333" s="12"/>
       <c r="C333" s="12"/>
@@ -15337,7 +15800,7 @@
       <c r="AM333" s="6"/>
       <c r="AN333" s="6"/>
     </row>
-    <row r="334" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A334" s="12"/>
       <c r="B334" s="12"/>
       <c r="C334" s="12"/>
@@ -15379,7 +15842,7 @@
       <c r="AM334" s="6"/>
       <c r="AN334" s="6"/>
     </row>
-    <row r="335" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A335" s="12"/>
       <c r="B335" s="12"/>
       <c r="C335" s="12"/>
@@ -15421,7 +15884,7 @@
       <c r="AM335" s="6"/>
       <c r="AN335" s="6"/>
     </row>
-    <row r="336" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A336" s="12"/>
       <c r="B336" s="12"/>
       <c r="C336" s="12"/>
@@ -15463,7 +15926,7 @@
       <c r="AM336" s="6"/>
       <c r="AN336" s="6"/>
     </row>
-    <row r="337" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A337" s="12"/>
       <c r="B337" s="12"/>
       <c r="C337" s="12"/>
@@ -15505,7 +15968,7 @@
       <c r="AM337" s="6"/>
       <c r="AN337" s="6"/>
     </row>
-    <row r="338" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A338" s="12"/>
       <c r="B338" s="12"/>
       <c r="C338" s="12"/>
@@ -15547,7 +16010,7 @@
       <c r="AM338" s="6"/>
       <c r="AN338" s="6"/>
     </row>
-    <row r="339" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A339" s="12"/>
       <c r="B339" s="12"/>
       <c r="C339" s="12"/>
@@ -15589,7 +16052,7 @@
       <c r="AM339" s="6"/>
       <c r="AN339" s="6"/>
     </row>
-    <row r="340" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A340" s="12"/>
       <c r="B340" s="12"/>
       <c r="C340" s="12"/>
@@ -15631,7 +16094,7 @@
       <c r="AM340" s="6"/>
       <c r="AN340" s="6"/>
     </row>
-    <row r="341" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A341" s="12"/>
       <c r="B341" s="12"/>
       <c r="C341" s="12"/>
@@ -15673,7 +16136,7 @@
       <c r="AM341" s="6"/>
       <c r="AN341" s="6"/>
     </row>
-    <row r="342" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A342" s="12"/>
       <c r="B342" s="12"/>
       <c r="C342" s="12"/>
@@ -15715,7 +16178,7 @@
       <c r="AM342" s="6"/>
       <c r="AN342" s="6"/>
     </row>
-    <row r="343" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A343" s="12"/>
       <c r="B343" s="12"/>
       <c r="C343" s="12"/>
@@ -15757,7 +16220,7 @@
       <c r="AM343" s="6"/>
       <c r="AN343" s="6"/>
     </row>
-    <row r="344" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A344" s="12"/>
       <c r="B344" s="12"/>
       <c r="C344" s="12"/>
@@ -15799,7 +16262,7 @@
       <c r="AM344" s="6"/>
       <c r="AN344" s="6"/>
     </row>
-    <row r="345" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A345" s="12"/>
       <c r="B345" s="12"/>
       <c r="C345" s="12"/>
@@ -15841,7 +16304,7 @@
       <c r="AM345" s="6"/>
       <c r="AN345" s="6"/>
     </row>
-    <row r="346" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A346" s="12"/>
       <c r="B346" s="12"/>
       <c r="C346" s="12"/>
@@ -15883,7 +16346,7 @@
       <c r="AM346" s="6"/>
       <c r="AN346" s="6"/>
     </row>
-    <row r="347" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A347" s="12"/>
       <c r="B347" s="12"/>
       <c r="C347" s="12"/>
@@ -15925,7 +16388,7 @@
       <c r="AM347" s="6"/>
       <c r="AN347" s="6"/>
     </row>
-    <row r="348" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A348" s="12"/>
       <c r="B348" s="12"/>
       <c r="C348" s="12"/>
@@ -15967,7 +16430,7 @@
       <c r="AM348" s="6"/>
       <c r="AN348" s="6"/>
     </row>
-    <row r="349" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A349" s="12"/>
       <c r="B349" s="12"/>
       <c r="C349" s="12"/>
@@ -16009,7 +16472,7 @@
       <c r="AM349" s="6"/>
       <c r="AN349" s="6"/>
     </row>
-    <row r="350" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A350" s="12"/>
       <c r="B350" s="12"/>
       <c r="C350" s="12"/>
@@ -16051,7 +16514,7 @@
       <c r="AM350" s="6"/>
       <c r="AN350" s="6"/>
     </row>
-    <row r="351" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A351" s="12"/>
       <c r="B351" s="12"/>
       <c r="C351" s="12"/>
@@ -16093,7 +16556,7 @@
       <c r="AM351" s="6"/>
       <c r="AN351" s="6"/>
     </row>
-    <row r="352" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A352" s="12"/>
       <c r="B352" s="12"/>
       <c r="C352" s="12"/>
@@ -16135,7 +16598,7 @@
       <c r="AM352" s="6"/>
       <c r="AN352" s="6"/>
     </row>
-    <row r="353" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A353" s="12"/>
       <c r="B353" s="12"/>
       <c r="C353" s="12"/>
@@ -16177,7 +16640,7 @@
       <c r="AM353" s="6"/>
       <c r="AN353" s="6"/>
     </row>
-    <row r="354" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A354" s="12"/>
       <c r="B354" s="12"/>
       <c r="C354" s="12"/>
@@ -16219,7 +16682,7 @@
       <c r="AM354" s="6"/>
       <c r="AN354" s="6"/>
     </row>
-    <row r="355" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A355" s="12"/>
       <c r="B355" s="12"/>
       <c r="C355" s="12"/>
@@ -16261,7 +16724,7 @@
       <c r="AM355" s="6"/>
       <c r="AN355" s="6"/>
     </row>
-    <row r="356" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A356" s="12"/>
       <c r="B356" s="12"/>
       <c r="C356" s="12"/>
@@ -16303,7 +16766,7 @@
       <c r="AM356" s="6"/>
       <c r="AN356" s="6"/>
     </row>
-    <row r="357" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A357" s="12"/>
       <c r="B357" s="12"/>
       <c r="C357" s="12"/>
@@ -16345,7 +16808,7 @@
       <c r="AM357" s="6"/>
       <c r="AN357" s="6"/>
     </row>
-    <row r="358" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A358" s="12"/>
       <c r="B358" s="12"/>
       <c r="C358" s="12"/>
@@ -16387,7 +16850,7 @@
       <c r="AM358" s="6"/>
       <c r="AN358" s="6"/>
     </row>
-    <row r="359" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A359" s="12"/>
       <c r="B359" s="12"/>
       <c r="C359" s="12"/>
@@ -16429,7 +16892,7 @@
       <c r="AM359" s="6"/>
       <c r="AN359" s="6"/>
     </row>
-    <row r="360" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A360" s="12"/>
       <c r="B360" s="12"/>
       <c r="C360" s="12"/>
@@ -16471,7 +16934,7 @@
       <c r="AM360" s="6"/>
       <c r="AN360" s="6"/>
     </row>
-    <row r="361" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A361" s="12"/>
       <c r="B361" s="12"/>
       <c r="C361" s="12"/>
@@ -16513,7 +16976,7 @@
       <c r="AM361" s="6"/>
       <c r="AN361" s="6"/>
     </row>
-    <row r="362" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A362" s="12"/>
       <c r="B362" s="12"/>
       <c r="C362" s="12"/>
@@ -16555,7 +17018,7 @@
       <c r="AM362" s="6"/>
       <c r="AN362" s="6"/>
     </row>
-    <row r="363" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A363" s="12"/>
       <c r="B363" s="12"/>
       <c r="C363" s="12"/>
@@ -16597,7 +17060,7 @@
       <c r="AM363" s="6"/>
       <c r="AN363" s="6"/>
     </row>
-    <row r="364" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A364" s="12"/>
       <c r="B364" s="12"/>
       <c r="C364" s="12"/>
@@ -16639,7 +17102,7 @@
       <c r="AM364" s="6"/>
       <c r="AN364" s="6"/>
     </row>
-    <row r="365" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A365" s="12"/>
       <c r="B365" s="12"/>
       <c r="C365" s="12"/>
@@ -16681,7 +17144,7 @@
       <c r="AM365" s="6"/>
       <c r="AN365" s="6"/>
     </row>
-    <row r="366" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A366" s="12"/>
       <c r="B366" s="12"/>
       <c r="C366" s="12"/>
@@ -16723,7 +17186,7 @@
       <c r="AM366" s="6"/>
       <c r="AN366" s="6"/>
     </row>
-    <row r="367" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A367" s="12"/>
       <c r="B367" s="12"/>
       <c r="C367" s="12"/>
@@ -16765,7 +17228,7 @@
       <c r="AM367" s="6"/>
       <c r="AN367" s="6"/>
     </row>
-    <row r="368" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A368" s="12"/>
       <c r="B368" s="12"/>
       <c r="C368" s="12"/>
@@ -16807,7 +17270,7 @@
       <c r="AM368" s="6"/>
       <c r="AN368" s="6"/>
     </row>
-    <row r="369" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A369" s="12"/>
       <c r="B369" s="12"/>
       <c r="C369" s="12"/>
@@ -16849,7 +17312,7 @@
       <c r="AM369" s="6"/>
       <c r="AN369" s="6"/>
     </row>
-    <row r="370" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A370" s="12"/>
       <c r="B370" s="12"/>
       <c r="C370" s="12"/>
@@ -16891,7 +17354,7 @@
       <c r="AM370" s="6"/>
       <c r="AN370" s="6"/>
     </row>
-    <row r="371" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A371" s="12"/>
       <c r="B371" s="12"/>
       <c r="C371" s="12"/>
@@ -16933,7 +17396,7 @@
       <c r="AM371" s="6"/>
       <c r="AN371" s="6"/>
     </row>
-    <row r="372" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A372" s="12"/>
       <c r="B372" s="12"/>
       <c r="C372" s="12"/>
@@ -16975,7 +17438,7 @@
       <c r="AM372" s="6"/>
       <c r="AN372" s="6"/>
     </row>
-    <row r="373" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A373" s="12"/>
       <c r="B373" s="12"/>
       <c r="C373" s="12"/>
@@ -17017,7 +17480,7 @@
       <c r="AM373" s="6"/>
       <c r="AN373" s="6"/>
     </row>
-    <row r="374" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A374" s="12"/>
       <c r="B374" s="12"/>
       <c r="C374" s="12"/>
@@ -17059,7 +17522,7 @@
       <c r="AM374" s="6"/>
       <c r="AN374" s="6"/>
     </row>
-    <row r="375" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A375" s="12"/>
       <c r="B375" s="12"/>
       <c r="C375" s="12"/>
@@ -17101,7 +17564,7 @@
       <c r="AM375" s="6"/>
       <c r="AN375" s="6"/>
     </row>
-    <row r="376" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A376" s="12"/>
       <c r="B376" s="12"/>
       <c r="C376" s="12"/>
@@ -17143,7 +17606,7 @@
       <c r="AM376" s="6"/>
       <c r="AN376" s="6"/>
     </row>
-    <row r="377" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A377" s="12"/>
       <c r="B377" s="12"/>
       <c r="C377" s="12"/>
@@ -17185,7 +17648,7 @@
       <c r="AM377" s="6"/>
       <c r="AN377" s="6"/>
     </row>
-    <row r="378" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A378" s="12"/>
       <c r="B378" s="12"/>
       <c r="C378" s="12"/>
@@ -17227,7 +17690,7 @@
       <c r="AM378" s="6"/>
       <c r="AN378" s="6"/>
     </row>
-    <row r="379" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A379" s="12"/>
       <c r="B379" s="12"/>
       <c r="C379" s="12"/>
@@ -17269,7 +17732,7 @@
       <c r="AM379" s="6"/>
       <c r="AN379" s="6"/>
     </row>
-    <row r="380" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A380" s="12"/>
       <c r="B380" s="12"/>
       <c r="C380" s="12"/>
@@ -17311,7 +17774,7 @@
       <c r="AM380" s="6"/>
       <c r="AN380" s="6"/>
     </row>
-    <row r="381" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A381" s="12"/>
       <c r="B381" s="12"/>
       <c r="C381" s="12"/>
@@ -17353,7 +17816,7 @@
       <c r="AM381" s="6"/>
       <c r="AN381" s="6"/>
     </row>
-    <row r="382" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A382" s="12"/>
       <c r="B382" s="12"/>
       <c r="C382" s="12"/>
@@ -17395,7 +17858,7 @@
       <c r="AM382" s="6"/>
       <c r="AN382" s="6"/>
     </row>
-    <row r="383" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A383" s="12"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12"/>
@@ -17437,7 +17900,7 @@
       <c r="AM383" s="6"/>
       <c r="AN383" s="6"/>
     </row>
-    <row r="384" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A384" s="12"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12"/>
@@ -17479,7 +17942,7 @@
       <c r="AM384" s="6"/>
       <c r="AN384" s="6"/>
     </row>
-    <row r="385" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A385" s="12"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12"/>
@@ -17521,7 +17984,7 @@
       <c r="AM385" s="6"/>
       <c r="AN385" s="6"/>
     </row>
-    <row r="386" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A386" s="12"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12"/>
@@ -17563,7 +18026,7 @@
       <c r="AM386" s="6"/>
       <c r="AN386" s="6"/>
     </row>
-    <row r="387" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A387" s="12"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12"/>
@@ -17605,7 +18068,7 @@
       <c r="AM387" s="6"/>
       <c r="AN387" s="6"/>
     </row>
-    <row r="388" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A388" s="12"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12"/>
@@ -17647,7 +18110,7 @@
       <c r="AM388" s="6"/>
       <c r="AN388" s="6"/>
     </row>
-    <row r="389" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A389" s="12"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12"/>
@@ -17689,7 +18152,7 @@
       <c r="AM389" s="6"/>
       <c r="AN389" s="6"/>
     </row>
-    <row r="390" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A390" s="12"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -17731,7 +18194,7 @@
       <c r="AM390" s="6"/>
       <c r="AN390" s="6"/>
     </row>
-    <row r="391" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A391" s="12"/>
       <c r="B391" s="12"/>
       <c r="C391" s="12"/>
@@ -17773,7 +18236,7 @@
       <c r="AM391" s="6"/>
       <c r="AN391" s="6"/>
     </row>
-    <row r="392" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A392" s="12"/>
       <c r="B392" s="12"/>
       <c r="C392" s="12"/>
@@ -17815,7 +18278,7 @@
       <c r="AM392" s="6"/>
       <c r="AN392" s="6"/>
     </row>
-    <row r="393" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A393" s="12"/>
       <c r="B393" s="12"/>
       <c r="C393" s="12"/>
@@ -17857,7 +18320,7 @@
       <c r="AM393" s="6"/>
       <c r="AN393" s="6"/>
     </row>
-    <row r="394" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A394" s="12"/>
       <c r="B394" s="12"/>
       <c r="C394" s="12"/>
@@ -17899,7 +18362,7 @@
       <c r="AM394" s="6"/>
       <c r="AN394" s="6"/>
     </row>
-    <row r="395" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A395" s="12"/>
       <c r="B395" s="12"/>
       <c r="C395" s="12"/>
@@ -17941,7 +18404,7 @@
       <c r="AM395" s="6"/>
       <c r="AN395" s="6"/>
     </row>
-    <row r="396" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A396" s="12"/>
       <c r="B396" s="12"/>
       <c r="C396" s="12"/>
@@ -17983,7 +18446,7 @@
       <c r="AM396" s="6"/>
       <c r="AN396" s="6"/>
     </row>
-    <row r="397" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A397" s="12"/>
       <c r="B397" s="12"/>
       <c r="C397" s="12"/>
@@ -18025,7 +18488,7 @@
       <c r="AM397" s="6"/>
       <c r="AN397" s="6"/>
     </row>
-    <row r="398" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A398" s="12"/>
       <c r="B398" s="12"/>
       <c r="C398" s="12"/>
@@ -18067,7 +18530,7 @@
       <c r="AM398" s="6"/>
       <c r="AN398" s="6"/>
     </row>
-    <row r="399" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A399" s="12"/>
       <c r="B399" s="12"/>
       <c r="C399" s="12"/>
@@ -18109,7 +18572,7 @@
       <c r="AM399" s="6"/>
       <c r="AN399" s="6"/>
     </row>
-    <row r="400" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A400" s="12"/>
       <c r="B400" s="12"/>
       <c r="C400" s="12"/>
@@ -18151,7 +18614,7 @@
       <c r="AM400" s="6"/>
       <c r="AN400" s="6"/>
     </row>
-    <row r="401" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
@@ -18193,7 +18656,7 @@
       <c r="AM401" s="6"/>
       <c r="AN401" s="6"/>
     </row>
-    <row r="402" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A402" s="12"/>
       <c r="B402" s="12"/>
       <c r="C402" s="12"/>
@@ -18235,7 +18698,7 @@
       <c r="AM402" s="6"/>
       <c r="AN402" s="6"/>
     </row>
-    <row r="403" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A403" s="12"/>
       <c r="B403" s="12"/>
       <c r="C403" s="12"/>
@@ -18277,7 +18740,7 @@
       <c r="AM403" s="6"/>
       <c r="AN403" s="6"/>
     </row>
-    <row r="404" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A404" s="12"/>
       <c r="B404" s="12"/>
       <c r="C404" s="12"/>
@@ -18319,7 +18782,7 @@
       <c r="AM404" s="6"/>
       <c r="AN404" s="6"/>
     </row>
-    <row r="405" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
@@ -18361,7 +18824,7 @@
       <c r="AM405" s="6"/>
       <c r="AN405" s="6"/>
     </row>
-    <row r="406" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A406" s="12"/>
       <c r="B406" s="12"/>
       <c r="C406" s="12"/>
@@ -18403,7 +18866,7 @@
       <c r="AM406" s="6"/>
       <c r="AN406" s="6"/>
     </row>
-    <row r="407" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A407" s="12"/>
       <c r="B407" s="12"/>
       <c r="C407" s="12"/>
@@ -18445,7 +18908,7 @@
       <c r="AM407" s="6"/>
       <c r="AN407" s="6"/>
     </row>
-    <row r="408" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A408" s="12"/>
       <c r="B408" s="12"/>
       <c r="C408" s="12"/>
@@ -18487,7 +18950,7 @@
       <c r="AM408" s="6"/>
       <c r="AN408" s="6"/>
     </row>
-    <row r="409" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A409" s="12"/>
       <c r="B409" s="12"/>
       <c r="C409" s="12"/>
@@ -18529,7 +18992,7 @@
       <c r="AM409" s="6"/>
       <c r="AN409" s="6"/>
     </row>
-    <row r="410" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A410" s="12"/>
       <c r="B410" s="12"/>
       <c r="C410" s="12"/>
@@ -18571,7 +19034,7 @@
       <c r="AM410" s="6"/>
       <c r="AN410" s="6"/>
     </row>
-    <row r="411" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A411" s="12"/>
       <c r="B411" s="12"/>
       <c r="C411" s="12"/>
@@ -18613,7 +19076,7 @@
       <c r="AM411" s="6"/>
       <c r="AN411" s="6"/>
     </row>
-    <row r="412" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A412" s="12"/>
       <c r="B412" s="12"/>
       <c r="C412" s="12"/>
@@ -18655,7 +19118,7 @@
       <c r="AM412" s="6"/>
       <c r="AN412" s="6"/>
     </row>
-    <row r="413" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A413" s="12"/>
       <c r="B413" s="12"/>
       <c r="C413" s="12"/>
@@ -18697,7 +19160,7 @@
       <c r="AM413" s="6"/>
       <c r="AN413" s="6"/>
     </row>
-    <row r="414" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A414" s="12"/>
       <c r="B414" s="12"/>
       <c r="C414" s="12"/>
@@ -18739,7 +19202,7 @@
       <c r="AM414" s="6"/>
       <c r="AN414" s="6"/>
     </row>
-    <row r="415" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A415" s="12"/>
       <c r="B415" s="12"/>
       <c r="C415" s="12"/>
@@ -18781,7 +19244,7 @@
       <c r="AM415" s="6"/>
       <c r="AN415" s="6"/>
     </row>
-    <row r="416" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A416" s="12"/>
       <c r="B416" s="12"/>
       <c r="C416" s="12"/>
@@ -18823,7 +19286,7 @@
       <c r="AM416" s="6"/>
       <c r="AN416" s="6"/>
     </row>
-    <row r="417" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A417" s="12"/>
       <c r="B417" s="12"/>
       <c r="C417" s="12"/>
@@ -18865,7 +19328,7 @@
       <c r="AM417" s="6"/>
       <c r="AN417" s="6"/>
     </row>
-    <row r="418" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A418" s="12"/>
       <c r="B418" s="12"/>
       <c r="C418" s="12"/>
@@ -18907,7 +19370,7 @@
       <c r="AM418" s="6"/>
       <c r="AN418" s="6"/>
     </row>
-    <row r="419" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A419" s="12"/>
       <c r="B419" s="12"/>
       <c r="C419" s="12"/>
@@ -18949,7 +19412,7 @@
       <c r="AM419" s="6"/>
       <c r="AN419" s="6"/>
     </row>
-    <row r="420" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A420" s="12"/>
       <c r="B420" s="12"/>
       <c r="C420" s="12"/>
@@ -18991,7 +19454,7 @@
       <c r="AM420" s="6"/>
       <c r="AN420" s="6"/>
     </row>
-    <row r="421" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A421" s="12"/>
       <c r="B421" s="12"/>
       <c r="C421" s="12"/>
@@ -19033,7 +19496,7 @@
       <c r="AM421" s="6"/>
       <c r="AN421" s="6"/>
     </row>
-    <row r="422" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A422" s="12"/>
       <c r="B422" s="12"/>
       <c r="C422" s="12"/>
@@ -19075,7 +19538,7 @@
       <c r="AM422" s="6"/>
       <c r="AN422" s="6"/>
     </row>
-    <row r="423" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A423" s="12"/>
       <c r="B423" s="12"/>
       <c r="C423" s="12"/>
@@ -19117,7 +19580,7 @@
       <c r="AM423" s="6"/>
       <c r="AN423" s="6"/>
     </row>
-    <row r="424" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A424" s="12"/>
       <c r="B424" s="12"/>
       <c r="C424" s="12"/>
@@ -19159,7 +19622,7 @@
       <c r="AM424" s="6"/>
       <c r="AN424" s="6"/>
     </row>
-    <row r="425" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A425" s="12"/>
       <c r="B425" s="12"/>
       <c r="C425" s="12"/>
@@ -19201,7 +19664,7 @@
       <c r="AM425" s="6"/>
       <c r="AN425" s="6"/>
     </row>
-    <row r="426" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A426" s="12"/>
       <c r="B426" s="12"/>
       <c r="C426" s="12"/>
@@ -19243,7 +19706,7 @@
       <c r="AM426" s="6"/>
       <c r="AN426" s="6"/>
     </row>
-    <row r="427" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A427" s="12"/>
       <c r="B427" s="12"/>
       <c r="C427" s="12"/>
@@ -19285,7 +19748,7 @@
       <c r="AM427" s="6"/>
       <c r="AN427" s="6"/>
     </row>
-    <row r="428" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A428" s="12"/>
       <c r="B428" s="12"/>
       <c r="C428" s="12"/>
@@ -19327,7 +19790,7 @@
       <c r="AM428" s="6"/>
       <c r="AN428" s="6"/>
     </row>
-    <row r="429" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A429" s="12"/>
       <c r="B429" s="12"/>
       <c r="C429" s="12"/>
@@ -19369,7 +19832,7 @@
       <c r="AM429" s="6"/>
       <c r="AN429" s="6"/>
     </row>
-    <row r="430" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A430" s="12"/>
       <c r="B430" s="12"/>
       <c r="C430" s="12"/>
@@ -19411,7 +19874,7 @@
       <c r="AM430" s="6"/>
       <c r="AN430" s="6"/>
     </row>
-    <row r="431" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A431" s="12"/>
       <c r="B431" s="12"/>
       <c r="C431" s="12"/>
@@ -19453,7 +19916,7 @@
       <c r="AM431" s="6"/>
       <c r="AN431" s="6"/>
     </row>
-    <row r="432" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A432" s="12"/>
       <c r="B432" s="12"/>
       <c r="C432" s="12"/>
@@ -19495,7 +19958,7 @@
       <c r="AM432" s="6"/>
       <c r="AN432" s="6"/>
     </row>
-    <row r="433" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A433" s="12"/>
       <c r="B433" s="12"/>
       <c r="C433" s="12"/>
@@ -19537,7 +20000,7 @@
       <c r="AM433" s="6"/>
       <c r="AN433" s="6"/>
     </row>
-    <row r="434" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A434" s="12"/>
       <c r="B434" s="12"/>
       <c r="C434" s="12"/>
@@ -19579,7 +20042,7 @@
       <c r="AM434" s="6"/>
       <c r="AN434" s="6"/>
     </row>
-    <row r="435" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A435" s="12"/>
       <c r="B435" s="12"/>
       <c r="C435" s="12"/>
@@ -19621,7 +20084,7 @@
       <c r="AM435" s="6"/>
       <c r="AN435" s="6"/>
     </row>
-    <row r="436" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A436" s="12"/>
       <c r="B436" s="12"/>
       <c r="C436" s="12"/>
@@ -19663,7 +20126,7 @@
       <c r="AM436" s="6"/>
       <c r="AN436" s="6"/>
     </row>
-    <row r="437" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A437" s="12"/>
       <c r="B437" s="12"/>
       <c r="C437" s="12"/>
@@ -19705,7 +20168,7 @@
       <c r="AM437" s="6"/>
       <c r="AN437" s="6"/>
     </row>
-    <row r="438" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A438" s="12"/>
       <c r="B438" s="12"/>
       <c r="C438" s="12"/>
@@ -19747,7 +20210,7 @@
       <c r="AM438" s="6"/>
       <c r="AN438" s="6"/>
     </row>
-    <row r="439" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A439" s="12"/>
       <c r="B439" s="12"/>
       <c r="C439" s="12"/>
@@ -19789,7 +20252,7 @@
       <c r="AM439" s="6"/>
       <c r="AN439" s="6"/>
     </row>
-    <row r="440" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A440" s="12"/>
       <c r="B440" s="12"/>
       <c r="C440" s="12"/>
@@ -19831,7 +20294,7 @@
       <c r="AM440" s="6"/>
       <c r="AN440" s="6"/>
     </row>
-    <row r="441" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A441" s="12"/>
       <c r="B441" s="12"/>
       <c r="C441" s="12"/>
@@ -19873,7 +20336,7 @@
       <c r="AM441" s="6"/>
       <c r="AN441" s="6"/>
     </row>
-    <row r="442" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A442" s="12"/>
       <c r="B442" s="12"/>
       <c r="C442" s="12"/>
@@ -19915,7 +20378,7 @@
       <c r="AM442" s="6"/>
       <c r="AN442" s="6"/>
     </row>
-    <row r="443" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A443" s="12"/>
       <c r="B443" s="12"/>
       <c r="C443" s="12"/>
@@ -19957,7 +20420,7 @@
       <c r="AM443" s="6"/>
       <c r="AN443" s="6"/>
     </row>
-    <row r="444" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A444" s="12"/>
       <c r="B444" s="12"/>
       <c r="C444" s="12"/>
@@ -19999,7 +20462,7 @@
       <c r="AM444" s="6"/>
       <c r="AN444" s="6"/>
     </row>
-    <row r="445" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A445" s="12"/>
       <c r="B445" s="12"/>
       <c r="C445" s="12"/>
@@ -20041,7 +20504,7 @@
       <c r="AM445" s="6"/>
       <c r="AN445" s="6"/>
     </row>
-    <row r="446" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A446" s="12"/>
       <c r="B446" s="12"/>
       <c r="C446" s="12"/>
@@ -20083,7 +20546,7 @@
       <c r="AM446" s="6"/>
       <c r="AN446" s="6"/>
     </row>
-    <row r="447" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A447" s="12"/>
       <c r="B447" s="12"/>
       <c r="C447" s="12"/>
@@ -20125,7 +20588,7 @@
       <c r="AM447" s="6"/>
       <c r="AN447" s="6"/>
     </row>
-    <row r="448" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A448" s="12"/>
       <c r="B448" s="12"/>
       <c r="C448" s="12"/>
@@ -20167,7 +20630,7 @@
       <c r="AM448" s="6"/>
       <c r="AN448" s="6"/>
     </row>
-    <row r="449" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A449" s="12"/>
       <c r="B449" s="12"/>
       <c r="C449" s="12"/>
@@ -20209,7 +20672,7 @@
       <c r="AM449" s="6"/>
       <c r="AN449" s="6"/>
     </row>
-    <row r="450" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A450" s="12"/>
       <c r="B450" s="12"/>
       <c r="C450" s="12"/>
@@ -20251,7 +20714,7 @@
       <c r="AM450" s="6"/>
       <c r="AN450" s="6"/>
     </row>
-    <row r="451" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A451" s="12"/>
       <c r="B451" s="12"/>
       <c r="C451" s="12"/>
@@ -20293,7 +20756,7 @@
       <c r="AM451" s="6"/>
       <c r="AN451" s="6"/>
     </row>
-    <row r="452" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A452" s="12"/>
       <c r="B452" s="12"/>
       <c r="C452" s="12"/>
@@ -20335,7 +20798,7 @@
       <c r="AM452" s="6"/>
       <c r="AN452" s="6"/>
     </row>
-    <row r="453" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A453" s="12"/>
       <c r="B453" s="12"/>
       <c r="C453" s="12"/>
@@ -20377,7 +20840,7 @@
       <c r="AM453" s="6"/>
       <c r="AN453" s="6"/>
     </row>
-    <row r="454" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A454" s="12"/>
       <c r="B454" s="12"/>
       <c r="C454" s="12"/>
@@ -20419,7 +20882,7 @@
       <c r="AM454" s="6"/>
       <c r="AN454" s="6"/>
     </row>
-    <row r="455" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A455" s="12"/>
       <c r="B455" s="12"/>
       <c r="C455" s="12"/>
@@ -20461,7 +20924,7 @@
       <c r="AM455" s="6"/>
       <c r="AN455" s="6"/>
     </row>
-    <row r="456" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A456" s="12"/>
       <c r="B456" s="12"/>
       <c r="C456" s="12"/>
@@ -20503,7 +20966,7 @@
       <c r="AM456" s="6"/>
       <c r="AN456" s="6"/>
     </row>
-    <row r="457" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A457" s="12"/>
       <c r="B457" s="12"/>
       <c r="C457" s="12"/>
@@ -20545,7 +21008,7 @@
       <c r="AM457" s="6"/>
       <c r="AN457" s="6"/>
     </row>
-    <row r="458" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A458" s="12"/>
       <c r="B458" s="12"/>
       <c r="C458" s="12"/>
@@ -20587,7 +21050,7 @@
       <c r="AM458" s="6"/>
       <c r="AN458" s="6"/>
     </row>
-    <row r="459" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A459" s="12"/>
       <c r="B459" s="12"/>
       <c r="C459" s="12"/>
@@ -20629,7 +21092,7 @@
       <c r="AM459" s="6"/>
       <c r="AN459" s="6"/>
     </row>
-    <row r="460" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A460" s="12"/>
       <c r="B460" s="12"/>
       <c r="C460" s="12"/>
@@ -20671,7 +21134,7 @@
       <c r="AM460" s="6"/>
       <c r="AN460" s="6"/>
     </row>
-    <row r="461" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A461" s="12"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12"/>
@@ -20713,7 +21176,7 @@
       <c r="AM461" s="6"/>
       <c r="AN461" s="6"/>
     </row>
-    <row r="462" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A462" s="12"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
@@ -20755,7 +21218,7 @@
       <c r="AM462" s="6"/>
       <c r="AN462" s="6"/>
     </row>
-    <row r="463" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A463" s="12"/>
       <c r="B463" s="12"/>
       <c r="C463" s="12"/>
@@ -20797,7 +21260,7 @@
       <c r="AM463" s="6"/>
       <c r="AN463" s="6"/>
     </row>
-    <row r="464" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A464" s="12"/>
       <c r="B464" s="12"/>
       <c r="C464" s="12"/>
@@ -20839,7 +21302,7 @@
       <c r="AM464" s="6"/>
       <c r="AN464" s="6"/>
     </row>
-    <row r="465" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A465" s="12"/>
       <c r="B465" s="12"/>
       <c r="C465" s="12"/>
@@ -20881,7 +21344,7 @@
       <c r="AM465" s="6"/>
       <c r="AN465" s="6"/>
     </row>
-    <row r="466" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A466" s="12"/>
       <c r="B466" s="12"/>
       <c r="C466" s="12"/>
@@ -20923,7 +21386,7 @@
       <c r="AM466" s="6"/>
       <c r="AN466" s="6"/>
     </row>
-    <row r="467" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A467" s="12"/>
       <c r="B467" s="12"/>
       <c r="C467" s="12"/>
@@ -20965,7 +21428,7 @@
       <c r="AM467" s="6"/>
       <c r="AN467" s="6"/>
     </row>
-    <row r="468" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A468" s="12"/>
       <c r="B468" s="12"/>
       <c r="C468" s="12"/>
@@ -21007,7 +21470,7 @@
       <c r="AM468" s="6"/>
       <c r="AN468" s="6"/>
     </row>
-    <row r="469" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A469" s="12"/>
       <c r="B469" s="12"/>
       <c r="C469" s="12"/>
@@ -21049,7 +21512,7 @@
       <c r="AM469" s="6"/>
       <c r="AN469" s="6"/>
     </row>
-    <row r="470" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A470" s="12"/>
       <c r="B470" s="12"/>
       <c r="C470" s="12"/>
@@ -21091,7 +21554,7 @@
       <c r="AM470" s="6"/>
       <c r="AN470" s="6"/>
     </row>
-    <row r="471" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A471" s="12"/>
       <c r="B471" s="12"/>
       <c r="C471" s="12"/>
@@ -21133,7 +21596,7 @@
       <c r="AM471" s="6"/>
       <c r="AN471" s="6"/>
     </row>
-    <row r="472" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A472" s="12"/>
       <c r="B472" s="12"/>
       <c r="C472" s="12"/>
@@ -21175,7 +21638,7 @@
       <c r="AM472" s="6"/>
       <c r="AN472" s="6"/>
     </row>
-    <row r="473" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A473" s="12"/>
       <c r="B473" s="12"/>
       <c r="C473" s="12"/>
@@ -21217,7 +21680,7 @@
       <c r="AM473" s="6"/>
       <c r="AN473" s="6"/>
     </row>
-    <row r="474" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A474" s="12"/>
       <c r="B474" s="12"/>
       <c r="C474" s="12"/>
@@ -21259,7 +21722,7 @@
       <c r="AM474" s="6"/>
       <c r="AN474" s="6"/>
     </row>
-    <row r="475" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A475" s="12"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12"/>
@@ -21301,7 +21764,7 @@
       <c r="AM475" s="6"/>
       <c r="AN475" s="6"/>
     </row>
-    <row r="476" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A476" s="12"/>
       <c r="B476" s="12"/>
       <c r="C476" s="12"/>
@@ -21343,7 +21806,7 @@
       <c r="AM476" s="6"/>
       <c r="AN476" s="6"/>
     </row>
-    <row r="477" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A477" s="12"/>
       <c r="B477" s="12"/>
       <c r="C477" s="12"/>
@@ -21385,7 +21848,7 @@
       <c r="AM477" s="6"/>
       <c r="AN477" s="6"/>
     </row>
-    <row r="478" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A478" s="12"/>
       <c r="B478" s="12"/>
       <c r="C478" s="12"/>
@@ -21427,7 +21890,7 @@
       <c r="AM478" s="6"/>
       <c r="AN478" s="6"/>
     </row>
-    <row r="479" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A479" s="12"/>
       <c r="B479" s="12"/>
       <c r="C479" s="12"/>
@@ -21469,7 +21932,7 @@
       <c r="AM479" s="6"/>
       <c r="AN479" s="6"/>
     </row>
-    <row r="480" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A480" s="12"/>
       <c r="B480" s="12"/>
       <c r="C480" s="12"/>
@@ -21511,7 +21974,7 @@
       <c r="AM480" s="6"/>
       <c r="AN480" s="6"/>
     </row>
-    <row r="481" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
@@ -21553,7 +22016,7 @@
       <c r="AM481" s="6"/>
       <c r="AN481" s="6"/>
     </row>
-    <row r="482" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A482" s="12"/>
       <c r="B482" s="12"/>
       <c r="C482" s="12"/>
@@ -21595,7 +22058,7 @@
       <c r="AM482" s="6"/>
       <c r="AN482" s="6"/>
     </row>
-    <row r="483" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A483" s="12"/>
       <c r="B483" s="12"/>
       <c r="C483" s="12"/>
@@ -21637,7 +22100,7 @@
       <c r="AM483" s="6"/>
       <c r="AN483" s="6"/>
     </row>
-    <row r="484" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A484" s="12"/>
       <c r="B484" s="12"/>
       <c r="C484" s="12"/>
@@ -21679,7 +22142,7 @@
       <c r="AM484" s="6"/>
       <c r="AN484" s="6"/>
     </row>
-    <row r="485" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A485" s="12"/>
       <c r="B485" s="12"/>
       <c r="C485" s="12"/>
@@ -21721,7 +22184,7 @@
       <c r="AM485" s="6"/>
       <c r="AN485" s="6"/>
     </row>
-    <row r="486" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A486" s="12"/>
       <c r="B486" s="12"/>
       <c r="C486" s="12"/>
@@ -21763,7 +22226,7 @@
       <c r="AM486" s="6"/>
       <c r="AN486" s="6"/>
     </row>
-    <row r="487" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A487" s="12"/>
       <c r="B487" s="12"/>
       <c r="C487" s="12"/>
@@ -21805,7 +22268,7 @@
       <c r="AM487" s="6"/>
       <c r="AN487" s="6"/>
     </row>
-    <row r="488" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A488" s="12"/>
       <c r="B488" s="12"/>
       <c r="C488" s="12"/>
@@ -21847,7 +22310,7 @@
       <c r="AM488" s="6"/>
       <c r="AN488" s="6"/>
     </row>
-    <row r="489" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A489" s="12"/>
       <c r="B489" s="12"/>
       <c r="C489" s="12"/>
@@ -21889,7 +22352,7 @@
       <c r="AM489" s="6"/>
       <c r="AN489" s="6"/>
     </row>
-    <row r="490" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A490" s="12"/>
       <c r="B490" s="12"/>
       <c r="C490" s="12"/>
@@ -21931,7 +22394,7 @@
       <c r="AM490" s="6"/>
       <c r="AN490" s="6"/>
     </row>
-    <row r="491" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -21973,7 +22436,7 @@
       <c r="AM491" s="6"/>
       <c r="AN491" s="6"/>
     </row>
-    <row r="492" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A492" s="12"/>
       <c r="B492" s="12"/>
       <c r="C492" s="12"/>
@@ -22015,7 +22478,7 @@
       <c r="AM492" s="6"/>
       <c r="AN492" s="6"/>
     </row>
-    <row r="493" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A493" s="12"/>
       <c r="B493" s="12"/>
       <c r="C493" s="12"/>
@@ -22057,7 +22520,7 @@
       <c r="AM493" s="6"/>
       <c r="AN493" s="6"/>
     </row>
-    <row r="494" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A494" s="12"/>
       <c r="B494" s="12"/>
       <c r="C494" s="12"/>
@@ -22099,7 +22562,7 @@
       <c r="AM494" s="6"/>
       <c r="AN494" s="6"/>
     </row>
-    <row r="495" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A495" s="12"/>
       <c r="B495" s="12"/>
       <c r="C495" s="12"/>
@@ -22141,7 +22604,7 @@
       <c r="AM495" s="6"/>
       <c r="AN495" s="6"/>
     </row>
-    <row r="496" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A496" s="12"/>
       <c r="B496" s="12"/>
       <c r="C496" s="12"/>
@@ -22183,7 +22646,7 @@
       <c r="AM496" s="6"/>
       <c r="AN496" s="6"/>
     </row>
-    <row r="497" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A497" s="12"/>
       <c r="B497" s="12"/>
       <c r="C497" s="12"/>
@@ -22225,7 +22688,7 @@
       <c r="AM497" s="6"/>
       <c r="AN497" s="6"/>
     </row>
-    <row r="498" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A498" s="12"/>
       <c r="B498" s="12"/>
       <c r="C498" s="12"/>
@@ -22267,7 +22730,7 @@
       <c r="AM498" s="6"/>
       <c r="AN498" s="6"/>
     </row>
-    <row r="499" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A499" s="12"/>
       <c r="B499" s="12"/>
       <c r="C499" s="12"/>
@@ -22309,7 +22772,7 @@
       <c r="AM499" s="6"/>
       <c r="AN499" s="6"/>
     </row>
-    <row r="500" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A500" s="12"/>
       <c r="B500" s="12"/>
       <c r="C500" s="12"/>
@@ -22351,7 +22814,7 @@
       <c r="AM500" s="6"/>
       <c r="AN500" s="6"/>
     </row>
-    <row r="501" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A501" s="12"/>
       <c r="B501" s="12"/>
       <c r="C501" s="12"/>
@@ -22393,7 +22856,7 @@
       <c r="AM501" s="6"/>
       <c r="AN501" s="6"/>
     </row>
-    <row r="502" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A502" s="12"/>
       <c r="B502" s="12"/>
       <c r="C502" s="12"/>
@@ -22435,7 +22898,7 @@
       <c r="AM502" s="6"/>
       <c r="AN502" s="6"/>
     </row>
-    <row r="503" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A503" s="12"/>
       <c r="B503" s="12"/>
       <c r="C503" s="12"/>
@@ -22477,7 +22940,7 @@
       <c r="AM503" s="6"/>
       <c r="AN503" s="6"/>
     </row>
-    <row r="504" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A504" s="12"/>
       <c r="B504" s="12"/>
       <c r="C504" s="12"/>
@@ -22519,7 +22982,7 @@
       <c r="AM504" s="6"/>
       <c r="AN504" s="6"/>
     </row>
-    <row r="505" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A505" s="12"/>
       <c r="B505" s="12"/>
       <c r="C505" s="12"/>
@@ -22561,7 +23024,7 @@
       <c r="AM505" s="6"/>
       <c r="AN505" s="6"/>
     </row>
-    <row r="506" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A506" s="12"/>
       <c r="B506" s="12"/>
       <c r="C506" s="12"/>
@@ -22603,7 +23066,7 @@
       <c r="AM506" s="6"/>
       <c r="AN506" s="6"/>
     </row>
-    <row r="507" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A507" s="12"/>
       <c r="B507" s="12"/>
       <c r="C507" s="12"/>
@@ -22645,7 +23108,7 @@
       <c r="AM507" s="6"/>
       <c r="AN507" s="6"/>
     </row>
-    <row r="508" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A508" s="12"/>
       <c r="B508" s="12"/>
       <c r="C508" s="12"/>
@@ -22687,7 +23150,7 @@
       <c r="AM508" s="6"/>
       <c r="AN508" s="6"/>
     </row>
-    <row r="509" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A509" s="12"/>
       <c r="B509" s="12"/>
       <c r="C509" s="12"/>
@@ -22729,7 +23192,7 @@
       <c r="AM509" s="6"/>
       <c r="AN509" s="6"/>
     </row>
-    <row r="510" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A510" s="12"/>
       <c r="B510" s="12"/>
       <c r="C510" s="12"/>
@@ -22771,7 +23234,7 @@
       <c r="AM510" s="6"/>
       <c r="AN510" s="6"/>
     </row>
-    <row r="511" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A511" s="12"/>
       <c r="B511" s="12"/>
       <c r="C511" s="12"/>
@@ -22813,7 +23276,7 @@
       <c r="AM511" s="6"/>
       <c r="AN511" s="6"/>
     </row>
-    <row r="512" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A512" s="12"/>
       <c r="B512" s="12"/>
       <c r="C512" s="12"/>
@@ -22855,7 +23318,7 @@
       <c r="AM512" s="6"/>
       <c r="AN512" s="6"/>
     </row>
-    <row r="513" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
@@ -22897,7 +23360,7 @@
       <c r="AM513" s="6"/>
       <c r="AN513" s="6"/>
     </row>
-    <row r="514" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A514" s="12"/>
       <c r="B514" s="12"/>
       <c r="C514" s="12"/>
@@ -22939,7 +23402,7 @@
       <c r="AM514" s="6"/>
       <c r="AN514" s="6"/>
     </row>
-    <row r="515" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A515" s="12"/>
       <c r="B515" s="12"/>
       <c r="C515" s="12"/>
@@ -22981,7 +23444,7 @@
       <c r="AM515" s="6"/>
       <c r="AN515" s="6"/>
     </row>
-    <row r="516" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A516" s="12"/>
       <c r="B516" s="12"/>
       <c r="C516" s="12"/>
@@ -23023,7 +23486,7 @@
       <c r="AM516" s="6"/>
       <c r="AN516" s="6"/>
     </row>
-    <row r="517" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A517" s="12"/>
       <c r="B517" s="12"/>
       <c r="C517" s="12"/>
@@ -23065,7 +23528,7 @@
       <c r="AM517" s="6"/>
       <c r="AN517" s="6"/>
     </row>
-    <row r="518" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A518" s="12"/>
       <c r="B518" s="12"/>
       <c r="C518" s="12"/>
@@ -23107,7 +23570,7 @@
       <c r="AM518" s="6"/>
       <c r="AN518" s="6"/>
     </row>
-    <row r="519" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A519" s="12"/>
       <c r="B519" s="12"/>
       <c r="C519" s="12"/>
@@ -23149,7 +23612,7 @@
       <c r="AM519" s="6"/>
       <c r="AN519" s="6"/>
     </row>
-    <row r="520" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A520" s="12"/>
       <c r="B520" s="12"/>
       <c r="C520" s="12"/>
@@ -23191,7 +23654,7 @@
       <c r="AM520" s="6"/>
       <c r="AN520" s="6"/>
     </row>
-    <row r="521" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A521" s="12"/>
       <c r="B521" s="12"/>
       <c r="C521" s="12"/>
@@ -23233,7 +23696,7 @@
       <c r="AM521" s="6"/>
       <c r="AN521" s="6"/>
     </row>
-    <row r="522" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A522" s="12"/>
       <c r="B522" s="12"/>
       <c r="C522" s="12"/>
@@ -23275,7 +23738,7 @@
       <c r="AM522" s="6"/>
       <c r="AN522" s="6"/>
     </row>
-    <row r="523" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A523" s="12"/>
       <c r="B523" s="12"/>
       <c r="C523" s="12"/>
@@ -23317,7 +23780,7 @@
       <c r="AM523" s="6"/>
       <c r="AN523" s="6"/>
     </row>
-    <row r="524" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A524" s="12"/>
       <c r="B524" s="12"/>
       <c r="C524" s="12"/>
@@ -23359,7 +23822,7 @@
       <c r="AM524" s="6"/>
       <c r="AN524" s="6"/>
     </row>
-    <row r="525" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A525" s="12"/>
       <c r="B525" s="12"/>
       <c r="C525" s="12"/>
@@ -23401,7 +23864,7 @@
       <c r="AM525" s="6"/>
       <c r="AN525" s="6"/>
     </row>
-    <row r="526" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A526" s="12"/>
       <c r="B526" s="12"/>
       <c r="C526" s="12"/>
@@ -23443,7 +23906,7 @@
       <c r="AM526" s="6"/>
       <c r="AN526" s="6"/>
     </row>
-    <row r="527" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A527" s="12"/>
       <c r="B527" s="12"/>
       <c r="C527" s="12"/>
@@ -23485,7 +23948,7 @@
       <c r="AM527" s="6"/>
       <c r="AN527" s="6"/>
     </row>
-    <row r="528" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A528" s="12"/>
       <c r="B528" s="12"/>
       <c r="C528" s="12"/>
@@ -23527,7 +23990,7 @@
       <c r="AM528" s="6"/>
       <c r="AN528" s="6"/>
     </row>
-    <row r="529" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A529" s="12"/>
       <c r="B529" s="12"/>
       <c r="C529" s="12"/>
@@ -23569,7 +24032,7 @@
       <c r="AM529" s="6"/>
       <c r="AN529" s="6"/>
     </row>
-    <row r="530" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A530" s="12"/>
       <c r="B530" s="12"/>
       <c r="C530" s="12"/>
@@ -23611,7 +24074,7 @@
       <c r="AM530" s="6"/>
       <c r="AN530" s="6"/>
     </row>
-    <row r="531" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A531" s="12"/>
       <c r="B531" s="12"/>
       <c r="C531" s="12"/>
@@ -23653,7 +24116,7 @@
       <c r="AM531" s="6"/>
       <c r="AN531" s="6"/>
     </row>
-    <row r="532" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A532" s="12"/>
       <c r="B532" s="12"/>
       <c r="C532" s="12"/>
@@ -23695,7 +24158,7 @@
       <c r="AM532" s="6"/>
       <c r="AN532" s="6"/>
     </row>
-    <row r="533" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A533" s="12"/>
       <c r="B533" s="12"/>
       <c r="C533" s="12"/>
@@ -23737,7 +24200,7 @@
       <c r="AM533" s="6"/>
       <c r="AN533" s="6"/>
     </row>
-    <row r="534" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A534" s="12"/>
       <c r="B534" s="12"/>
       <c r="C534" s="12"/>
@@ -23779,7 +24242,7 @@
       <c r="AM534" s="6"/>
       <c r="AN534" s="6"/>
     </row>
-    <row r="535" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A535" s="12"/>
       <c r="B535" s="12"/>
       <c r="C535" s="12"/>
@@ -23821,7 +24284,7 @@
       <c r="AM535" s="6"/>
       <c r="AN535" s="6"/>
     </row>
-    <row r="536" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A536" s="12"/>
       <c r="B536" s="12"/>
       <c r="C536" s="12"/>
@@ -23863,7 +24326,7 @@
       <c r="AM536" s="6"/>
       <c r="AN536" s="6"/>
     </row>
-    <row r="537" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A537" s="12"/>
       <c r="B537" s="12"/>
       <c r="C537" s="12"/>
@@ -23905,7 +24368,7 @@
       <c r="AM537" s="6"/>
       <c r="AN537" s="6"/>
     </row>
-    <row r="538" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A538" s="12"/>
       <c r="B538" s="12"/>
       <c r="C538" s="12"/>
@@ -23947,7 +24410,7 @@
       <c r="AM538" s="6"/>
       <c r="AN538" s="6"/>
     </row>
-    <row r="539" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A539" s="12"/>
       <c r="B539" s="12"/>
       <c r="C539" s="12"/>
@@ -23989,7 +24452,7 @@
       <c r="AM539" s="6"/>
       <c r="AN539" s="6"/>
     </row>
-    <row r="540" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
@@ -24031,7 +24494,7 @@
       <c r="AM540" s="6"/>
       <c r="AN540" s="6"/>
     </row>
-    <row r="541" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
@@ -24073,7 +24536,7 @@
       <c r="AM541" s="6"/>
       <c r="AN541" s="6"/>
     </row>
-    <row r="542" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
@@ -24115,7 +24578,7 @@
       <c r="AM542" s="6"/>
       <c r="AN542" s="6"/>
     </row>
-    <row r="543" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
@@ -24157,7 +24620,7 @@
       <c r="AM543" s="6"/>
       <c r="AN543" s="6"/>
     </row>
-    <row r="544" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
@@ -24199,7 +24662,7 @@
       <c r="AM544" s="6"/>
       <c r="AN544" s="6"/>
     </row>
-    <row r="545" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A545" s="12"/>
       <c r="B545" s="12"/>
       <c r="C545" s="12"/>
@@ -24241,7 +24704,7 @@
       <c r="AM545" s="6"/>
       <c r="AN545" s="6"/>
     </row>
-    <row r="546" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A546" s="12"/>
       <c r="B546" s="12"/>
       <c r="C546" s="12"/>
@@ -24283,7 +24746,7 @@
       <c r="AM546" s="6"/>
       <c r="AN546" s="6"/>
     </row>
-    <row r="547" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A547" s="12"/>
       <c r="B547" s="12"/>
       <c r="C547" s="12"/>
@@ -24325,7 +24788,7 @@
       <c r="AM547" s="6"/>
       <c r="AN547" s="6"/>
     </row>
-    <row r="548" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A548" s="12"/>
       <c r="B548" s="12"/>
       <c r="C548" s="12"/>
@@ -24367,7 +24830,7 @@
       <c r="AM548" s="6"/>
       <c r="AN548" s="6"/>
     </row>
-    <row r="549" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A549" s="12"/>
       <c r="B549" s="12"/>
       <c r="C549" s="12"/>
@@ -24409,7 +24872,7 @@
       <c r="AM549" s="6"/>
       <c r="AN549" s="6"/>
     </row>
-    <row r="550" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A550" s="12"/>
       <c r="B550" s="12"/>
       <c r="C550" s="12"/>
@@ -24451,7 +24914,7 @@
       <c r="AM550" s="6"/>
       <c r="AN550" s="6"/>
     </row>
-    <row r="551" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A551" s="12"/>
       <c r="B551" s="12"/>
       <c r="C551" s="12"/>
@@ -24493,7 +24956,7 @@
       <c r="AM551" s="6"/>
       <c r="AN551" s="6"/>
     </row>
-    <row r="552" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A552" s="12"/>
       <c r="B552" s="12"/>
       <c r="C552" s="12"/>
@@ -24535,7 +24998,7 @@
       <c r="AM552" s="6"/>
       <c r="AN552" s="6"/>
     </row>
-    <row r="553" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A553" s="12"/>
       <c r="B553" s="12"/>
       <c r="C553" s="12"/>
@@ -24577,7 +25040,7 @@
       <c r="AM553" s="6"/>
       <c r="AN553" s="6"/>
     </row>
-    <row r="554" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
@@ -24619,7 +25082,7 @@
       <c r="AM554" s="6"/>
       <c r="AN554" s="6"/>
     </row>
-    <row r="555" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A555" s="12"/>
       <c r="B555" s="12"/>
       <c r="C555" s="12"/>
@@ -24661,7 +25124,7 @@
       <c r="AM555" s="6"/>
       <c r="AN555" s="6"/>
     </row>
-    <row r="556" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A556" s="12"/>
       <c r="B556" s="12"/>
       <c r="C556" s="12"/>
@@ -24703,7 +25166,7 @@
       <c r="AM556" s="6"/>
       <c r="AN556" s="6"/>
     </row>
-    <row r="557" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A557" s="12"/>
       <c r="B557" s="12"/>
       <c r="C557" s="12"/>
@@ -24745,7 +25208,7 @@
       <c r="AM557" s="6"/>
       <c r="AN557" s="6"/>
     </row>
-    <row r="558" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A558" s="12"/>
       <c r="B558" s="12"/>
       <c r="C558" s="12"/>
@@ -24787,7 +25250,7 @@
       <c r="AM558" s="6"/>
       <c r="AN558" s="6"/>
     </row>
-    <row r="559" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A559" s="12"/>
       <c r="B559" s="12"/>
       <c r="C559" s="12"/>
@@ -24829,7 +25292,7 @@
       <c r="AM559" s="6"/>
       <c r="AN559" s="6"/>
     </row>
-    <row r="560" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
@@ -24871,7 +25334,7 @@
       <c r="AM560" s="6"/>
       <c r="AN560" s="6"/>
     </row>
-    <row r="561" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A561" s="12"/>
       <c r="B561" s="12"/>
       <c r="C561" s="12"/>
@@ -24913,7 +25376,7 @@
       <c r="AM561" s="6"/>
       <c r="AN561" s="6"/>
     </row>
-    <row r="562" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A562" s="12"/>
       <c r="B562" s="12"/>
       <c r="C562" s="12"/>
@@ -24955,7 +25418,7 @@
       <c r="AM562" s="6"/>
       <c r="AN562" s="6"/>
     </row>
-    <row r="563" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A563" s="12"/>
       <c r="B563" s="12"/>
       <c r="C563" s="12"/>
@@ -24997,7 +25460,7 @@
       <c r="AM563" s="6"/>
       <c r="AN563" s="6"/>
     </row>
-    <row r="564" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A564" s="12"/>
       <c r="B564" s="12"/>
       <c r="C564" s="12"/>
@@ -25039,7 +25502,7 @@
       <c r="AM564" s="6"/>
       <c r="AN564" s="6"/>
     </row>
-    <row r="565" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A565" s="12"/>
       <c r="B565" s="12"/>
       <c r="C565" s="12"/>
@@ -25081,7 +25544,7 @@
       <c r="AM565" s="6"/>
       <c r="AN565" s="6"/>
     </row>
-    <row r="566" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A566" s="12"/>
       <c r="B566" s="12"/>
       <c r="C566" s="12"/>
@@ -25123,7 +25586,7 @@
       <c r="AM566" s="6"/>
       <c r="AN566" s="6"/>
     </row>
-    <row r="567" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A567" s="12"/>
       <c r="B567" s="12"/>
       <c r="C567" s="12"/>
@@ -25165,7 +25628,7 @@
       <c r="AM567" s="6"/>
       <c r="AN567" s="6"/>
     </row>
-    <row r="568" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A568" s="12"/>
       <c r="B568" s="12"/>
       <c r="C568" s="12"/>
@@ -25207,7 +25670,7 @@
       <c r="AM568" s="6"/>
       <c r="AN568" s="6"/>
     </row>
-    <row r="569" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A569" s="12"/>
       <c r="B569" s="12"/>
       <c r="C569" s="12"/>
@@ -25249,7 +25712,7 @@
       <c r="AM569" s="6"/>
       <c r="AN569" s="6"/>
     </row>
-    <row r="570" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A570" s="12"/>
       <c r="B570" s="12"/>
       <c r="C570" s="12"/>
@@ -25291,7 +25754,7 @@
       <c r="AM570" s="6"/>
       <c r="AN570" s="6"/>
     </row>
-    <row r="571" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A571" s="12"/>
       <c r="B571" s="12"/>
       <c r="C571" s="12"/>
@@ -25333,7 +25796,7 @@
       <c r="AM571" s="6"/>
       <c r="AN571" s="6"/>
     </row>
-    <row r="572" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A572" s="12"/>
       <c r="B572" s="12"/>
       <c r="C572" s="12"/>
@@ -25375,7 +25838,7 @@
       <c r="AM572" s="6"/>
       <c r="AN572" s="6"/>
     </row>
-    <row r="573" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A573" s="12"/>
       <c r="B573" s="12"/>
       <c r="C573" s="12"/>
@@ -25417,7 +25880,7 @@
       <c r="AM573" s="6"/>
       <c r="AN573" s="6"/>
     </row>
-    <row r="574" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A574" s="12"/>
       <c r="B574" s="12"/>
       <c r="C574" s="12"/>
@@ -25459,7 +25922,7 @@
       <c r="AM574" s="6"/>
       <c r="AN574" s="6"/>
     </row>
-    <row r="575" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A575" s="12"/>
       <c r="B575" s="12"/>
       <c r="C575" s="12"/>
@@ -25501,7 +25964,7 @@
       <c r="AM575" s="6"/>
       <c r="AN575" s="6"/>
     </row>
-    <row r="576" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A576" s="12"/>
       <c r="B576" s="12"/>
       <c r="C576" s="12"/>
@@ -25543,7 +26006,7 @@
       <c r="AM576" s="6"/>
       <c r="AN576" s="6"/>
     </row>
-    <row r="577" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A577" s="12"/>
       <c r="B577" s="12"/>
       <c r="C577" s="12"/>
@@ -25585,7 +26048,7 @@
       <c r="AM577" s="6"/>
       <c r="AN577" s="6"/>
     </row>
-    <row r="578" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A578" s="12"/>
       <c r="B578" s="12"/>
       <c r="C578" s="12"/>
@@ -25627,7 +26090,7 @@
       <c r="AM578" s="6"/>
       <c r="AN578" s="6"/>
     </row>
-    <row r="579" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A579" s="12"/>
       <c r="B579" s="12"/>
       <c r="C579" s="12"/>
@@ -25669,7 +26132,7 @@
       <c r="AM579" s="6"/>
       <c r="AN579" s="6"/>
     </row>
-    <row r="580" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A580" s="12"/>
       <c r="B580" s="12"/>
       <c r="C580" s="12"/>
@@ -25711,7 +26174,7 @@
       <c r="AM580" s="6"/>
       <c r="AN580" s="6"/>
     </row>
-    <row r="581" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A581" s="12"/>
       <c r="B581" s="12"/>
       <c r="C581" s="12"/>
@@ -25753,7 +26216,7 @@
       <c r="AM581" s="6"/>
       <c r="AN581" s="6"/>
     </row>
-    <row r="582" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A582" s="12"/>
       <c r="B582" s="12"/>
       <c r="C582" s="12"/>
@@ -25795,7 +26258,7 @@
       <c r="AM582" s="6"/>
       <c r="AN582" s="6"/>
     </row>
-    <row r="583" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A583" s="12"/>
       <c r="B583" s="12"/>
       <c r="C583" s="12"/>
@@ -25837,7 +26300,7 @@
       <c r="AM583" s="6"/>
       <c r="AN583" s="6"/>
     </row>
-    <row r="584" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A584" s="12"/>
       <c r="B584" s="12"/>
       <c r="C584" s="12"/>
@@ -25879,7 +26342,7 @@
       <c r="AM584" s="6"/>
       <c r="AN584" s="6"/>
     </row>
-    <row r="585" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A585" s="12"/>
       <c r="B585" s="12"/>
       <c r="C585" s="12"/>
@@ -25921,7 +26384,7 @@
       <c r="AM585" s="6"/>
       <c r="AN585" s="6"/>
     </row>
-    <row r="586" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A586" s="12"/>
       <c r="B586" s="12"/>
       <c r="C586" s="12"/>
@@ -25963,7 +26426,7 @@
       <c r="AM586" s="6"/>
       <c r="AN586" s="6"/>
     </row>
-    <row r="587" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A587" s="12"/>
       <c r="B587" s="12"/>
       <c r="C587" s="12"/>
@@ -26005,7 +26468,7 @@
       <c r="AM587" s="6"/>
       <c r="AN587" s="6"/>
     </row>
-    <row r="588" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A588" s="12"/>
       <c r="B588" s="12"/>
       <c r="C588" s="12"/>
@@ -26047,7 +26510,7 @@
       <c r="AM588" s="6"/>
       <c r="AN588" s="6"/>
     </row>
-    <row r="589" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A589" s="12"/>
       <c r="B589" s="12"/>
       <c r="C589" s="12"/>
@@ -26089,7 +26552,7 @@
       <c r="AM589" s="6"/>
       <c r="AN589" s="6"/>
     </row>
-    <row r="590" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A590" s="12"/>
       <c r="B590" s="12"/>
       <c r="C590" s="12"/>
@@ -26131,7 +26594,7 @@
       <c r="AM590" s="6"/>
       <c r="AN590" s="6"/>
     </row>
-    <row r="591" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A591" s="12"/>
       <c r="B591" s="12"/>
       <c r="C591" s="12"/>
@@ -26173,7 +26636,7 @@
       <c r="AM591" s="6"/>
       <c r="AN591" s="6"/>
     </row>
-    <row r="592" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A592" s="12"/>
       <c r="B592" s="12"/>
       <c r="C592" s="12"/>
@@ -26215,7 +26678,7 @@
       <c r="AM592" s="6"/>
       <c r="AN592" s="6"/>
     </row>
-    <row r="593" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A593" s="12"/>
       <c r="B593" s="12"/>
       <c r="C593" s="12"/>
@@ -26257,7 +26720,7 @@
       <c r="AM593" s="6"/>
       <c r="AN593" s="6"/>
     </row>
-    <row r="594" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A594" s="12"/>
       <c r="B594" s="12"/>
       <c r="C594" s="12"/>
@@ -26299,7 +26762,7 @@
       <c r="AM594" s="6"/>
       <c r="AN594" s="6"/>
     </row>
-    <row r="595" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A595" s="12"/>
       <c r="B595" s="12"/>
       <c r="C595" s="12"/>
@@ -26341,7 +26804,7 @@
       <c r="AM595" s="6"/>
       <c r="AN595" s="6"/>
     </row>
-    <row r="596" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A596" s="12"/>
       <c r="B596" s="12"/>
       <c r="C596" s="12"/>
@@ -26383,7 +26846,7 @@
       <c r="AM596" s="6"/>
       <c r="AN596" s="6"/>
     </row>
-    <row r="597" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A597" s="12"/>
       <c r="B597" s="12"/>
       <c r="C597" s="12"/>
@@ -26425,7 +26888,7 @@
       <c r="AM597" s="6"/>
       <c r="AN597" s="6"/>
     </row>
-    <row r="598" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A598" s="12"/>
       <c r="B598" s="12"/>
       <c r="C598" s="12"/>
@@ -26467,7 +26930,7 @@
       <c r="AM598" s="6"/>
       <c r="AN598" s="6"/>
     </row>
-    <row r="599" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A599" s="12"/>
       <c r="B599" s="12"/>
       <c r="C599" s="12"/>
@@ -26509,7 +26972,7 @@
       <c r="AM599" s="6"/>
       <c r="AN599" s="6"/>
     </row>
-    <row r="600" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A600" s="12"/>
       <c r="B600" s="12"/>
       <c r="C600" s="12"/>
@@ -26551,7 +27014,7 @@
       <c r="AM600" s="6"/>
       <c r="AN600" s="6"/>
     </row>
-    <row r="601" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A601" s="12"/>
       <c r="B601" s="12"/>
       <c r="C601" s="12"/>
@@ -26593,7 +27056,7 @@
       <c r="AM601" s="6"/>
       <c r="AN601" s="6"/>
     </row>
-    <row r="602" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A602" s="12"/>
       <c r="B602" s="12"/>
       <c r="C602" s="12"/>
@@ -26635,7 +27098,7 @@
       <c r="AM602" s="6"/>
       <c r="AN602" s="6"/>
     </row>
-    <row r="603" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A603" s="12"/>
       <c r="B603" s="12"/>
       <c r="C603" s="12"/>
@@ -26677,7 +27140,7 @@
       <c r="AM603" s="6"/>
       <c r="AN603" s="6"/>
     </row>
-    <row r="604" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A604" s="12"/>
       <c r="B604" s="12"/>
       <c r="C604" s="12"/>
@@ -26719,7 +27182,7 @@
       <c r="AM604" s="6"/>
       <c r="AN604" s="6"/>
     </row>
-    <row r="605" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A605" s="12"/>
       <c r="B605" s="12"/>
       <c r="C605" s="12"/>
@@ -26761,7 +27224,7 @@
       <c r="AM605" s="6"/>
       <c r="AN605" s="6"/>
     </row>
-    <row r="606" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A606" s="12"/>
       <c r="B606" s="12"/>
       <c r="C606" s="12"/>
@@ -26803,7 +27266,7 @@
       <c r="AM606" s="6"/>
       <c r="AN606" s="6"/>
     </row>
-    <row r="607" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A607" s="12"/>
       <c r="B607" s="12"/>
       <c r="C607" s="12"/>
@@ -26845,7 +27308,7 @@
       <c r="AM607" s="6"/>
       <c r="AN607" s="6"/>
     </row>
-    <row r="608" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A608" s="12"/>
       <c r="B608" s="12"/>
       <c r="C608" s="12"/>
@@ -26887,7 +27350,7 @@
       <c r="AM608" s="6"/>
       <c r="AN608" s="6"/>
     </row>
-    <row r="609" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A609" s="12"/>
       <c r="B609" s="12"/>
       <c r="C609" s="12"/>
@@ -26929,7 +27392,7 @@
       <c r="AM609" s="6"/>
       <c r="AN609" s="6"/>
     </row>
-    <row r="610" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A610" s="12"/>
       <c r="B610" s="12"/>
       <c r="C610" s="12"/>
@@ -26971,7 +27434,7 @@
       <c r="AM610" s="6"/>
       <c r="AN610" s="6"/>
     </row>
-    <row r="611" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A611" s="12"/>
       <c r="B611" s="12"/>
       <c r="C611" s="12"/>
@@ -27013,7 +27476,7 @@
       <c r="AM611" s="6"/>
       <c r="AN611" s="6"/>
     </row>
-    <row r="612" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A612" s="12"/>
       <c r="B612" s="12"/>
       <c r="C612" s="12"/>
@@ -27055,7 +27518,7 @@
       <c r="AM612" s="6"/>
       <c r="AN612" s="6"/>
     </row>
-    <row r="613" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A613" s="12"/>
       <c r="B613" s="12"/>
       <c r="C613" s="12"/>
@@ -27097,7 +27560,7 @@
       <c r="AM613" s="6"/>
       <c r="AN613" s="6"/>
     </row>
-    <row r="614" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A614" s="12"/>
       <c r="B614" s="12"/>
       <c r="C614" s="12"/>
@@ -27139,7 +27602,7 @@
       <c r="AM614" s="6"/>
       <c r="AN614" s="6"/>
     </row>
-    <row r="615" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A615" s="12"/>
       <c r="B615" s="12"/>
       <c r="C615" s="12"/>
@@ -27181,7 +27644,7 @@
       <c r="AM615" s="6"/>
       <c r="AN615" s="6"/>
     </row>
-    <row r="616" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A616" s="12"/>
       <c r="B616" s="12"/>
       <c r="C616" s="12"/>
@@ -27223,7 +27686,7 @@
       <c r="AM616" s="6"/>
       <c r="AN616" s="6"/>
     </row>
-    <row r="617" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A617" s="12"/>
       <c r="B617" s="12"/>
       <c r="C617" s="12"/>
@@ -27265,7 +27728,7 @@
       <c r="AM617" s="6"/>
       <c r="AN617" s="6"/>
     </row>
-    <row r="618" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A618" s="12"/>
       <c r="B618" s="12"/>
       <c r="C618" s="12"/>
@@ -27307,7 +27770,7 @@
       <c r="AM618" s="6"/>
       <c r="AN618" s="6"/>
     </row>
-    <row r="619" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A619" s="12"/>
       <c r="B619" s="12"/>
       <c r="C619" s="12"/>
@@ -27349,7 +27812,7 @@
       <c r="AM619" s="6"/>
       <c r="AN619" s="6"/>
     </row>
-    <row r="620" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A620" s="12"/>
       <c r="B620" s="12"/>
       <c r="C620" s="12"/>
@@ -27391,7 +27854,7 @@
       <c r="AM620" s="6"/>
       <c r="AN620" s="6"/>
     </row>
-    <row r="621" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A621" s="12"/>
       <c r="B621" s="12"/>
       <c r="C621" s="12"/>
@@ -27433,7 +27896,7 @@
       <c r="AM621" s="6"/>
       <c r="AN621" s="6"/>
     </row>
-    <row r="622" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A622" s="12"/>
       <c r="B622" s="12"/>
       <c r="C622" s="12"/>
@@ -27475,7 +27938,7 @@
       <c r="AM622" s="6"/>
       <c r="AN622" s="6"/>
     </row>
-    <row r="623" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A623" s="12"/>
       <c r="B623" s="12"/>
       <c r="C623" s="12"/>
@@ -27517,7 +27980,7 @@
       <c r="AM623" s="6"/>
       <c r="AN623" s="6"/>
     </row>
-    <row r="624" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A624" s="12"/>
       <c r="B624" s="12"/>
       <c r="C624" s="12"/>
@@ -27559,7 +28022,7 @@
       <c r="AM624" s="6"/>
       <c r="AN624" s="6"/>
     </row>
-    <row r="625" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A625" s="12"/>
       <c r="B625" s="12"/>
       <c r="C625" s="12"/>
@@ -27601,7 +28064,7 @@
       <c r="AM625" s="6"/>
       <c r="AN625" s="6"/>
     </row>
-    <row r="626" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A626" s="12"/>
       <c r="B626" s="12"/>
       <c r="C626" s="12"/>
@@ -27643,7 +28106,7 @@
       <c r="AM626" s="6"/>
       <c r="AN626" s="6"/>
     </row>
-    <row r="627" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A627" s="12"/>
       <c r="B627" s="12"/>
       <c r="C627" s="12"/>
@@ -27685,7 +28148,7 @@
       <c r="AM627" s="6"/>
       <c r="AN627" s="6"/>
     </row>
-    <row r="628" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A628" s="12"/>
       <c r="B628" s="12"/>
       <c r="C628" s="12"/>
@@ -27727,7 +28190,7 @@
       <c r="AM628" s="6"/>
       <c r="AN628" s="6"/>
     </row>
-    <row r="629" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A629" s="12"/>
       <c r="B629" s="12"/>
       <c r="C629" s="12"/>
@@ -27769,7 +28232,7 @@
       <c r="AM629" s="6"/>
       <c r="AN629" s="6"/>
     </row>
-    <row r="630" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A630" s="12"/>
       <c r="B630" s="12"/>
       <c r="C630" s="12"/>
@@ -27811,7 +28274,7 @@
       <c r="AM630" s="6"/>
       <c r="AN630" s="6"/>
     </row>
-    <row r="631" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A631" s="12"/>
       <c r="B631" s="12"/>
       <c r="C631" s="12"/>
@@ -27853,7 +28316,7 @@
       <c r="AM631" s="6"/>
       <c r="AN631" s="6"/>
     </row>
-    <row r="632" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A632" s="12"/>
       <c r="B632" s="12"/>
       <c r="C632" s="12"/>
@@ -27895,7 +28358,7 @@
       <c r="AM632" s="6"/>
       <c r="AN632" s="6"/>
     </row>
-    <row r="633" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A633" s="12"/>
       <c r="B633" s="12"/>
       <c r="C633" s="12"/>
@@ -27937,7 +28400,7 @@
       <c r="AM633" s="6"/>
       <c r="AN633" s="6"/>
     </row>
-    <row r="634" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A634" s="12"/>
       <c r="B634" s="12"/>
       <c r="C634" s="12"/>
@@ -27979,7 +28442,7 @@
       <c r="AM634" s="6"/>
       <c r="AN634" s="6"/>
     </row>
-    <row r="635" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A635" s="12"/>
       <c r="B635" s="12"/>
       <c r="C635" s="12"/>
@@ -28021,7 +28484,7 @@
       <c r="AM635" s="6"/>
       <c r="AN635" s="6"/>
     </row>
-    <row r="636" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A636" s="12"/>
       <c r="B636" s="12"/>
       <c r="C636" s="12"/>
@@ -28063,7 +28526,7 @@
       <c r="AM636" s="6"/>
       <c r="AN636" s="6"/>
     </row>
-    <row r="637" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A637" s="12"/>
       <c r="B637" s="12"/>
       <c r="C637" s="12"/>
@@ -28105,7 +28568,7 @@
       <c r="AM637" s="6"/>
       <c r="AN637" s="6"/>
     </row>
-    <row r="638" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A638" s="12"/>
       <c r="B638" s="12"/>
       <c r="C638" s="12"/>
@@ -28147,7 +28610,7 @@
       <c r="AM638" s="6"/>
       <c r="AN638" s="6"/>
     </row>
-    <row r="639" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A639" s="12"/>
       <c r="B639" s="12"/>
       <c r="C639" s="12"/>
@@ -28189,7 +28652,7 @@
       <c r="AM639" s="6"/>
       <c r="AN639" s="6"/>
     </row>
-    <row r="640" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A640" s="12"/>
       <c r="B640" s="12"/>
       <c r="C640" s="12"/>
@@ -28231,7 +28694,7 @@
       <c r="AM640" s="6"/>
       <c r="AN640" s="6"/>
     </row>
-    <row r="641" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A641" s="12"/>
       <c r="B641" s="12"/>
       <c r="C641" s="12"/>
@@ -28273,7 +28736,7 @@
       <c r="AM641" s="6"/>
       <c r="AN641" s="6"/>
     </row>
-    <row r="642" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A642" s="12"/>
       <c r="B642" s="12"/>
       <c r="C642" s="12"/>
@@ -28315,7 +28778,7 @@
       <c r="AM642" s="6"/>
       <c r="AN642" s="6"/>
     </row>
-    <row r="643" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A643" s="12"/>
       <c r="B643" s="12"/>
       <c r="C643" s="12"/>
@@ -28357,7 +28820,7 @@
       <c r="AM643" s="6"/>
       <c r="AN643" s="6"/>
     </row>
-    <row r="644" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A644" s="12"/>
       <c r="B644" s="12"/>
       <c r="C644" s="12"/>
@@ -28399,7 +28862,7 @@
       <c r="AM644" s="6"/>
       <c r="AN644" s="6"/>
     </row>
-    <row r="645" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A645" s="12"/>
       <c r="B645" s="12"/>
       <c r="C645" s="12"/>
@@ -28441,7 +28904,7 @@
       <c r="AM645" s="6"/>
       <c r="AN645" s="6"/>
     </row>
-    <row r="646" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A646" s="12"/>
       <c r="B646" s="12"/>
       <c r="C646" s="12"/>
@@ -28483,7 +28946,7 @@
       <c r="AM646" s="6"/>
       <c r="AN646" s="6"/>
     </row>
-    <row r="647" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A647" s="12"/>
       <c r="B647" s="12"/>
       <c r="C647" s="12"/>
@@ -28525,7 +28988,7 @@
       <c r="AM647" s="6"/>
       <c r="AN647" s="6"/>
     </row>
-    <row r="648" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A648" s="12"/>
       <c r="B648" s="12"/>
       <c r="C648" s="12"/>
@@ -28567,7 +29030,7 @@
       <c r="AM648" s="6"/>
       <c r="AN648" s="6"/>
     </row>
-    <row r="649" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A649" s="12"/>
       <c r="B649" s="12"/>
       <c r="C649" s="12"/>
@@ -28609,7 +29072,7 @@
       <c r="AM649" s="6"/>
       <c r="AN649" s="6"/>
     </row>
-    <row r="650" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A650" s="12"/>
       <c r="B650" s="12"/>
       <c r="C650" s="12"/>
@@ -28651,7 +29114,7 @@
       <c r="AM650" s="6"/>
       <c r="AN650" s="6"/>
     </row>
-    <row r="651" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A651" s="12"/>
       <c r="B651" s="12"/>
       <c r="C651" s="12"/>
@@ -28693,7 +29156,7 @@
       <c r="AM651" s="6"/>
       <c r="AN651" s="6"/>
     </row>
-    <row r="652" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A652" s="12"/>
       <c r="B652" s="12"/>
       <c r="C652" s="12"/>
@@ -28735,7 +29198,7 @@
       <c r="AM652" s="6"/>
       <c r="AN652" s="6"/>
     </row>
-    <row r="653" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A653" s="12"/>
       <c r="B653" s="12"/>
       <c r="C653" s="12"/>
@@ -28777,7 +29240,7 @@
       <c r="AM653" s="6"/>
       <c r="AN653" s="6"/>
     </row>
-    <row r="654" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A654" s="12"/>
       <c r="B654" s="12"/>
       <c r="C654" s="12"/>
@@ -28819,7 +29282,7 @@
       <c r="AM654" s="6"/>
       <c r="AN654" s="6"/>
     </row>
-    <row r="655" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A655" s="12"/>
       <c r="B655" s="12"/>
       <c r="C655" s="12"/>
@@ -28861,7 +29324,7 @@
       <c r="AM655" s="6"/>
       <c r="AN655" s="6"/>
     </row>
-    <row r="656" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A656" s="12"/>
       <c r="B656" s="12"/>
       <c r="C656" s="12"/>
@@ -28903,7 +29366,7 @@
       <c r="AM656" s="6"/>
       <c r="AN656" s="6"/>
     </row>
-    <row r="657" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A657" s="12"/>
       <c r="B657" s="12"/>
       <c r="C657" s="12"/>
@@ -28945,7 +29408,7 @@
       <c r="AM657" s="6"/>
       <c r="AN657" s="6"/>
     </row>
-    <row r="658" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A658" s="12"/>
       <c r="B658" s="12"/>
       <c r="C658" s="12"/>
@@ -28987,7 +29450,7 @@
       <c r="AM658" s="6"/>
       <c r="AN658" s="6"/>
     </row>
-    <row r="659" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A659" s="12"/>
       <c r="B659" s="12"/>
       <c r="C659" s="12"/>
@@ -29029,7 +29492,7 @@
       <c r="AM659" s="6"/>
       <c r="AN659" s="6"/>
     </row>
-    <row r="660" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A660" s="12"/>
       <c r="B660" s="12"/>
       <c r="C660" s="12"/>
@@ -29071,7 +29534,7 @@
       <c r="AM660" s="6"/>
       <c r="AN660" s="6"/>
     </row>
-    <row r="661" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A661" s="12"/>
       <c r="B661" s="12"/>
       <c r="C661" s="12"/>
@@ -29113,7 +29576,7 @@
       <c r="AM661" s="6"/>
       <c r="AN661" s="6"/>
     </row>
-    <row r="662" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A662" s="12"/>
       <c r="B662" s="12"/>
       <c r="C662" s="12"/>
@@ -29155,7 +29618,7 @@
       <c r="AM662" s="6"/>
       <c r="AN662" s="6"/>
     </row>
-    <row r="663" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A663" s="12"/>
       <c r="B663" s="12"/>
       <c r="C663" s="12"/>
@@ -29197,7 +29660,7 @@
       <c r="AM663" s="6"/>
       <c r="AN663" s="6"/>
     </row>
-    <row r="664" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A664" s="12"/>
       <c r="B664" s="12"/>
       <c r="C664" s="12"/>
@@ -29239,7 +29702,7 @@
       <c r="AM664" s="6"/>
       <c r="AN664" s="6"/>
     </row>
-    <row r="665" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A665" s="12"/>
       <c r="B665" s="12"/>
       <c r="C665" s="12"/>
@@ -29281,7 +29744,7 @@
       <c r="AM665" s="6"/>
       <c r="AN665" s="6"/>
     </row>
-    <row r="666" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A666" s="12"/>
       <c r="B666" s="12"/>
       <c r="C666" s="12"/>
@@ -29323,7 +29786,7 @@
       <c r="AM666" s="6"/>
       <c r="AN666" s="6"/>
     </row>
-    <row r="667" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A667" s="12"/>
       <c r="B667" s="12"/>
       <c r="C667" s="12"/>
@@ -29365,7 +29828,7 @@
       <c r="AM667" s="6"/>
       <c r="AN667" s="6"/>
     </row>
-    <row r="668" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A668" s="12"/>
       <c r="B668" s="12"/>
       <c r="C668" s="12"/>
@@ -29407,7 +29870,7 @@
       <c r="AM668" s="6"/>
       <c r="AN668" s="6"/>
     </row>
-    <row r="669" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A669" s="12"/>
       <c r="B669" s="12"/>
       <c r="C669" s="12"/>
@@ -29449,7 +29912,7 @@
       <c r="AM669" s="6"/>
       <c r="AN669" s="6"/>
     </row>
-    <row r="670" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A670" s="12"/>
       <c r="B670" s="12"/>
       <c r="C670" s="12"/>
@@ -29491,7 +29954,7 @@
       <c r="AM670" s="6"/>
       <c r="AN670" s="6"/>
     </row>
-    <row r="671" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A671" s="12"/>
       <c r="B671" s="12"/>
       <c r="C671" s="12"/>
@@ -29533,7 +29996,7 @@
       <c r="AM671" s="6"/>
       <c r="AN671" s="6"/>
     </row>
-    <row r="672" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A672" s="12"/>
       <c r="B672" s="12"/>
       <c r="C672" s="12"/>
@@ -29575,7 +30038,7 @@
       <c r="AM672" s="6"/>
       <c r="AN672" s="6"/>
     </row>
-    <row r="673" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A673" s="12"/>
       <c r="B673" s="12"/>
       <c r="C673" s="12"/>
@@ -29617,7 +30080,7 @@
       <c r="AM673" s="6"/>
       <c r="AN673" s="6"/>
     </row>
-    <row r="674" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A674" s="12"/>
       <c r="B674" s="12"/>
       <c r="C674" s="12"/>
@@ -29659,7 +30122,7 @@
       <c r="AM674" s="6"/>
       <c r="AN674" s="6"/>
     </row>
-    <row r="675" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A675" s="12"/>
       <c r="B675" s="12"/>
       <c r="C675" s="12"/>
@@ -29701,7 +30164,7 @@
       <c r="AM675" s="6"/>
       <c r="AN675" s="6"/>
     </row>
-    <row r="676" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A676" s="12"/>
       <c r="B676" s="12"/>
       <c r="C676" s="12"/>
@@ -29743,7 +30206,7 @@
       <c r="AM676" s="6"/>
       <c r="AN676" s="6"/>
     </row>
-    <row r="677" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A677" s="12"/>
       <c r="B677" s="12"/>
       <c r="C677" s="12"/>
@@ -29785,7 +30248,7 @@
       <c r="AM677" s="6"/>
       <c r="AN677" s="6"/>
     </row>
-    <row r="678" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A678" s="12"/>
       <c r="B678" s="12"/>
       <c r="C678" s="12"/>
@@ -29827,7 +30290,7 @@
       <c r="AM678" s="6"/>
       <c r="AN678" s="6"/>
     </row>
-    <row r="679" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A679" s="12"/>
       <c r="B679" s="12"/>
       <c r="C679" s="12"/>
@@ -29869,7 +30332,7 @@
       <c r="AM679" s="6"/>
       <c r="AN679" s="6"/>
     </row>
-    <row r="680" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A680" s="12"/>
       <c r="B680" s="12"/>
       <c r="C680" s="12"/>
@@ -29911,7 +30374,7 @@
       <c r="AM680" s="6"/>
       <c r="AN680" s="6"/>
     </row>
-    <row r="681" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A681" s="12"/>
       <c r="B681" s="12"/>
       <c r="C681" s="12"/>
@@ -29953,7 +30416,7 @@
       <c r="AM681" s="6"/>
       <c r="AN681" s="6"/>
     </row>
-    <row r="682" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A682" s="12"/>
       <c r="B682" s="12"/>
       <c r="C682" s="12"/>
@@ -29995,7 +30458,7 @@
       <c r="AM682" s="6"/>
       <c r="AN682" s="6"/>
     </row>
-    <row r="683" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A683" s="12"/>
       <c r="B683" s="12"/>
       <c r="C683" s="12"/>
@@ -30037,7 +30500,7 @@
       <c r="AM683" s="6"/>
       <c r="AN683" s="6"/>
     </row>
-    <row r="684" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A684" s="12"/>
       <c r="B684" s="12"/>
       <c r="C684" s="12"/>
@@ -30079,7 +30542,7 @@
       <c r="AM684" s="6"/>
       <c r="AN684" s="6"/>
     </row>
-    <row r="685" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A685" s="12"/>
       <c r="B685" s="12"/>
       <c r="C685" s="12"/>
@@ -30121,7 +30584,7 @@
       <c r="AM685" s="6"/>
       <c r="AN685" s="6"/>
     </row>
-    <row r="686" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A686" s="12"/>
       <c r="B686" s="12"/>
       <c r="C686" s="12"/>
@@ -30163,7 +30626,7 @@
       <c r="AM686" s="6"/>
       <c r="AN686" s="6"/>
     </row>
-    <row r="687" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A687" s="12"/>
       <c r="B687" s="12"/>
       <c r="C687" s="12"/>
@@ -30205,7 +30668,7 @@
       <c r="AM687" s="6"/>
       <c r="AN687" s="6"/>
     </row>
-    <row r="688" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A688" s="12"/>
       <c r="B688" s="12"/>
       <c r="C688" s="12"/>
@@ -30247,7 +30710,7 @@
       <c r="AM688" s="6"/>
       <c r="AN688" s="6"/>
     </row>
-    <row r="689" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A689" s="12"/>
       <c r="B689" s="12"/>
       <c r="C689" s="12"/>
@@ -30289,7 +30752,7 @@
       <c r="AM689" s="6"/>
       <c r="AN689" s="6"/>
     </row>
-    <row r="690" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A690" s="12"/>
       <c r="B690" s="12"/>
       <c r="C690" s="12"/>
@@ -30331,7 +30794,7 @@
       <c r="AM690" s="6"/>
       <c r="AN690" s="6"/>
     </row>
-    <row r="691" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A691" s="12"/>
       <c r="B691" s="12"/>
       <c r="C691" s="12"/>
@@ -30373,7 +30836,7 @@
       <c r="AM691" s="6"/>
       <c r="AN691" s="6"/>
     </row>
-    <row r="692" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A692" s="12"/>
       <c r="B692" s="12"/>
       <c r="C692" s="12"/>
@@ -30415,7 +30878,7 @@
       <c r="AM692" s="6"/>
       <c r="AN692" s="6"/>
     </row>
-    <row r="693" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A693" s="12"/>
       <c r="B693" s="12"/>
       <c r="C693" s="12"/>
@@ -30457,7 +30920,7 @@
       <c r="AM693" s="6"/>
       <c r="AN693" s="6"/>
     </row>
-    <row r="694" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A694" s="12"/>
       <c r="B694" s="12"/>
       <c r="C694" s="12"/>
@@ -30499,7 +30962,7 @@
       <c r="AM694" s="6"/>
       <c r="AN694" s="6"/>
     </row>
-    <row r="695" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A695" s="12"/>
       <c r="B695" s="12"/>
       <c r="C695" s="12"/>
@@ -30541,7 +31004,7 @@
       <c r="AM695" s="6"/>
       <c r="AN695" s="6"/>
     </row>
-    <row r="696" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A696" s="12"/>
       <c r="B696" s="12"/>
       <c r="C696" s="12"/>
@@ -30583,7 +31046,7 @@
       <c r="AM696" s="6"/>
       <c r="AN696" s="6"/>
     </row>
-    <row r="697" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A697" s="12"/>
       <c r="B697" s="12"/>
       <c r="C697" s="12"/>
@@ -30625,7 +31088,7 @@
       <c r="AM697" s="6"/>
       <c r="AN697" s="6"/>
     </row>
-    <row r="698" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A698" s="12"/>
       <c r="B698" s="12"/>
       <c r="C698" s="12"/>
@@ -30667,7 +31130,7 @@
       <c r="AM698" s="6"/>
       <c r="AN698" s="6"/>
     </row>
-    <row r="699" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A699" s="12"/>
       <c r="B699" s="12"/>
       <c r="C699" s="12"/>
@@ -30709,7 +31172,7 @@
       <c r="AM699" s="6"/>
       <c r="AN699" s="6"/>
     </row>
-    <row r="700" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A700" s="12"/>
       <c r="B700" s="12"/>
       <c r="C700" s="12"/>
@@ -30751,7 +31214,7 @@
       <c r="AM700" s="6"/>
       <c r="AN700" s="6"/>
     </row>
-    <row r="701" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A701" s="12"/>
       <c r="B701" s="12"/>
       <c r="C701" s="12"/>
@@ -30793,7 +31256,7 @@
       <c r="AM701" s="6"/>
       <c r="AN701" s="6"/>
     </row>
-    <row r="702" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A702" s="12"/>
       <c r="B702" s="12"/>
       <c r="C702" s="12"/>
@@ -30835,7 +31298,7 @@
       <c r="AM702" s="6"/>
       <c r="AN702" s="6"/>
     </row>
-    <row r="703" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A703" s="12"/>
       <c r="B703" s="12"/>
       <c r="C703" s="12"/>
@@ -30877,7 +31340,7 @@
       <c r="AM703" s="6"/>
       <c r="AN703" s="6"/>
     </row>
-    <row r="704" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A704" s="12"/>
       <c r="B704" s="12"/>
       <c r="C704" s="12"/>
@@ -30919,7 +31382,7 @@
       <c r="AM704" s="6"/>
       <c r="AN704" s="6"/>
     </row>
-    <row r="705" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A705" s="12"/>
       <c r="B705" s="12"/>
       <c r="C705" s="12"/>
@@ -30961,7 +31424,7 @@
       <c r="AM705" s="6"/>
       <c r="AN705" s="6"/>
     </row>
-    <row r="706" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A706" s="12"/>
       <c r="B706" s="12"/>
       <c r="C706" s="12"/>
@@ -31003,7 +31466,7 @@
       <c r="AM706" s="6"/>
       <c r="AN706" s="6"/>
     </row>
-    <row r="707" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A707" s="12"/>
       <c r="B707" s="12"/>
       <c r="C707" s="12"/>
@@ -31045,7 +31508,7 @@
       <c r="AM707" s="6"/>
       <c r="AN707" s="6"/>
     </row>
-    <row r="708" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A708" s="12"/>
       <c r="B708" s="12"/>
       <c r="C708" s="12"/>
@@ -31087,7 +31550,7 @@
       <c r="AM708" s="6"/>
       <c r="AN708" s="6"/>
     </row>
-    <row r="709" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A709" s="12"/>
       <c r="B709" s="12"/>
       <c r="C709" s="12"/>
@@ -31129,7 +31592,7 @@
       <c r="AM709" s="6"/>
       <c r="AN709" s="6"/>
     </row>
-    <row r="710" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A710" s="12"/>
       <c r="B710" s="12"/>
       <c r="C710" s="12"/>
@@ -31171,7 +31634,7 @@
       <c r="AM710" s="6"/>
       <c r="AN710" s="6"/>
     </row>
-    <row r="711" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A711" s="12"/>
       <c r="B711" s="12"/>
       <c r="C711" s="12"/>
@@ -31213,7 +31676,7 @@
       <c r="AM711" s="6"/>
       <c r="AN711" s="6"/>
     </row>
-    <row r="712" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A712" s="12"/>
       <c r="B712" s="12"/>
       <c r="C712" s="12"/>
@@ -31255,7 +31718,7 @@
       <c r="AM712" s="6"/>
       <c r="AN712" s="6"/>
     </row>
-    <row r="713" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A713" s="12"/>
       <c r="B713" s="12"/>
       <c r="C713" s="12"/>
@@ -31297,7 +31760,7 @@
       <c r="AM713" s="6"/>
       <c r="AN713" s="6"/>
     </row>
-    <row r="714" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A714" s="12"/>
       <c r="B714" s="12"/>
       <c r="C714" s="12"/>
@@ -31339,7 +31802,7 @@
       <c r="AM714" s="6"/>
       <c r="AN714" s="6"/>
     </row>
-    <row r="715" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A715" s="12"/>
       <c r="B715" s="12"/>
       <c r="C715" s="12"/>
@@ -31381,7 +31844,7 @@
       <c r="AM715" s="6"/>
       <c r="AN715" s="6"/>
     </row>
-    <row r="716" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A716" s="12"/>
       <c r="B716" s="12"/>
       <c r="C716" s="12"/>
@@ -31423,7 +31886,7 @@
       <c r="AM716" s="6"/>
       <c r="AN716" s="6"/>
     </row>
-    <row r="717" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A717" s="12"/>
       <c r="B717" s="12"/>
       <c r="C717" s="12"/>
@@ -31465,7 +31928,7 @@
       <c r="AM717" s="6"/>
       <c r="AN717" s="6"/>
     </row>
-    <row r="718" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A718" s="12"/>
       <c r="B718" s="12"/>
       <c r="C718" s="12"/>
@@ -31507,7 +31970,7 @@
       <c r="AM718" s="6"/>
       <c r="AN718" s="6"/>
     </row>
-    <row r="719" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A719" s="12"/>
       <c r="B719" s="12"/>
       <c r="C719" s="12"/>
@@ -31549,7 +32012,7 @@
       <c r="AM719" s="6"/>
       <c r="AN719" s="6"/>
     </row>
-    <row r="720" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A720" s="12"/>
       <c r="B720" s="12"/>
       <c r="C720" s="12"/>
@@ -31591,7 +32054,7 @@
       <c r="AM720" s="6"/>
       <c r="AN720" s="6"/>
     </row>
-    <row r="721" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A721" s="12"/>
       <c r="B721" s="12"/>
       <c r="C721" s="12"/>
@@ -31633,7 +32096,7 @@
       <c r="AM721" s="6"/>
       <c r="AN721" s="6"/>
     </row>
-    <row r="722" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A722" s="12"/>
       <c r="B722" s="12"/>
       <c r="C722" s="12"/>
@@ -31675,7 +32138,7 @@
       <c r="AM722" s="6"/>
       <c r="AN722" s="6"/>
     </row>
-    <row r="723" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A723" s="12"/>
       <c r="B723" s="12"/>
       <c r="C723" s="12"/>
@@ -31717,7 +32180,7 @@
       <c r="AM723" s="6"/>
       <c r="AN723" s="6"/>
     </row>
-    <row r="724" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A724" s="12"/>
       <c r="B724" s="12"/>
       <c r="C724" s="12"/>
@@ -31759,7 +32222,7 @@
       <c r="AM724" s="6"/>
       <c r="AN724" s="6"/>
     </row>
-    <row r="725" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A725" s="12"/>
       <c r="B725" s="12"/>
       <c r="C725" s="12"/>
@@ -31801,7 +32264,7 @@
       <c r="AM725" s="6"/>
       <c r="AN725" s="6"/>
     </row>
-    <row r="726" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A726" s="12"/>
       <c r="B726" s="12"/>
       <c r="C726" s="12"/>
@@ -31843,7 +32306,7 @@
       <c r="AM726" s="6"/>
       <c r="AN726" s="6"/>
     </row>
-    <row r="727" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A727" s="12"/>
       <c r="B727" s="12"/>
       <c r="C727" s="12"/>
@@ -31885,7 +32348,7 @@
       <c r="AM727" s="6"/>
       <c r="AN727" s="6"/>
     </row>
-    <row r="728" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A728" s="12"/>
       <c r="B728" s="12"/>
       <c r="C728" s="12"/>
@@ -31927,7 +32390,7 @@
       <c r="AM728" s="6"/>
       <c r="AN728" s="6"/>
     </row>
-    <row r="729" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A729" s="12"/>
       <c r="B729" s="12"/>
       <c r="C729" s="12"/>
@@ -31969,7 +32432,7 @@
       <c r="AM729" s="6"/>
       <c r="AN729" s="6"/>
     </row>
-    <row r="730" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A730" s="12"/>
       <c r="B730" s="12"/>
       <c r="C730" s="12"/>
@@ -32011,7 +32474,7 @@
       <c r="AM730" s="6"/>
       <c r="AN730" s="6"/>
     </row>
-    <row r="731" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A731" s="12"/>
       <c r="B731" s="12"/>
       <c r="C731" s="12"/>
@@ -32053,7 +32516,7 @@
       <c r="AM731" s="6"/>
       <c r="AN731" s="6"/>
     </row>
-    <row r="732" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A732" s="12"/>
       <c r="B732" s="12"/>
       <c r="C732" s="12"/>
@@ -32095,7 +32558,7 @@
       <c r="AM732" s="6"/>
       <c r="AN732" s="6"/>
     </row>
-    <row r="733" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A733" s="12"/>
       <c r="B733" s="12"/>
       <c r="C733" s="12"/>
@@ -32137,7 +32600,7 @@
       <c r="AM733" s="6"/>
       <c r="AN733" s="6"/>
     </row>
-    <row r="734" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A734" s="12"/>
       <c r="B734" s="12"/>
       <c r="C734" s="12"/>
@@ -32179,7 +32642,7 @@
       <c r="AM734" s="6"/>
       <c r="AN734" s="6"/>
     </row>
-    <row r="735" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A735" s="12"/>
       <c r="B735" s="12"/>
       <c r="C735" s="12"/>
@@ -32221,7 +32684,7 @@
       <c r="AM735" s="6"/>
       <c r="AN735" s="6"/>
     </row>
-    <row r="736" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A736" s="12"/>
       <c r="B736" s="12"/>
       <c r="C736" s="12"/>
@@ -32263,7 +32726,7 @@
       <c r="AM736" s="6"/>
       <c r="AN736" s="6"/>
     </row>
-    <row r="737" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A737" s="12"/>
       <c r="B737" s="12"/>
       <c r="C737" s="12"/>
@@ -32305,7 +32768,7 @@
       <c r="AM737" s="6"/>
       <c r="AN737" s="6"/>
     </row>
-    <row r="738" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A738" s="12"/>
       <c r="B738" s="12"/>
       <c r="C738" s="12"/>
@@ -32347,7 +32810,7 @@
       <c r="AM738" s="6"/>
       <c r="AN738" s="6"/>
     </row>
-    <row r="739" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A739" s="12"/>
       <c r="B739" s="12"/>
       <c r="C739" s="12"/>
@@ -32389,7 +32852,7 @@
       <c r="AM739" s="6"/>
       <c r="AN739" s="6"/>
     </row>
-    <row r="740" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A740" s="12"/>
       <c r="B740" s="12"/>
       <c r="C740" s="12"/>
@@ -32431,7 +32894,7 @@
       <c r="AM740" s="6"/>
       <c r="AN740" s="6"/>
     </row>
-    <row r="741" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A741" s="12"/>
       <c r="B741" s="12"/>
       <c r="C741" s="12"/>
@@ -32473,7 +32936,7 @@
       <c r="AM741" s="6"/>
       <c r="AN741" s="6"/>
     </row>
-    <row r="742" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A742" s="12"/>
       <c r="B742" s="12"/>
       <c r="C742" s="12"/>
@@ -32515,7 +32978,7 @@
       <c r="AM742" s="6"/>
       <c r="AN742" s="6"/>
     </row>
-    <row r="743" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A743" s="12"/>
       <c r="B743" s="12"/>
       <c r="C743" s="12"/>
@@ -32557,7 +33020,7 @@
       <c r="AM743" s="6"/>
       <c r="AN743" s="6"/>
     </row>
-    <row r="744" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A744" s="12"/>
       <c r="B744" s="12"/>
       <c r="C744" s="12"/>
@@ -32599,7 +33062,7 @@
       <c r="AM744" s="6"/>
       <c r="AN744" s="6"/>
     </row>
-    <row r="745" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A745" s="12"/>
       <c r="B745" s="12"/>
       <c r="C745" s="12"/>
@@ -32641,7 +33104,7 @@
       <c r="AM745" s="6"/>
       <c r="AN745" s="6"/>
     </row>
-    <row r="746" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A746" s="12"/>
       <c r="B746" s="12"/>
       <c r="C746" s="12"/>
@@ -32683,7 +33146,7 @@
       <c r="AM746" s="6"/>
       <c r="AN746" s="6"/>
     </row>
-    <row r="747" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A747" s="12"/>
       <c r="B747" s="12"/>
       <c r="C747" s="12"/>
@@ -32725,7 +33188,7 @@
       <c r="AM747" s="6"/>
       <c r="AN747" s="6"/>
     </row>
-    <row r="748" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A748" s="12"/>
       <c r="B748" s="12"/>
       <c r="C748" s="12"/>
@@ -32767,7 +33230,7 @@
       <c r="AM748" s="6"/>
       <c r="AN748" s="6"/>
     </row>
-    <row r="749" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A749" s="12"/>
       <c r="B749" s="12"/>
       <c r="C749" s="12"/>
@@ -32809,7 +33272,7 @@
       <c r="AM749" s="6"/>
       <c r="AN749" s="6"/>
     </row>
-    <row r="750" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A750" s="12"/>
       <c r="B750" s="12"/>
       <c r="C750" s="12"/>
@@ -32851,7 +33314,7 @@
       <c r="AM750" s="6"/>
       <c r="AN750" s="6"/>
     </row>
-    <row r="751" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A751" s="12"/>
       <c r="B751" s="12"/>
       <c r="C751" s="12"/>
@@ -32893,7 +33356,7 @@
       <c r="AM751" s="6"/>
       <c r="AN751" s="6"/>
     </row>
-    <row r="752" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A752" s="12"/>
       <c r="B752" s="12"/>
       <c r="C752" s="12"/>
@@ -32935,7 +33398,7 @@
       <c r="AM752" s="6"/>
       <c r="AN752" s="6"/>
     </row>
-    <row r="753" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A753" s="12"/>
       <c r="B753" s="12"/>
       <c r="C753" s="12"/>
@@ -32977,7 +33440,7 @@
       <c r="AM753" s="6"/>
       <c r="AN753" s="6"/>
     </row>
-    <row r="754" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A754" s="12"/>
       <c r="B754" s="12"/>
       <c r="C754" s="12"/>
@@ -33019,7 +33482,7 @@
       <c r="AM754" s="6"/>
       <c r="AN754" s="6"/>
     </row>
-    <row r="755" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A755" s="12"/>
       <c r="B755" s="12"/>
       <c r="C755" s="12"/>
@@ -33123,4 +33586,405 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C179FE-D1C9-4048-A0D3-B569542EE019}">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.1796875" style="13"/>
+    <col min="2" max="2" width="23.26953125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="13" customWidth="1"/>
+    <col min="4" max="5" width="19" style="13" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.1796875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="29.26953125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="27" style="13" customWidth="1"/>
+    <col min="12" max="12" width="25.453125" style="13" customWidth="1"/>
+    <col min="13" max="13" width="25.1796875" style="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3406010B-37DA-462B-8DC6-B4E80ECF9E33}">
+  <dimension ref="A1:AD3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="9.1796875" style="13"/>
+    <col min="3" max="3" width="8.7265625" style="13"/>
+    <col min="4" max="30" width="9.1796875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A1" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1">
+        <v>14</v>
+      </c>
+      <c r="O1" s="1">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1">
+        <v>18</v>
+      </c>
+      <c r="S1" s="1">
+        <v>19</v>
+      </c>
+      <c r="T1" s="1">
+        <v>20</v>
+      </c>
+      <c r="U1" s="1">
+        <v>21</v>
+      </c>
+      <c r="V1" s="1">
+        <v>22</v>
+      </c>
+      <c r="W1" s="1">
+        <v>23</v>
+      </c>
+      <c r="X1" s="1">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>26</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="X2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="95.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="28"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/wwwroot/template/TemplateExportHistoryNew.xlsx
+++ b/wwwroot/template/TemplateExportHistoryNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2E918D-C833-44BE-A860-CE277F8A2A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3961455E-40F1-4A28-93C8-7F09ADA2929E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{D99E87B9-757D-492C-8DC2-9D6FEAFC762F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99E87B9-757D-492C-8DC2-9D6FEAFC762F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử yêu cầu" sheetId="1" r:id="rId1"/>
@@ -1248,23 +1248,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1284,11 +1278,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1631,18 +1631,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AC2F7D2-707F-4FAA-BAE9-54D056C0C3CB}">
   <dimension ref="A1:AN755"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.1796875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" customWidth="1"/>
-    <col min="10" max="10" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="15" max="26" width="0" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1685,15 +1685,15 @@
       <c r="N1" s="1">
         <v>12</v>
       </c>
-      <c r="O1" s="20">
+      <c r="O1" s="18">
         <f>N1+1</f>
         <v>13</v>
       </c>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="22"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="20"/>
       <c r="U1" s="2">
         <v>14</v>
       </c>
@@ -1774,133 +1774,133 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="18" t="s">
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="18" t="s">
+      <c r="W2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="18" t="s">
+      <c r="X2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="18" t="s">
+      <c r="Y2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="18" t="s">
+      <c r="Z2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="18" t="s">
+      <c r="AA2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="18" t="s">
+      <c r="AB2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="18" t="s">
+      <c r="AC2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AE2" s="18" t="s">
+      <c r="AE2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AF2" s="18" t="s">
+      <c r="AF2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AG2" s="17" t="s">
+      <c r="AG2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AH2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AK2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AL2" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AM2" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AN2" s="25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="115" x14ac:dyDescent="0.35">
-      <c r="A3" s="27"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
+    <row r="3" spans="1:40" ht="132" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
       <c r="O3" s="5" t="s">
         <v>19</v>
       </c>
@@ -1919,28 +1919,28 @@
       <c r="T3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="19"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="19"/>
-      <c r="AG3" s="17"/>
-      <c r="AH3" s="17"/>
-      <c r="AI3" s="16"/>
-      <c r="AJ3" s="16"/>
-      <c r="AK3" s="17"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14"/>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1982,7 +1982,7 @@
       <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -2024,7 +2024,7 @@
       <c r="AM5" s="6"/>
       <c r="AN5" s="6"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -2066,7 +2066,7 @@
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -2108,7 +2108,7 @@
       <c r="AM7" s="6"/>
       <c r="AN7" s="6"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2150,7 +2150,7 @@
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2192,7 +2192,7 @@
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2234,7 +2234,7 @@
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -2276,7 +2276,7 @@
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2318,7 +2318,7 @@
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2360,7 +2360,7 @@
       <c r="AM13" s="6"/>
       <c r="AN13" s="6"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -2402,7 +2402,7 @@
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -2444,7 +2444,7 @@
       <c r="AM15" s="6"/>
       <c r="AN15" s="6"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -2486,7 +2486,7 @@
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -2528,7 +2528,7 @@
       <c r="AM17" s="6"/>
       <c r="AN17" s="6"/>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2570,7 +2570,7 @@
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -2612,7 +2612,7 @@
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -2654,7 +2654,7 @@
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -2696,7 +2696,7 @@
       <c r="AM21" s="6"/>
       <c r="AN21" s="6"/>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -2738,7 +2738,7 @@
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -2780,7 +2780,7 @@
       <c r="AM23" s="6"/>
       <c r="AN23" s="6"/>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2822,7 +2822,7 @@
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2864,7 +2864,7 @@
       <c r="AM25" s="6"/>
       <c r="AN25" s="6"/>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -2906,7 +2906,7 @@
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -2948,7 +2948,7 @@
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2990,7 +2990,7 @@
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -3032,7 +3032,7 @@
       <c r="AM29" s="6"/>
       <c r="AN29" s="6"/>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -3074,7 +3074,7 @@
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -3116,7 +3116,7 @@
       <c r="AM31" s="6"/>
       <c r="AN31" s="6"/>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -3158,7 +3158,7 @@
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -3200,7 +3200,7 @@
       <c r="AM33" s="6"/>
       <c r="AN33" s="6"/>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -3242,7 +3242,7 @@
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -3284,7 +3284,7 @@
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -3326,7 +3326,7 @@
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -3368,7 +3368,7 @@
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -3410,7 +3410,7 @@
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -3452,7 +3452,7 @@
       <c r="AM39" s="6"/>
       <c r="AN39" s="6"/>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -3494,7 +3494,7 @@
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -3536,7 +3536,7 @@
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -3578,7 +3578,7 @@
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -3620,7 +3620,7 @@
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -3662,7 +3662,7 @@
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -3704,7 +3704,7 @@
       <c r="AM45" s="6"/>
       <c r="AN45" s="6"/>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -3746,7 +3746,7 @@
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -3788,7 +3788,7 @@
       <c r="AM47" s="6"/>
       <c r="AN47" s="6"/>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -3830,7 +3830,7 @@
       <c r="AM48" s="6"/>
       <c r="AN48" s="6"/>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -3872,7 +3872,7 @@
       <c r="AM49" s="6"/>
       <c r="AN49" s="6"/>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -3914,7 +3914,7 @@
       <c r="AM50" s="6"/>
       <c r="AN50" s="6"/>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -3956,7 +3956,7 @@
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -3998,7 +3998,7 @@
       <c r="AM52" s="6"/>
       <c r="AN52" s="6"/>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -4040,7 +4040,7 @@
       <c r="AM53" s="6"/>
       <c r="AN53" s="6"/>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -4082,7 +4082,7 @@
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -4124,7 +4124,7 @@
       <c r="AM55" s="6"/>
       <c r="AN55" s="6"/>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -4166,7 +4166,7 @@
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -4208,7 +4208,7 @@
       <c r="AM57" s="6"/>
       <c r="AN57" s="6"/>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -4250,7 +4250,7 @@
       <c r="AM58" s="6"/>
       <c r="AN58" s="6"/>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -4292,7 +4292,7 @@
       <c r="AM59" s="6"/>
       <c r="AN59" s="6"/>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -4334,7 +4334,7 @@
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -4376,7 +4376,7 @@
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -4418,7 +4418,7 @@
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -4460,7 +4460,7 @@
       <c r="AM63" s="6"/>
       <c r="AN63" s="6"/>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -4502,7 +4502,7 @@
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -4544,7 +4544,7 @@
       <c r="AM65" s="6"/>
       <c r="AN65" s="6"/>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -4586,7 +4586,7 @@
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -4628,7 +4628,7 @@
       <c r="AM67" s="6"/>
       <c r="AN67" s="6"/>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -4670,7 +4670,7 @@
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -4712,7 +4712,7 @@
       <c r="AM69" s="6"/>
       <c r="AN69" s="6"/>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -4754,7 +4754,7 @@
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -4796,7 +4796,7 @@
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -4838,7 +4838,7 @@
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
@@ -4880,7 +4880,7 @@
       <c r="AM73" s="6"/>
       <c r="AN73" s="6"/>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -4922,7 +4922,7 @@
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
@@ -4964,7 +4964,7 @@
       <c r="AM75" s="6"/>
       <c r="AN75" s="6"/>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -5006,7 +5006,7 @@
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
@@ -5048,7 +5048,7 @@
       <c r="AM77" s="6"/>
       <c r="AN77" s="6"/>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -5090,7 +5090,7 @@
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
     </row>
-    <row r="79" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
@@ -5132,7 +5132,7 @@
       <c r="AM79" s="6"/>
       <c r="AN79" s="6"/>
     </row>
-    <row r="80" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
@@ -5174,7 +5174,7 @@
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
     </row>
-    <row r="81" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
@@ -5216,7 +5216,7 @@
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
     </row>
-    <row r="82" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -5258,7 +5258,7 @@
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
     </row>
-    <row r="83" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
@@ -5300,7 +5300,7 @@
       <c r="AM83" s="6"/>
       <c r="AN83" s="6"/>
     </row>
-    <row r="84" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
@@ -5342,7 +5342,7 @@
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
     </row>
-    <row r="85" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -5384,7 +5384,7 @@
       <c r="AM85" s="6"/>
       <c r="AN85" s="6"/>
     </row>
-    <row r="86" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
@@ -5426,7 +5426,7 @@
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
     </row>
-    <row r="87" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
@@ -5468,7 +5468,7 @@
       <c r="AM87" s="6"/>
       <c r="AN87" s="6"/>
     </row>
-    <row r="88" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
@@ -5510,7 +5510,7 @@
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
     </row>
-    <row r="89" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -5552,7 +5552,7 @@
       <c r="AM89" s="6"/>
       <c r="AN89" s="6"/>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
@@ -5594,7 +5594,7 @@
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
     </row>
-    <row r="91" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
@@ -5636,7 +5636,7 @@
       <c r="AM91" s="6"/>
       <c r="AN91" s="6"/>
     </row>
-    <row r="92" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -5678,7 +5678,7 @@
       <c r="AM92" s="6"/>
       <c r="AN92" s="6"/>
     </row>
-    <row r="93" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -5720,7 +5720,7 @@
       <c r="AM93" s="6"/>
       <c r="AN93" s="6"/>
     </row>
-    <row r="94" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
@@ -5762,7 +5762,7 @@
       <c r="AM94" s="6"/>
       <c r="AN94" s="6"/>
     </row>
-    <row r="95" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -5804,7 +5804,7 @@
       <c r="AM95" s="6"/>
       <c r="AN95" s="6"/>
     </row>
-    <row r="96" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -5846,7 +5846,7 @@
       <c r="AM96" s="6"/>
       <c r="AN96" s="6"/>
     </row>
-    <row r="97" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -5888,7 +5888,7 @@
       <c r="AM97" s="6"/>
       <c r="AN97" s="6"/>
     </row>
-    <row r="98" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
@@ -5930,7 +5930,7 @@
       <c r="AM98" s="6"/>
       <c r="AN98" s="6"/>
     </row>
-    <row r="99" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
@@ -5972,7 +5972,7 @@
       <c r="AM99" s="6"/>
       <c r="AN99" s="6"/>
     </row>
-    <row r="100" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -6014,7 +6014,7 @@
       <c r="AM100" s="6"/>
       <c r="AN100" s="6"/>
     </row>
-    <row r="101" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -6056,7 +6056,7 @@
       <c r="AM101" s="6"/>
       <c r="AN101" s="6"/>
     </row>
-    <row r="102" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -6098,7 +6098,7 @@
       <c r="AM102" s="6"/>
       <c r="AN102" s="6"/>
     </row>
-    <row r="103" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -6140,7 +6140,7 @@
       <c r="AM103" s="6"/>
       <c r="AN103" s="6"/>
     </row>
-    <row r="104" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -6182,7 +6182,7 @@
       <c r="AM104" s="6"/>
       <c r="AN104" s="6"/>
     </row>
-    <row r="105" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -6224,7 +6224,7 @@
       <c r="AM105" s="6"/>
       <c r="AN105" s="6"/>
     </row>
-    <row r="106" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -6266,7 +6266,7 @@
       <c r="AM106" s="6"/>
       <c r="AN106" s="6"/>
     </row>
-    <row r="107" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -6308,7 +6308,7 @@
       <c r="AM107" s="6"/>
       <c r="AN107" s="6"/>
     </row>
-    <row r="108" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -6350,7 +6350,7 @@
       <c r="AM108" s="6"/>
       <c r="AN108" s="6"/>
     </row>
-    <row r="109" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -6392,7 +6392,7 @@
       <c r="AM109" s="6"/>
       <c r="AN109" s="6"/>
     </row>
-    <row r="110" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -6434,7 +6434,7 @@
       <c r="AM110" s="6"/>
       <c r="AN110" s="6"/>
     </row>
-    <row r="111" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -6476,7 +6476,7 @@
       <c r="AM111" s="6"/>
       <c r="AN111" s="6"/>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -6518,7 +6518,7 @@
       <c r="AM112" s="6"/>
       <c r="AN112" s="6"/>
     </row>
-    <row r="113" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -6560,7 +6560,7 @@
       <c r="AM113" s="6"/>
       <c r="AN113" s="6"/>
     </row>
-    <row r="114" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -6602,7 +6602,7 @@
       <c r="AM114" s="6"/>
       <c r="AN114" s="6"/>
     </row>
-    <row r="115" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -6644,7 +6644,7 @@
       <c r="AM115" s="6"/>
       <c r="AN115" s="6"/>
     </row>
-    <row r="116" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -6686,7 +6686,7 @@
       <c r="AM116" s="6"/>
       <c r="AN116" s="6"/>
     </row>
-    <row r="117" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -6728,7 +6728,7 @@
       <c r="AM117" s="6"/>
       <c r="AN117" s="6"/>
     </row>
-    <row r="118" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -6770,7 +6770,7 @@
       <c r="AM118" s="6"/>
       <c r="AN118" s="6"/>
     </row>
-    <row r="119" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -6812,7 +6812,7 @@
       <c r="AM119" s="6"/>
       <c r="AN119" s="6"/>
     </row>
-    <row r="120" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -6854,7 +6854,7 @@
       <c r="AM120" s="6"/>
       <c r="AN120" s="6"/>
     </row>
-    <row r="121" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -6896,7 +6896,7 @@
       <c r="AM121" s="6"/>
       <c r="AN121" s="6"/>
     </row>
-    <row r="122" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -6938,7 +6938,7 @@
       <c r="AM122" s="6"/>
       <c r="AN122" s="6"/>
     </row>
-    <row r="123" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -6980,7 +6980,7 @@
       <c r="AM123" s="6"/>
       <c r="AN123" s="6"/>
     </row>
-    <row r="124" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -7022,7 +7022,7 @@
       <c r="AM124" s="6"/>
       <c r="AN124" s="6"/>
     </row>
-    <row r="125" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -7064,7 +7064,7 @@
       <c r="AM125" s="6"/>
       <c r="AN125" s="6"/>
     </row>
-    <row r="126" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -7106,7 +7106,7 @@
       <c r="AM126" s="6"/>
       <c r="AN126" s="6"/>
     </row>
-    <row r="127" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -7148,7 +7148,7 @@
       <c r="AM127" s="6"/>
       <c r="AN127" s="6"/>
     </row>
-    <row r="128" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
@@ -7190,7 +7190,7 @@
       <c r="AM128" s="6"/>
       <c r="AN128" s="6"/>
     </row>
-    <row r="129" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -7232,7 +7232,7 @@
       <c r="AM129" s="6"/>
       <c r="AN129" s="6"/>
     </row>
-    <row r="130" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -7274,7 +7274,7 @@
       <c r="AM130" s="6"/>
       <c r="AN130" s="6"/>
     </row>
-    <row r="131" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -7316,7 +7316,7 @@
       <c r="AM131" s="6"/>
       <c r="AN131" s="6"/>
     </row>
-    <row r="132" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -7358,7 +7358,7 @@
       <c r="AM132" s="6"/>
       <c r="AN132" s="6"/>
     </row>
-    <row r="133" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -7400,7 +7400,7 @@
       <c r="AM133" s="6"/>
       <c r="AN133" s="6"/>
     </row>
-    <row r="134" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -7442,7 +7442,7 @@
       <c r="AM134" s="6"/>
       <c r="AN134" s="6"/>
     </row>
-    <row r="135" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -7484,7 +7484,7 @@
       <c r="AM135" s="6"/>
       <c r="AN135" s="6"/>
     </row>
-    <row r="136" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -7526,7 +7526,7 @@
       <c r="AM136" s="6"/>
       <c r="AN136" s="6"/>
     </row>
-    <row r="137" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -7568,7 +7568,7 @@
       <c r="AM137" s="6"/>
       <c r="AN137" s="6"/>
     </row>
-    <row r="138" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
@@ -7610,7 +7610,7 @@
       <c r="AM138" s="6"/>
       <c r="AN138" s="6"/>
     </row>
-    <row r="139" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -7652,7 +7652,7 @@
       <c r="AM139" s="6"/>
       <c r="AN139" s="6"/>
     </row>
-    <row r="140" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -7694,7 +7694,7 @@
       <c r="AM140" s="6"/>
       <c r="AN140" s="6"/>
     </row>
-    <row r="141" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -7736,7 +7736,7 @@
       <c r="AM141" s="6"/>
       <c r="AN141" s="6"/>
     </row>
-    <row r="142" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
@@ -7778,7 +7778,7 @@
       <c r="AM142" s="6"/>
       <c r="AN142" s="6"/>
     </row>
-    <row r="143" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
@@ -7820,7 +7820,7 @@
       <c r="AM143" s="6"/>
       <c r="AN143" s="6"/>
     </row>
-    <row r="144" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
@@ -7862,7 +7862,7 @@
       <c r="AM144" s="6"/>
       <c r="AN144" s="6"/>
     </row>
-    <row r="145" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
@@ -7904,7 +7904,7 @@
       <c r="AM145" s="6"/>
       <c r="AN145" s="6"/>
     </row>
-    <row r="146" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -7946,7 +7946,7 @@
       <c r="AM146" s="6"/>
       <c r="AN146" s="6"/>
     </row>
-    <row r="147" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12"/>
@@ -7988,7 +7988,7 @@
       <c r="AM147" s="6"/>
       <c r="AN147" s="6"/>
     </row>
-    <row r="148" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -8030,7 +8030,7 @@
       <c r="AM148" s="6"/>
       <c r="AN148" s="6"/>
     </row>
-    <row r="149" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
@@ -8072,7 +8072,7 @@
       <c r="AM149" s="6"/>
       <c r="AN149" s="6"/>
     </row>
-    <row r="150" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -8114,7 +8114,7 @@
       <c r="AM150" s="6"/>
       <c r="AN150" s="6"/>
     </row>
-    <row r="151" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
@@ -8156,7 +8156,7 @@
       <c r="AM151" s="6"/>
       <c r="AN151" s="6"/>
     </row>
-    <row r="152" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="12"/>
@@ -8198,7 +8198,7 @@
       <c r="AM152" s="6"/>
       <c r="AN152" s="6"/>
     </row>
-    <row r="153" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
@@ -8240,7 +8240,7 @@
       <c r="AM153" s="6"/>
       <c r="AN153" s="6"/>
     </row>
-    <row r="154" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -8282,7 +8282,7 @@
       <c r="AM154" s="6"/>
       <c r="AN154" s="6"/>
     </row>
-    <row r="155" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -8324,7 +8324,7 @@
       <c r="AM155" s="6"/>
       <c r="AN155" s="6"/>
     </row>
-    <row r="156" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -8366,7 +8366,7 @@
       <c r="AM156" s="6"/>
       <c r="AN156" s="6"/>
     </row>
-    <row r="157" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
@@ -8408,7 +8408,7 @@
       <c r="AM157" s="6"/>
       <c r="AN157" s="6"/>
     </row>
-    <row r="158" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12"/>
@@ -8450,7 +8450,7 @@
       <c r="AM158" s="6"/>
       <c r="AN158" s="6"/>
     </row>
-    <row r="159" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12"/>
@@ -8492,7 +8492,7 @@
       <c r="AM159" s="6"/>
       <c r="AN159" s="6"/>
     </row>
-    <row r="160" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12"/>
@@ -8534,7 +8534,7 @@
       <c r="AM160" s="6"/>
       <c r="AN160" s="6"/>
     </row>
-    <row r="161" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -8576,7 +8576,7 @@
       <c r="AM161" s="6"/>
       <c r="AN161" s="6"/>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
@@ -8618,7 +8618,7 @@
       <c r="AM162" s="6"/>
       <c r="AN162" s="6"/>
     </row>
-    <row r="163" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
@@ -8660,7 +8660,7 @@
       <c r="AM163" s="6"/>
       <c r="AN163" s="6"/>
     </row>
-    <row r="164" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12"/>
@@ -8702,7 +8702,7 @@
       <c r="AM164" s="6"/>
       <c r="AN164" s="6"/>
     </row>
-    <row r="165" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
@@ -8744,7 +8744,7 @@
       <c r="AM165" s="6"/>
       <c r="AN165" s="6"/>
     </row>
-    <row r="166" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
@@ -8786,7 +8786,7 @@
       <c r="AM166" s="6"/>
       <c r="AN166" s="6"/>
     </row>
-    <row r="167" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
@@ -8828,7 +8828,7 @@
       <c r="AM167" s="6"/>
       <c r="AN167" s="6"/>
     </row>
-    <row r="168" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -8870,7 +8870,7 @@
       <c r="AM168" s="6"/>
       <c r="AN168" s="6"/>
     </row>
-    <row r="169" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
@@ -8912,7 +8912,7 @@
       <c r="AM169" s="6"/>
       <c r="AN169" s="6"/>
     </row>
-    <row r="170" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
@@ -8954,7 +8954,7 @@
       <c r="AM170" s="6"/>
       <c r="AN170" s="6"/>
     </row>
-    <row r="171" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
@@ -8996,7 +8996,7 @@
       <c r="AM171" s="6"/>
       <c r="AN171" s="6"/>
     </row>
-    <row r="172" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -9038,7 +9038,7 @@
       <c r="AM172" s="6"/>
       <c r="AN172" s="6"/>
     </row>
-    <row r="173" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
@@ -9080,7 +9080,7 @@
       <c r="AM173" s="6"/>
       <c r="AN173" s="6"/>
     </row>
-    <row r="174" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
@@ -9122,7 +9122,7 @@
       <c r="AM174" s="6"/>
       <c r="AN174" s="6"/>
     </row>
-    <row r="175" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
@@ -9164,7 +9164,7 @@
       <c r="AM175" s="6"/>
       <c r="AN175" s="6"/>
     </row>
-    <row r="176" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
@@ -9206,7 +9206,7 @@
       <c r="AM176" s="6"/>
       <c r="AN176" s="6"/>
     </row>
-    <row r="177" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
@@ -9248,7 +9248,7 @@
       <c r="AM177" s="6"/>
       <c r="AN177" s="6"/>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
@@ -9290,7 +9290,7 @@
       <c r="AM178" s="6"/>
       <c r="AN178" s="6"/>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="12"/>
@@ -9332,7 +9332,7 @@
       <c r="AM179" s="6"/>
       <c r="AN179" s="6"/>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="12"/>
@@ -9374,7 +9374,7 @@
       <c r="AM180" s="6"/>
       <c r="AN180" s="6"/>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="12"/>
@@ -9416,7 +9416,7 @@
       <c r="AM181" s="6"/>
       <c r="AN181" s="6"/>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="12"/>
@@ -9458,7 +9458,7 @@
       <c r="AM182" s="6"/>
       <c r="AN182" s="6"/>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="12"/>
@@ -9500,7 +9500,7 @@
       <c r="AM183" s="6"/>
       <c r="AN183" s="6"/>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="12"/>
@@ -9542,7 +9542,7 @@
       <c r="AM184" s="6"/>
       <c r="AN184" s="6"/>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="12"/>
@@ -9584,7 +9584,7 @@
       <c r="AM185" s="6"/>
       <c r="AN185" s="6"/>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="12"/>
@@ -9626,7 +9626,7 @@
       <c r="AM186" s="6"/>
       <c r="AN186" s="6"/>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="12"/>
@@ -9668,7 +9668,7 @@
       <c r="AM187" s="6"/>
       <c r="AN187" s="6"/>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
@@ -9710,7 +9710,7 @@
       <c r="AM188" s="6"/>
       <c r="AN188" s="6"/>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="12"/>
@@ -9752,7 +9752,7 @@
       <c r="AM189" s="6"/>
       <c r="AN189" s="6"/>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="12"/>
@@ -9794,7 +9794,7 @@
       <c r="AM190" s="6"/>
       <c r="AN190" s="6"/>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="12"/>
@@ -9836,7 +9836,7 @@
       <c r="AM191" s="6"/>
       <c r="AN191" s="6"/>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
@@ -9878,7 +9878,7 @@
       <c r="AM192" s="6"/>
       <c r="AN192" s="6"/>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="12"/>
@@ -9920,7 +9920,7 @@
       <c r="AM193" s="6"/>
       <c r="AN193" s="6"/>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="12"/>
@@ -9962,7 +9962,7 @@
       <c r="AM194" s="6"/>
       <c r="AN194" s="6"/>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="12"/>
@@ -10004,7 +10004,7 @@
       <c r="AM195" s="6"/>
       <c r="AN195" s="6"/>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="12"/>
@@ -10046,7 +10046,7 @@
       <c r="AM196" s="6"/>
       <c r="AN196" s="6"/>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="12"/>
@@ -10088,7 +10088,7 @@
       <c r="AM197" s="6"/>
       <c r="AN197" s="6"/>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="12"/>
@@ -10130,7 +10130,7 @@
       <c r="AM198" s="6"/>
       <c r="AN198" s="6"/>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="12"/>
@@ -10172,7 +10172,7 @@
       <c r="AM199" s="6"/>
       <c r="AN199" s="6"/>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="12"/>
@@ -10214,7 +10214,7 @@
       <c r="AM200" s="6"/>
       <c r="AN200" s="6"/>
     </row>
-    <row r="201" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="12"/>
@@ -10256,7 +10256,7 @@
       <c r="AM201" s="6"/>
       <c r="AN201" s="6"/>
     </row>
-    <row r="202" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="12"/>
@@ -10298,7 +10298,7 @@
       <c r="AM202" s="6"/>
       <c r="AN202" s="6"/>
     </row>
-    <row r="203" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="12"/>
@@ -10340,7 +10340,7 @@
       <c r="AM203" s="6"/>
       <c r="AN203" s="6"/>
     </row>
-    <row r="204" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="12"/>
@@ -10382,7 +10382,7 @@
       <c r="AM204" s="6"/>
       <c r="AN204" s="6"/>
     </row>
-    <row r="205" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="12"/>
@@ -10424,7 +10424,7 @@
       <c r="AM205" s="6"/>
       <c r="AN205" s="6"/>
     </row>
-    <row r="206" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="12"/>
@@ -10466,7 +10466,7 @@
       <c r="AM206" s="6"/>
       <c r="AN206" s="6"/>
     </row>
-    <row r="207" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12"/>
@@ -10508,7 +10508,7 @@
       <c r="AM207" s="6"/>
       <c r="AN207" s="6"/>
     </row>
-    <row r="208" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12"/>
@@ -10550,7 +10550,7 @@
       <c r="AM208" s="6"/>
       <c r="AN208" s="6"/>
     </row>
-    <row r="209" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12"/>
@@ -10592,7 +10592,7 @@
       <c r="AM209" s="6"/>
       <c r="AN209" s="6"/>
     </row>
-    <row r="210" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12"/>
@@ -10634,7 +10634,7 @@
       <c r="AM210" s="6"/>
       <c r="AN210" s="6"/>
     </row>
-    <row r="211" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12"/>
@@ -10676,7 +10676,7 @@
       <c r="AM211" s="6"/>
       <c r="AN211" s="6"/>
     </row>
-    <row r="212" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12"/>
@@ -10718,7 +10718,7 @@
       <c r="AM212" s="6"/>
       <c r="AN212" s="6"/>
     </row>
-    <row r="213" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12"/>
@@ -10760,7 +10760,7 @@
       <c r="AM213" s="6"/>
       <c r="AN213" s="6"/>
     </row>
-    <row r="214" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -10802,7 +10802,7 @@
       <c r="AM214" s="6"/>
       <c r="AN214" s="6"/>
     </row>
-    <row r="215" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="12"/>
@@ -10844,7 +10844,7 @@
       <c r="AM215" s="6"/>
       <c r="AN215" s="6"/>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="12"/>
@@ -10886,7 +10886,7 @@
       <c r="AM216" s="6"/>
       <c r="AN216" s="6"/>
     </row>
-    <row r="217" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="12"/>
@@ -10928,7 +10928,7 @@
       <c r="AM217" s="6"/>
       <c r="AN217" s="6"/>
     </row>
-    <row r="218" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="12"/>
@@ -10970,7 +10970,7 @@
       <c r="AM218" s="6"/>
       <c r="AN218" s="6"/>
     </row>
-    <row r="219" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="12"/>
@@ -11012,7 +11012,7 @@
       <c r="AM219" s="6"/>
       <c r="AN219" s="6"/>
     </row>
-    <row r="220" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="12"/>
@@ -11054,7 +11054,7 @@
       <c r="AM220" s="6"/>
       <c r="AN220" s="6"/>
     </row>
-    <row r="221" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="12"/>
@@ -11096,7 +11096,7 @@
       <c r="AM221" s="6"/>
       <c r="AN221" s="6"/>
     </row>
-    <row r="222" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="12"/>
@@ -11138,7 +11138,7 @@
       <c r="AM222" s="6"/>
       <c r="AN222" s="6"/>
     </row>
-    <row r="223" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="12"/>
@@ -11180,7 +11180,7 @@
       <c r="AM223" s="6"/>
       <c r="AN223" s="6"/>
     </row>
-    <row r="224" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="12"/>
@@ -11222,7 +11222,7 @@
       <c r="AM224" s="6"/>
       <c r="AN224" s="6"/>
     </row>
-    <row r="225" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="12"/>
@@ -11264,7 +11264,7 @@
       <c r="AM225" s="6"/>
       <c r="AN225" s="6"/>
     </row>
-    <row r="226" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="12"/>
@@ -11306,7 +11306,7 @@
       <c r="AM226" s="6"/>
       <c r="AN226" s="6"/>
     </row>
-    <row r="227" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="12"/>
@@ -11348,7 +11348,7 @@
       <c r="AM227" s="6"/>
       <c r="AN227" s="6"/>
     </row>
-    <row r="228" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="12"/>
@@ -11390,7 +11390,7 @@
       <c r="AM228" s="6"/>
       <c r="AN228" s="6"/>
     </row>
-    <row r="229" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="12"/>
@@ -11432,7 +11432,7 @@
       <c r="AM229" s="6"/>
       <c r="AN229" s="6"/>
     </row>
-    <row r="230" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="12"/>
@@ -11474,7 +11474,7 @@
       <c r="AM230" s="6"/>
       <c r="AN230" s="6"/>
     </row>
-    <row r="231" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="12"/>
@@ -11516,7 +11516,7 @@
       <c r="AM231" s="6"/>
       <c r="AN231" s="6"/>
     </row>
-    <row r="232" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="12"/>
@@ -11558,7 +11558,7 @@
       <c r="AM232" s="6"/>
       <c r="AN232" s="6"/>
     </row>
-    <row r="233" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="12"/>
@@ -11600,7 +11600,7 @@
       <c r="AM233" s="6"/>
       <c r="AN233" s="6"/>
     </row>
-    <row r="234" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="12"/>
@@ -11642,7 +11642,7 @@
       <c r="AM234" s="6"/>
       <c r="AN234" s="6"/>
     </row>
-    <row r="235" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="12"/>
@@ -11684,7 +11684,7 @@
       <c r="AM235" s="6"/>
       <c r="AN235" s="6"/>
     </row>
-    <row r="236" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="12"/>
@@ -11726,7 +11726,7 @@
       <c r="AM236" s="6"/>
       <c r="AN236" s="6"/>
     </row>
-    <row r="237" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="12"/>
@@ -11768,7 +11768,7 @@
       <c r="AM237" s="6"/>
       <c r="AN237" s="6"/>
     </row>
-    <row r="238" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="12"/>
@@ -11810,7 +11810,7 @@
       <c r="AM238" s="6"/>
       <c r="AN238" s="6"/>
     </row>
-    <row r="239" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="12"/>
@@ -11852,7 +11852,7 @@
       <c r="AM239" s="6"/>
       <c r="AN239" s="6"/>
     </row>
-    <row r="240" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="12"/>
@@ -11894,7 +11894,7 @@
       <c r="AM240" s="6"/>
       <c r="AN240" s="6"/>
     </row>
-    <row r="241" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
@@ -11936,7 +11936,7 @@
       <c r="AM241" s="6"/>
       <c r="AN241" s="6"/>
     </row>
-    <row r="242" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="12"/>
@@ -11978,7 +11978,7 @@
       <c r="AM242" s="6"/>
       <c r="AN242" s="6"/>
     </row>
-    <row r="243" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="12"/>
@@ -12020,7 +12020,7 @@
       <c r="AM243" s="6"/>
       <c r="AN243" s="6"/>
     </row>
-    <row r="244" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="12"/>
@@ -12062,7 +12062,7 @@
       <c r="AM244" s="6"/>
       <c r="AN244" s="6"/>
     </row>
-    <row r="245" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="12"/>
@@ -12104,7 +12104,7 @@
       <c r="AM245" s="6"/>
       <c r="AN245" s="6"/>
     </row>
-    <row r="246" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="12"/>
@@ -12146,7 +12146,7 @@
       <c r="AM246" s="6"/>
       <c r="AN246" s="6"/>
     </row>
-    <row r="247" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="12"/>
@@ -12188,7 +12188,7 @@
       <c r="AM247" s="6"/>
       <c r="AN247" s="6"/>
     </row>
-    <row r="248" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="12"/>
@@ -12230,7 +12230,7 @@
       <c r="AM248" s="6"/>
       <c r="AN248" s="6"/>
     </row>
-    <row r="249" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="12"/>
@@ -12272,7 +12272,7 @@
       <c r="AM249" s="6"/>
       <c r="AN249" s="6"/>
     </row>
-    <row r="250" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="12"/>
@@ -12314,7 +12314,7 @@
       <c r="AM250" s="6"/>
       <c r="AN250" s="6"/>
     </row>
-    <row r="251" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="12"/>
@@ -12356,7 +12356,7 @@
       <c r="AM251" s="6"/>
       <c r="AN251" s="6"/>
     </row>
-    <row r="252" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="12"/>
@@ -12398,7 +12398,7 @@
       <c r="AM252" s="6"/>
       <c r="AN252" s="6"/>
     </row>
-    <row r="253" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="12"/>
@@ -12440,7 +12440,7 @@
       <c r="AM253" s="6"/>
       <c r="AN253" s="6"/>
     </row>
-    <row r="254" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="12"/>
@@ -12482,7 +12482,7 @@
       <c r="AM254" s="6"/>
       <c r="AN254" s="6"/>
     </row>
-    <row r="255" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -12524,7 +12524,7 @@
       <c r="AM255" s="6"/>
       <c r="AN255" s="6"/>
     </row>
-    <row r="256" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="12"/>
@@ -12566,7 +12566,7 @@
       <c r="AM256" s="6"/>
       <c r="AN256" s="6"/>
     </row>
-    <row r="257" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="12"/>
@@ -12608,7 +12608,7 @@
       <c r="AM257" s="6"/>
       <c r="AN257" s="6"/>
     </row>
-    <row r="258" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
@@ -12650,7 +12650,7 @@
       <c r="AM258" s="6"/>
       <c r="AN258" s="6"/>
     </row>
-    <row r="259" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
@@ -12692,7 +12692,7 @@
       <c r="AM259" s="6"/>
       <c r="AN259" s="6"/>
     </row>
-    <row r="260" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
@@ -12734,7 +12734,7 @@
       <c r="AM260" s="6"/>
       <c r="AN260" s="6"/>
     </row>
-    <row r="261" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
@@ -12776,7 +12776,7 @@
       <c r="AM261" s="6"/>
       <c r="AN261" s="6"/>
     </row>
-    <row r="262" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
@@ -12818,7 +12818,7 @@
       <c r="AM262" s="6"/>
       <c r="AN262" s="6"/>
     </row>
-    <row r="263" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -12860,7 +12860,7 @@
       <c r="AM263" s="6"/>
       <c r="AN263" s="6"/>
     </row>
-    <row r="264" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="12"/>
@@ -12902,7 +12902,7 @@
       <c r="AM264" s="6"/>
       <c r="AN264" s="6"/>
     </row>
-    <row r="265" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="12"/>
@@ -12944,7 +12944,7 @@
       <c r="AM265" s="6"/>
       <c r="AN265" s="6"/>
     </row>
-    <row r="266" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="12"/>
@@ -12986,7 +12986,7 @@
       <c r="AM266" s="6"/>
       <c r="AN266" s="6"/>
     </row>
-    <row r="267" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="12"/>
@@ -13028,7 +13028,7 @@
       <c r="AM267" s="6"/>
       <c r="AN267" s="6"/>
     </row>
-    <row r="268" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
@@ -13070,7 +13070,7 @@
       <c r="AM268" s="6"/>
       <c r="AN268" s="6"/>
     </row>
-    <row r="269" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="12"/>
@@ -13112,7 +13112,7 @@
       <c r="AM269" s="6"/>
       <c r="AN269" s="6"/>
     </row>
-    <row r="270" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A270" s="12"/>
       <c r="B270" s="12"/>
       <c r="C270" s="12"/>
@@ -13154,7 +13154,7 @@
       <c r="AM270" s="6"/>
       <c r="AN270" s="6"/>
     </row>
-    <row r="271" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A271" s="12"/>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
@@ -13196,7 +13196,7 @@
       <c r="AM271" s="6"/>
       <c r="AN271" s="6"/>
     </row>
-    <row r="272" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A272" s="12"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
@@ -13238,7 +13238,7 @@
       <c r="AM272" s="6"/>
       <c r="AN272" s="6"/>
     </row>
-    <row r="273" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A273" s="12"/>
       <c r="B273" s="12"/>
       <c r="C273" s="12"/>
@@ -13280,7 +13280,7 @@
       <c r="AM273" s="6"/>
       <c r="AN273" s="6"/>
     </row>
-    <row r="274" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -13322,7 +13322,7 @@
       <c r="AM274" s="6"/>
       <c r="AN274" s="6"/>
     </row>
-    <row r="275" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -13364,7 +13364,7 @@
       <c r="AM275" s="6"/>
       <c r="AN275" s="6"/>
     </row>
-    <row r="276" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -13406,7 +13406,7 @@
       <c r="AM276" s="6"/>
       <c r="AN276" s="6"/>
     </row>
-    <row r="277" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -13448,7 +13448,7 @@
       <c r="AM277" s="6"/>
       <c r="AN277" s="6"/>
     </row>
-    <row r="278" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -13490,7 +13490,7 @@
       <c r="AM278" s="6"/>
       <c r="AN278" s="6"/>
     </row>
-    <row r="279" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12"/>
@@ -13532,7 +13532,7 @@
       <c r="AM279" s="6"/>
       <c r="AN279" s="6"/>
     </row>
-    <row r="280" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -13574,7 +13574,7 @@
       <c r="AM280" s="6"/>
       <c r="AN280" s="6"/>
     </row>
-    <row r="281" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -13616,7 +13616,7 @@
       <c r="AM281" s="6"/>
       <c r="AN281" s="6"/>
     </row>
-    <row r="282" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -13658,7 +13658,7 @@
       <c r="AM282" s="6"/>
       <c r="AN282" s="6"/>
     </row>
-    <row r="283" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -13700,7 +13700,7 @@
       <c r="AM283" s="6"/>
       <c r="AN283" s="6"/>
     </row>
-    <row r="284" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -13742,7 +13742,7 @@
       <c r="AM284" s="6"/>
       <c r="AN284" s="6"/>
     </row>
-    <row r="285" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A285" s="12"/>
       <c r="B285" s="12"/>
       <c r="C285" s="12"/>
@@ -13784,7 +13784,7 @@
       <c r="AM285" s="6"/>
       <c r="AN285" s="6"/>
     </row>
-    <row r="286" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A286" s="12"/>
       <c r="B286" s="12"/>
       <c r="C286" s="12"/>
@@ -13826,7 +13826,7 @@
       <c r="AM286" s="6"/>
       <c r="AN286" s="6"/>
     </row>
-    <row r="287" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A287" s="12"/>
       <c r="B287" s="12"/>
       <c r="C287" s="12"/>
@@ -13868,7 +13868,7 @@
       <c r="AM287" s="6"/>
       <c r="AN287" s="6"/>
     </row>
-    <row r="288" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A288" s="12"/>
       <c r="B288" s="12"/>
       <c r="C288" s="12"/>
@@ -13910,7 +13910,7 @@
       <c r="AM288" s="6"/>
       <c r="AN288" s="6"/>
     </row>
-    <row r="289" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A289" s="12"/>
       <c r="B289" s="12"/>
       <c r="C289" s="12"/>
@@ -13952,7 +13952,7 @@
       <c r="AM289" s="6"/>
       <c r="AN289" s="6"/>
     </row>
-    <row r="290" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A290" s="12"/>
       <c r="B290" s="12"/>
       <c r="C290" s="12"/>
@@ -13994,7 +13994,7 @@
       <c r="AM290" s="6"/>
       <c r="AN290" s="6"/>
     </row>
-    <row r="291" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A291" s="12"/>
       <c r="B291" s="12"/>
       <c r="C291" s="12"/>
@@ -14036,7 +14036,7 @@
       <c r="AM291" s="6"/>
       <c r="AN291" s="6"/>
     </row>
-    <row r="292" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A292" s="12"/>
       <c r="B292" s="12"/>
       <c r="C292" s="12"/>
@@ -14078,7 +14078,7 @@
       <c r="AM292" s="6"/>
       <c r="AN292" s="6"/>
     </row>
-    <row r="293" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A293" s="12"/>
       <c r="B293" s="12"/>
       <c r="C293" s="12"/>
@@ -14120,7 +14120,7 @@
       <c r="AM293" s="6"/>
       <c r="AN293" s="6"/>
     </row>
-    <row r="294" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A294" s="12"/>
       <c r="B294" s="12"/>
       <c r="C294" s="12"/>
@@ -14162,7 +14162,7 @@
       <c r="AM294" s="6"/>
       <c r="AN294" s="6"/>
     </row>
-    <row r="295" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
       <c r="B295" s="12"/>
       <c r="C295" s="12"/>
@@ -14204,7 +14204,7 @@
       <c r="AM295" s="6"/>
       <c r="AN295" s="6"/>
     </row>
-    <row r="296" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12"/>
@@ -14246,7 +14246,7 @@
       <c r="AM296" s="6"/>
       <c r="AN296" s="6"/>
     </row>
-    <row r="297" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12"/>
@@ -14288,7 +14288,7 @@
       <c r="AM297" s="6"/>
       <c r="AN297" s="6"/>
     </row>
-    <row r="298" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
       <c r="B298" s="12"/>
       <c r="C298" s="12"/>
@@ -14330,7 +14330,7 @@
       <c r="AM298" s="6"/>
       <c r="AN298" s="6"/>
     </row>
-    <row r="299" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12"/>
@@ -14372,7 +14372,7 @@
       <c r="AM299" s="6"/>
       <c r="AN299" s="6"/>
     </row>
-    <row r="300" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12"/>
@@ -14414,7 +14414,7 @@
       <c r="AM300" s="6"/>
       <c r="AN300" s="6"/>
     </row>
-    <row r="301" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A301" s="12"/>
       <c r="B301" s="12"/>
       <c r="C301" s="12"/>
@@ -14456,7 +14456,7 @@
       <c r="AM301" s="6"/>
       <c r="AN301" s="6"/>
     </row>
-    <row r="302" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A302" s="12"/>
       <c r="B302" s="12"/>
       <c r="C302" s="12"/>
@@ -14498,7 +14498,7 @@
       <c r="AM302" s="6"/>
       <c r="AN302" s="6"/>
     </row>
-    <row r="303" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A303" s="12"/>
       <c r="B303" s="12"/>
       <c r="C303" s="12"/>
@@ -14540,7 +14540,7 @@
       <c r="AM303" s="6"/>
       <c r="AN303" s="6"/>
     </row>
-    <row r="304" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A304" s="12"/>
       <c r="B304" s="12"/>
       <c r="C304" s="12"/>
@@ -14582,7 +14582,7 @@
       <c r="AM304" s="6"/>
       <c r="AN304" s="6"/>
     </row>
-    <row r="305" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A305" s="12"/>
       <c r="B305" s="12"/>
       <c r="C305" s="12"/>
@@ -14624,7 +14624,7 @@
       <c r="AM305" s="6"/>
       <c r="AN305" s="6"/>
     </row>
-    <row r="306" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A306" s="12"/>
       <c r="B306" s="12"/>
       <c r="C306" s="12"/>
@@ -14666,7 +14666,7 @@
       <c r="AM306" s="6"/>
       <c r="AN306" s="6"/>
     </row>
-    <row r="307" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A307" s="12"/>
       <c r="B307" s="12"/>
       <c r="C307" s="12"/>
@@ -14708,7 +14708,7 @@
       <c r="AM307" s="6"/>
       <c r="AN307" s="6"/>
     </row>
-    <row r="308" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A308" s="12"/>
       <c r="B308" s="12"/>
       <c r="C308" s="12"/>
@@ -14750,7 +14750,7 @@
       <c r="AM308" s="6"/>
       <c r="AN308" s="6"/>
     </row>
-    <row r="309" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A309" s="12"/>
       <c r="B309" s="12"/>
       <c r="C309" s="12"/>
@@ -14792,7 +14792,7 @@
       <c r="AM309" s="6"/>
       <c r="AN309" s="6"/>
     </row>
-    <row r="310" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A310" s="12"/>
       <c r="B310" s="12"/>
       <c r="C310" s="12"/>
@@ -14834,7 +14834,7 @@
       <c r="AM310" s="6"/>
       <c r="AN310" s="6"/>
     </row>
-    <row r="311" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -14876,7 +14876,7 @@
       <c r="AM311" s="6"/>
       <c r="AN311" s="6"/>
     </row>
-    <row r="312" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A312" s="12"/>
       <c r="B312" s="12"/>
       <c r="C312" s="12"/>
@@ -14918,7 +14918,7 @@
       <c r="AM312" s="6"/>
       <c r="AN312" s="6"/>
     </row>
-    <row r="313" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A313" s="12"/>
       <c r="B313" s="12"/>
       <c r="C313" s="12"/>
@@ -14960,7 +14960,7 @@
       <c r="AM313" s="6"/>
       <c r="AN313" s="6"/>
     </row>
-    <row r="314" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A314" s="12"/>
       <c r="B314" s="12"/>
       <c r="C314" s="12"/>
@@ -15002,7 +15002,7 @@
       <c r="AM314" s="6"/>
       <c r="AN314" s="6"/>
     </row>
-    <row r="315" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A315" s="12"/>
       <c r="B315" s="12"/>
       <c r="C315" s="12"/>
@@ -15044,7 +15044,7 @@
       <c r="AM315" s="6"/>
       <c r="AN315" s="6"/>
     </row>
-    <row r="316" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A316" s="12"/>
       <c r="B316" s="12"/>
       <c r="C316" s="12"/>
@@ -15086,7 +15086,7 @@
       <c r="AM316" s="6"/>
       <c r="AN316" s="6"/>
     </row>
-    <row r="317" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A317" s="12"/>
       <c r="B317" s="12"/>
       <c r="C317" s="12"/>
@@ -15128,7 +15128,7 @@
       <c r="AM317" s="6"/>
       <c r="AN317" s="6"/>
     </row>
-    <row r="318" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A318" s="12"/>
       <c r="B318" s="12"/>
       <c r="C318" s="12"/>
@@ -15170,7 +15170,7 @@
       <c r="AM318" s="6"/>
       <c r="AN318" s="6"/>
     </row>
-    <row r="319" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A319" s="12"/>
       <c r="B319" s="12"/>
       <c r="C319" s="12"/>
@@ -15212,7 +15212,7 @@
       <c r="AM319" s="6"/>
       <c r="AN319" s="6"/>
     </row>
-    <row r="320" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A320" s="12"/>
       <c r="B320" s="12"/>
       <c r="C320" s="12"/>
@@ -15254,7 +15254,7 @@
       <c r="AM320" s="6"/>
       <c r="AN320" s="6"/>
     </row>
-    <row r="321" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A321" s="12"/>
       <c r="B321" s="12"/>
       <c r="C321" s="12"/>
@@ -15296,7 +15296,7 @@
       <c r="AM321" s="6"/>
       <c r="AN321" s="6"/>
     </row>
-    <row r="322" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A322" s="12"/>
       <c r="B322" s="12"/>
       <c r="C322" s="12"/>
@@ -15338,7 +15338,7 @@
       <c r="AM322" s="6"/>
       <c r="AN322" s="6"/>
     </row>
-    <row r="323" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A323" s="12"/>
       <c r="B323" s="12"/>
       <c r="C323" s="12"/>
@@ -15380,7 +15380,7 @@
       <c r="AM323" s="6"/>
       <c r="AN323" s="6"/>
     </row>
-    <row r="324" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A324" s="12"/>
       <c r="B324" s="12"/>
       <c r="C324" s="12"/>
@@ -15422,7 +15422,7 @@
       <c r="AM324" s="6"/>
       <c r="AN324" s="6"/>
     </row>
-    <row r="325" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A325" s="12"/>
       <c r="B325" s="12"/>
       <c r="C325" s="12"/>
@@ -15464,7 +15464,7 @@
       <c r="AM325" s="6"/>
       <c r="AN325" s="6"/>
     </row>
-    <row r="326" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A326" s="12"/>
       <c r="B326" s="12"/>
       <c r="C326" s="12"/>
@@ -15506,7 +15506,7 @@
       <c r="AM326" s="6"/>
       <c r="AN326" s="6"/>
     </row>
-    <row r="327" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A327" s="12"/>
       <c r="B327" s="12"/>
       <c r="C327" s="12"/>
@@ -15548,7 +15548,7 @@
       <c r="AM327" s="6"/>
       <c r="AN327" s="6"/>
     </row>
-    <row r="328" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A328" s="12"/>
       <c r="B328" s="12"/>
       <c r="C328" s="12"/>
@@ -15590,7 +15590,7 @@
       <c r="AM328" s="6"/>
       <c r="AN328" s="6"/>
     </row>
-    <row r="329" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A329" s="12"/>
       <c r="B329" s="12"/>
       <c r="C329" s="12"/>
@@ -15632,7 +15632,7 @@
       <c r="AM329" s="6"/>
       <c r="AN329" s="6"/>
     </row>
-    <row r="330" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A330" s="12"/>
       <c r="B330" s="12"/>
       <c r="C330" s="12"/>
@@ -15674,7 +15674,7 @@
       <c r="AM330" s="6"/>
       <c r="AN330" s="6"/>
     </row>
-    <row r="331" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A331" s="12"/>
       <c r="B331" s="12"/>
       <c r="C331" s="12"/>
@@ -15716,7 +15716,7 @@
       <c r="AM331" s="6"/>
       <c r="AN331" s="6"/>
     </row>
-    <row r="332" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A332" s="12"/>
       <c r="B332" s="12"/>
       <c r="C332" s="12"/>
@@ -15758,7 +15758,7 @@
       <c r="AM332" s="6"/>
       <c r="AN332" s="6"/>
     </row>
-    <row r="333" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A333" s="12"/>
       <c r="B333" s="12"/>
       <c r="C333" s="12"/>
@@ -15800,7 +15800,7 @@
       <c r="AM333" s="6"/>
       <c r="AN333" s="6"/>
     </row>
-    <row r="334" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A334" s="12"/>
       <c r="B334" s="12"/>
       <c r="C334" s="12"/>
@@ -15842,7 +15842,7 @@
       <c r="AM334" s="6"/>
       <c r="AN334" s="6"/>
     </row>
-    <row r="335" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A335" s="12"/>
       <c r="B335" s="12"/>
       <c r="C335" s="12"/>
@@ -15884,7 +15884,7 @@
       <c r="AM335" s="6"/>
       <c r="AN335" s="6"/>
     </row>
-    <row r="336" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A336" s="12"/>
       <c r="B336" s="12"/>
       <c r="C336" s="12"/>
@@ -15926,7 +15926,7 @@
       <c r="AM336" s="6"/>
       <c r="AN336" s="6"/>
     </row>
-    <row r="337" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A337" s="12"/>
       <c r="B337" s="12"/>
       <c r="C337" s="12"/>
@@ -15968,7 +15968,7 @@
       <c r="AM337" s="6"/>
       <c r="AN337" s="6"/>
     </row>
-    <row r="338" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A338" s="12"/>
       <c r="B338" s="12"/>
       <c r="C338" s="12"/>
@@ -16010,7 +16010,7 @@
       <c r="AM338" s="6"/>
       <c r="AN338" s="6"/>
     </row>
-    <row r="339" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A339" s="12"/>
       <c r="B339" s="12"/>
       <c r="C339" s="12"/>
@@ -16052,7 +16052,7 @@
       <c r="AM339" s="6"/>
       <c r="AN339" s="6"/>
     </row>
-    <row r="340" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A340" s="12"/>
       <c r="B340" s="12"/>
       <c r="C340" s="12"/>
@@ -16094,7 +16094,7 @@
       <c r="AM340" s="6"/>
       <c r="AN340" s="6"/>
     </row>
-    <row r="341" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A341" s="12"/>
       <c r="B341" s="12"/>
       <c r="C341" s="12"/>
@@ -16136,7 +16136,7 @@
       <c r="AM341" s="6"/>
       <c r="AN341" s="6"/>
     </row>
-    <row r="342" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A342" s="12"/>
       <c r="B342" s="12"/>
       <c r="C342" s="12"/>
@@ -16178,7 +16178,7 @@
       <c r="AM342" s="6"/>
       <c r="AN342" s="6"/>
     </row>
-    <row r="343" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A343" s="12"/>
       <c r="B343" s="12"/>
       <c r="C343" s="12"/>
@@ -16220,7 +16220,7 @@
       <c r="AM343" s="6"/>
       <c r="AN343" s="6"/>
     </row>
-    <row r="344" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A344" s="12"/>
       <c r="B344" s="12"/>
       <c r="C344" s="12"/>
@@ -16262,7 +16262,7 @@
       <c r="AM344" s="6"/>
       <c r="AN344" s="6"/>
     </row>
-    <row r="345" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A345" s="12"/>
       <c r="B345" s="12"/>
       <c r="C345" s="12"/>
@@ -16304,7 +16304,7 @@
       <c r="AM345" s="6"/>
       <c r="AN345" s="6"/>
     </row>
-    <row r="346" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A346" s="12"/>
       <c r="B346" s="12"/>
       <c r="C346" s="12"/>
@@ -16346,7 +16346,7 @@
       <c r="AM346" s="6"/>
       <c r="AN346" s="6"/>
     </row>
-    <row r="347" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A347" s="12"/>
       <c r="B347" s="12"/>
       <c r="C347" s="12"/>
@@ -16388,7 +16388,7 @@
       <c r="AM347" s="6"/>
       <c r="AN347" s="6"/>
     </row>
-    <row r="348" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A348" s="12"/>
       <c r="B348" s="12"/>
       <c r="C348" s="12"/>
@@ -16430,7 +16430,7 @@
       <c r="AM348" s="6"/>
       <c r="AN348" s="6"/>
     </row>
-    <row r="349" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A349" s="12"/>
       <c r="B349" s="12"/>
       <c r="C349" s="12"/>
@@ -16472,7 +16472,7 @@
       <c r="AM349" s="6"/>
       <c r="AN349" s="6"/>
     </row>
-    <row r="350" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A350" s="12"/>
       <c r="B350" s="12"/>
       <c r="C350" s="12"/>
@@ -16514,7 +16514,7 @@
       <c r="AM350" s="6"/>
       <c r="AN350" s="6"/>
     </row>
-    <row r="351" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A351" s="12"/>
       <c r="B351" s="12"/>
       <c r="C351" s="12"/>
@@ -16556,7 +16556,7 @@
       <c r="AM351" s="6"/>
       <c r="AN351" s="6"/>
     </row>
-    <row r="352" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A352" s="12"/>
       <c r="B352" s="12"/>
       <c r="C352" s="12"/>
@@ -16598,7 +16598,7 @@
       <c r="AM352" s="6"/>
       <c r="AN352" s="6"/>
     </row>
-    <row r="353" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A353" s="12"/>
       <c r="B353" s="12"/>
       <c r="C353" s="12"/>
@@ -16640,7 +16640,7 @@
       <c r="AM353" s="6"/>
       <c r="AN353" s="6"/>
     </row>
-    <row r="354" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A354" s="12"/>
       <c r="B354" s="12"/>
       <c r="C354" s="12"/>
@@ -16682,7 +16682,7 @@
       <c r="AM354" s="6"/>
       <c r="AN354" s="6"/>
     </row>
-    <row r="355" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A355" s="12"/>
       <c r="B355" s="12"/>
       <c r="C355" s="12"/>
@@ -16724,7 +16724,7 @@
       <c r="AM355" s="6"/>
       <c r="AN355" s="6"/>
     </row>
-    <row r="356" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A356" s="12"/>
       <c r="B356" s="12"/>
       <c r="C356" s="12"/>
@@ -16766,7 +16766,7 @@
       <c r="AM356" s="6"/>
       <c r="AN356" s="6"/>
     </row>
-    <row r="357" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A357" s="12"/>
       <c r="B357" s="12"/>
       <c r="C357" s="12"/>
@@ -16808,7 +16808,7 @@
       <c r="AM357" s="6"/>
       <c r="AN357" s="6"/>
     </row>
-    <row r="358" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A358" s="12"/>
       <c r="B358" s="12"/>
       <c r="C358" s="12"/>
@@ -16850,7 +16850,7 @@
       <c r="AM358" s="6"/>
       <c r="AN358" s="6"/>
     </row>
-    <row r="359" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A359" s="12"/>
       <c r="B359" s="12"/>
       <c r="C359" s="12"/>
@@ -16892,7 +16892,7 @@
       <c r="AM359" s="6"/>
       <c r="AN359" s="6"/>
     </row>
-    <row r="360" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A360" s="12"/>
       <c r="B360" s="12"/>
       <c r="C360" s="12"/>
@@ -16934,7 +16934,7 @@
       <c r="AM360" s="6"/>
       <c r="AN360" s="6"/>
     </row>
-    <row r="361" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A361" s="12"/>
       <c r="B361" s="12"/>
       <c r="C361" s="12"/>
@@ -16976,7 +16976,7 @@
       <c r="AM361" s="6"/>
       <c r="AN361" s="6"/>
     </row>
-    <row r="362" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A362" s="12"/>
       <c r="B362" s="12"/>
       <c r="C362" s="12"/>
@@ -17018,7 +17018,7 @@
       <c r="AM362" s="6"/>
       <c r="AN362" s="6"/>
     </row>
-    <row r="363" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A363" s="12"/>
       <c r="B363" s="12"/>
       <c r="C363" s="12"/>
@@ -17060,7 +17060,7 @@
       <c r="AM363" s="6"/>
       <c r="AN363" s="6"/>
     </row>
-    <row r="364" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A364" s="12"/>
       <c r="B364" s="12"/>
       <c r="C364" s="12"/>
@@ -17102,7 +17102,7 @@
       <c r="AM364" s="6"/>
       <c r="AN364" s="6"/>
     </row>
-    <row r="365" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A365" s="12"/>
       <c r="B365" s="12"/>
       <c r="C365" s="12"/>
@@ -17144,7 +17144,7 @@
       <c r="AM365" s="6"/>
       <c r="AN365" s="6"/>
     </row>
-    <row r="366" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A366" s="12"/>
       <c r="B366" s="12"/>
       <c r="C366" s="12"/>
@@ -17186,7 +17186,7 @@
       <c r="AM366" s="6"/>
       <c r="AN366" s="6"/>
     </row>
-    <row r="367" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A367" s="12"/>
       <c r="B367" s="12"/>
       <c r="C367" s="12"/>
@@ -17228,7 +17228,7 @@
       <c r="AM367" s="6"/>
       <c r="AN367" s="6"/>
     </row>
-    <row r="368" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A368" s="12"/>
       <c r="B368" s="12"/>
       <c r="C368" s="12"/>
@@ -17270,7 +17270,7 @@
       <c r="AM368" s="6"/>
       <c r="AN368" s="6"/>
     </row>
-    <row r="369" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A369" s="12"/>
       <c r="B369" s="12"/>
       <c r="C369" s="12"/>
@@ -17312,7 +17312,7 @@
       <c r="AM369" s="6"/>
       <c r="AN369" s="6"/>
     </row>
-    <row r="370" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A370" s="12"/>
       <c r="B370" s="12"/>
       <c r="C370" s="12"/>
@@ -17354,7 +17354,7 @@
       <c r="AM370" s="6"/>
       <c r="AN370" s="6"/>
     </row>
-    <row r="371" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A371" s="12"/>
       <c r="B371" s="12"/>
       <c r="C371" s="12"/>
@@ -17396,7 +17396,7 @@
       <c r="AM371" s="6"/>
       <c r="AN371" s="6"/>
     </row>
-    <row r="372" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A372" s="12"/>
       <c r="B372" s="12"/>
       <c r="C372" s="12"/>
@@ -17438,7 +17438,7 @@
       <c r="AM372" s="6"/>
       <c r="AN372" s="6"/>
     </row>
-    <row r="373" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A373" s="12"/>
       <c r="B373" s="12"/>
       <c r="C373" s="12"/>
@@ -17480,7 +17480,7 @@
       <c r="AM373" s="6"/>
       <c r="AN373" s="6"/>
     </row>
-    <row r="374" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A374" s="12"/>
       <c r="B374" s="12"/>
       <c r="C374" s="12"/>
@@ -17522,7 +17522,7 @@
       <c r="AM374" s="6"/>
       <c r="AN374" s="6"/>
     </row>
-    <row r="375" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A375" s="12"/>
       <c r="B375" s="12"/>
       <c r="C375" s="12"/>
@@ -17564,7 +17564,7 @@
       <c r="AM375" s="6"/>
       <c r="AN375" s="6"/>
     </row>
-    <row r="376" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A376" s="12"/>
       <c r="B376" s="12"/>
       <c r="C376" s="12"/>
@@ -17606,7 +17606,7 @@
       <c r="AM376" s="6"/>
       <c r="AN376" s="6"/>
     </row>
-    <row r="377" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A377" s="12"/>
       <c r="B377" s="12"/>
       <c r="C377" s="12"/>
@@ -17648,7 +17648,7 @@
       <c r="AM377" s="6"/>
       <c r="AN377" s="6"/>
     </row>
-    <row r="378" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A378" s="12"/>
       <c r="B378" s="12"/>
       <c r="C378" s="12"/>
@@ -17690,7 +17690,7 @@
       <c r="AM378" s="6"/>
       <c r="AN378" s="6"/>
     </row>
-    <row r="379" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A379" s="12"/>
       <c r="B379" s="12"/>
       <c r="C379" s="12"/>
@@ -17732,7 +17732,7 @@
       <c r="AM379" s="6"/>
       <c r="AN379" s="6"/>
     </row>
-    <row r="380" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A380" s="12"/>
       <c r="B380" s="12"/>
       <c r="C380" s="12"/>
@@ -17774,7 +17774,7 @@
       <c r="AM380" s="6"/>
       <c r="AN380" s="6"/>
     </row>
-    <row r="381" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A381" s="12"/>
       <c r="B381" s="12"/>
       <c r="C381" s="12"/>
@@ -17816,7 +17816,7 @@
       <c r="AM381" s="6"/>
       <c r="AN381" s="6"/>
     </row>
-    <row r="382" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A382" s="12"/>
       <c r="B382" s="12"/>
       <c r="C382" s="12"/>
@@ -17858,7 +17858,7 @@
       <c r="AM382" s="6"/>
       <c r="AN382" s="6"/>
     </row>
-    <row r="383" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A383" s="12"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12"/>
@@ -17900,7 +17900,7 @@
       <c r="AM383" s="6"/>
       <c r="AN383" s="6"/>
     </row>
-    <row r="384" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A384" s="12"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12"/>
@@ -17942,7 +17942,7 @@
       <c r="AM384" s="6"/>
       <c r="AN384" s="6"/>
     </row>
-    <row r="385" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A385" s="12"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12"/>
@@ -17984,7 +17984,7 @@
       <c r="AM385" s="6"/>
       <c r="AN385" s="6"/>
     </row>
-    <row r="386" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A386" s="12"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12"/>
@@ -18026,7 +18026,7 @@
       <c r="AM386" s="6"/>
       <c r="AN386" s="6"/>
     </row>
-    <row r="387" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A387" s="12"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12"/>
@@ -18068,7 +18068,7 @@
       <c r="AM387" s="6"/>
       <c r="AN387" s="6"/>
     </row>
-    <row r="388" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A388" s="12"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12"/>
@@ -18110,7 +18110,7 @@
       <c r="AM388" s="6"/>
       <c r="AN388" s="6"/>
     </row>
-    <row r="389" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A389" s="12"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12"/>
@@ -18152,7 +18152,7 @@
       <c r="AM389" s="6"/>
       <c r="AN389" s="6"/>
     </row>
-    <row r="390" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A390" s="12"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -18194,7 +18194,7 @@
       <c r="AM390" s="6"/>
       <c r="AN390" s="6"/>
     </row>
-    <row r="391" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A391" s="12"/>
       <c r="B391" s="12"/>
       <c r="C391" s="12"/>
@@ -18236,7 +18236,7 @@
       <c r="AM391" s="6"/>
       <c r="AN391" s="6"/>
     </row>
-    <row r="392" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A392" s="12"/>
       <c r="B392" s="12"/>
       <c r="C392" s="12"/>
@@ -18278,7 +18278,7 @@
       <c r="AM392" s="6"/>
       <c r="AN392" s="6"/>
     </row>
-    <row r="393" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A393" s="12"/>
       <c r="B393" s="12"/>
       <c r="C393" s="12"/>
@@ -18320,7 +18320,7 @@
       <c r="AM393" s="6"/>
       <c r="AN393" s="6"/>
     </row>
-    <row r="394" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A394" s="12"/>
       <c r="B394" s="12"/>
       <c r="C394" s="12"/>
@@ -18362,7 +18362,7 @@
       <c r="AM394" s="6"/>
       <c r="AN394" s="6"/>
     </row>
-    <row r="395" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A395" s="12"/>
       <c r="B395" s="12"/>
       <c r="C395" s="12"/>
@@ -18404,7 +18404,7 @@
       <c r="AM395" s="6"/>
       <c r="AN395" s="6"/>
     </row>
-    <row r="396" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A396" s="12"/>
       <c r="B396" s="12"/>
       <c r="C396" s="12"/>
@@ -18446,7 +18446,7 @@
       <c r="AM396" s="6"/>
       <c r="AN396" s="6"/>
     </row>
-    <row r="397" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A397" s="12"/>
       <c r="B397" s="12"/>
       <c r="C397" s="12"/>
@@ -18488,7 +18488,7 @@
       <c r="AM397" s="6"/>
       <c r="AN397" s="6"/>
     </row>
-    <row r="398" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A398" s="12"/>
       <c r="B398" s="12"/>
       <c r="C398" s="12"/>
@@ -18530,7 +18530,7 @@
       <c r="AM398" s="6"/>
       <c r="AN398" s="6"/>
     </row>
-    <row r="399" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A399" s="12"/>
       <c r="B399" s="12"/>
       <c r="C399" s="12"/>
@@ -18572,7 +18572,7 @@
       <c r="AM399" s="6"/>
       <c r="AN399" s="6"/>
     </row>
-    <row r="400" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A400" s="12"/>
       <c r="B400" s="12"/>
       <c r="C400" s="12"/>
@@ -18614,7 +18614,7 @@
       <c r="AM400" s="6"/>
       <c r="AN400" s="6"/>
     </row>
-    <row r="401" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A401" s="12"/>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
@@ -18656,7 +18656,7 @@
       <c r="AM401" s="6"/>
       <c r="AN401" s="6"/>
     </row>
-    <row r="402" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A402" s="12"/>
       <c r="B402" s="12"/>
       <c r="C402" s="12"/>
@@ -18698,7 +18698,7 @@
       <c r="AM402" s="6"/>
       <c r="AN402" s="6"/>
     </row>
-    <row r="403" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A403" s="12"/>
       <c r="B403" s="12"/>
       <c r="C403" s="12"/>
@@ -18740,7 +18740,7 @@
       <c r="AM403" s="6"/>
       <c r="AN403" s="6"/>
     </row>
-    <row r="404" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A404" s="12"/>
       <c r="B404" s="12"/>
       <c r="C404" s="12"/>
@@ -18782,7 +18782,7 @@
       <c r="AM404" s="6"/>
       <c r="AN404" s="6"/>
     </row>
-    <row r="405" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A405" s="12"/>
       <c r="B405" s="12"/>
       <c r="C405" s="12"/>
@@ -18824,7 +18824,7 @@
       <c r="AM405" s="6"/>
       <c r="AN405" s="6"/>
     </row>
-    <row r="406" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A406" s="12"/>
       <c r="B406" s="12"/>
       <c r="C406" s="12"/>
@@ -18866,7 +18866,7 @@
       <c r="AM406" s="6"/>
       <c r="AN406" s="6"/>
     </row>
-    <row r="407" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A407" s="12"/>
       <c r="B407" s="12"/>
       <c r="C407" s="12"/>
@@ -18908,7 +18908,7 @@
       <c r="AM407" s="6"/>
       <c r="AN407" s="6"/>
     </row>
-    <row r="408" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A408" s="12"/>
       <c r="B408" s="12"/>
       <c r="C408" s="12"/>
@@ -18950,7 +18950,7 @@
       <c r="AM408" s="6"/>
       <c r="AN408" s="6"/>
     </row>
-    <row r="409" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A409" s="12"/>
       <c r="B409" s="12"/>
       <c r="C409" s="12"/>
@@ -18992,7 +18992,7 @@
       <c r="AM409" s="6"/>
       <c r="AN409" s="6"/>
     </row>
-    <row r="410" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A410" s="12"/>
       <c r="B410" s="12"/>
       <c r="C410" s="12"/>
@@ -19034,7 +19034,7 @@
       <c r="AM410" s="6"/>
       <c r="AN410" s="6"/>
     </row>
-    <row r="411" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A411" s="12"/>
       <c r="B411" s="12"/>
       <c r="C411" s="12"/>
@@ -19076,7 +19076,7 @@
       <c r="AM411" s="6"/>
       <c r="AN411" s="6"/>
     </row>
-    <row r="412" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A412" s="12"/>
       <c r="B412" s="12"/>
       <c r="C412" s="12"/>
@@ -19118,7 +19118,7 @@
       <c r="AM412" s="6"/>
       <c r="AN412" s="6"/>
     </row>
-    <row r="413" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A413" s="12"/>
       <c r="B413" s="12"/>
       <c r="C413" s="12"/>
@@ -19160,7 +19160,7 @@
       <c r="AM413" s="6"/>
       <c r="AN413" s="6"/>
     </row>
-    <row r="414" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A414" s="12"/>
       <c r="B414" s="12"/>
       <c r="C414" s="12"/>
@@ -19202,7 +19202,7 @@
       <c r="AM414" s="6"/>
       <c r="AN414" s="6"/>
     </row>
-    <row r="415" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A415" s="12"/>
       <c r="B415" s="12"/>
       <c r="C415" s="12"/>
@@ -19244,7 +19244,7 @@
       <c r="AM415" s="6"/>
       <c r="AN415" s="6"/>
     </row>
-    <row r="416" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A416" s="12"/>
       <c r="B416" s="12"/>
       <c r="C416" s="12"/>
@@ -19286,7 +19286,7 @@
       <c r="AM416" s="6"/>
       <c r="AN416" s="6"/>
     </row>
-    <row r="417" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A417" s="12"/>
       <c r="B417" s="12"/>
       <c r="C417" s="12"/>
@@ -19328,7 +19328,7 @@
       <c r="AM417" s="6"/>
       <c r="AN417" s="6"/>
     </row>
-    <row r="418" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A418" s="12"/>
       <c r="B418" s="12"/>
       <c r="C418" s="12"/>
@@ -19370,7 +19370,7 @@
       <c r="AM418" s="6"/>
       <c r="AN418" s="6"/>
     </row>
-    <row r="419" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A419" s="12"/>
       <c r="B419" s="12"/>
       <c r="C419" s="12"/>
@@ -19412,7 +19412,7 @@
       <c r="AM419" s="6"/>
       <c r="AN419" s="6"/>
     </row>
-    <row r="420" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A420" s="12"/>
       <c r="B420" s="12"/>
       <c r="C420" s="12"/>
@@ -19454,7 +19454,7 @@
       <c r="AM420" s="6"/>
       <c r="AN420" s="6"/>
     </row>
-    <row r="421" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A421" s="12"/>
       <c r="B421" s="12"/>
       <c r="C421" s="12"/>
@@ -19496,7 +19496,7 @@
       <c r="AM421" s="6"/>
       <c r="AN421" s="6"/>
     </row>
-    <row r="422" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A422" s="12"/>
       <c r="B422" s="12"/>
       <c r="C422" s="12"/>
@@ -19538,7 +19538,7 @@
       <c r="AM422" s="6"/>
       <c r="AN422" s="6"/>
     </row>
-    <row r="423" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A423" s="12"/>
       <c r="B423" s="12"/>
       <c r="C423" s="12"/>
@@ -19580,7 +19580,7 @@
       <c r="AM423" s="6"/>
       <c r="AN423" s="6"/>
     </row>
-    <row r="424" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A424" s="12"/>
       <c r="B424" s="12"/>
       <c r="C424" s="12"/>
@@ -19622,7 +19622,7 @@
       <c r="AM424" s="6"/>
       <c r="AN424" s="6"/>
     </row>
-    <row r="425" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A425" s="12"/>
       <c r="B425" s="12"/>
       <c r="C425" s="12"/>
@@ -19664,7 +19664,7 @@
       <c r="AM425" s="6"/>
       <c r="AN425" s="6"/>
     </row>
-    <row r="426" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A426" s="12"/>
       <c r="B426" s="12"/>
       <c r="C426" s="12"/>
@@ -19706,7 +19706,7 @@
       <c r="AM426" s="6"/>
       <c r="AN426" s="6"/>
     </row>
-    <row r="427" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A427" s="12"/>
       <c r="B427" s="12"/>
       <c r="C427" s="12"/>
@@ -19748,7 +19748,7 @@
       <c r="AM427" s="6"/>
       <c r="AN427" s="6"/>
     </row>
-    <row r="428" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A428" s="12"/>
       <c r="B428" s="12"/>
       <c r="C428" s="12"/>
@@ -19790,7 +19790,7 @@
       <c r="AM428" s="6"/>
       <c r="AN428" s="6"/>
     </row>
-    <row r="429" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A429" s="12"/>
       <c r="B429" s="12"/>
       <c r="C429" s="12"/>
@@ -19832,7 +19832,7 @@
       <c r="AM429" s="6"/>
       <c r="AN429" s="6"/>
     </row>
-    <row r="430" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A430" s="12"/>
       <c r="B430" s="12"/>
       <c r="C430" s="12"/>
@@ -19874,7 +19874,7 @@
       <c r="AM430" s="6"/>
       <c r="AN430" s="6"/>
     </row>
-    <row r="431" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A431" s="12"/>
       <c r="B431" s="12"/>
       <c r="C431" s="12"/>
@@ -19916,7 +19916,7 @@
       <c r="AM431" s="6"/>
       <c r="AN431" s="6"/>
     </row>
-    <row r="432" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A432" s="12"/>
       <c r="B432" s="12"/>
       <c r="C432" s="12"/>
@@ -19958,7 +19958,7 @@
       <c r="AM432" s="6"/>
       <c r="AN432" s="6"/>
     </row>
-    <row r="433" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A433" s="12"/>
       <c r="B433" s="12"/>
       <c r="C433" s="12"/>
@@ -20000,7 +20000,7 @@
       <c r="AM433" s="6"/>
       <c r="AN433" s="6"/>
     </row>
-    <row r="434" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A434" s="12"/>
       <c r="B434" s="12"/>
       <c r="C434" s="12"/>
@@ -20042,7 +20042,7 @@
       <c r="AM434" s="6"/>
       <c r="AN434" s="6"/>
     </row>
-    <row r="435" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A435" s="12"/>
       <c r="B435" s="12"/>
       <c r="C435" s="12"/>
@@ -20084,7 +20084,7 @@
       <c r="AM435" s="6"/>
       <c r="AN435" s="6"/>
     </row>
-    <row r="436" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A436" s="12"/>
       <c r="B436" s="12"/>
       <c r="C436" s="12"/>
@@ -20126,7 +20126,7 @@
       <c r="AM436" s="6"/>
       <c r="AN436" s="6"/>
     </row>
-    <row r="437" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A437" s="12"/>
       <c r="B437" s="12"/>
       <c r="C437" s="12"/>
@@ -20168,7 +20168,7 @@
       <c r="AM437" s="6"/>
       <c r="AN437" s="6"/>
     </row>
-    <row r="438" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A438" s="12"/>
       <c r="B438" s="12"/>
       <c r="C438" s="12"/>
@@ -20210,7 +20210,7 @@
       <c r="AM438" s="6"/>
       <c r="AN438" s="6"/>
     </row>
-    <row r="439" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A439" s="12"/>
       <c r="B439" s="12"/>
       <c r="C439" s="12"/>
@@ -20252,7 +20252,7 @@
       <c r="AM439" s="6"/>
       <c r="AN439" s="6"/>
     </row>
-    <row r="440" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A440" s="12"/>
       <c r="B440" s="12"/>
       <c r="C440" s="12"/>
@@ -20294,7 +20294,7 @@
       <c r="AM440" s="6"/>
       <c r="AN440" s="6"/>
     </row>
-    <row r="441" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A441" s="12"/>
       <c r="B441" s="12"/>
       <c r="C441" s="12"/>
@@ -20336,7 +20336,7 @@
       <c r="AM441" s="6"/>
       <c r="AN441" s="6"/>
     </row>
-    <row r="442" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A442" s="12"/>
       <c r="B442" s="12"/>
       <c r="C442" s="12"/>
@@ -20378,7 +20378,7 @@
       <c r="AM442" s="6"/>
       <c r="AN442" s="6"/>
     </row>
-    <row r="443" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A443" s="12"/>
       <c r="B443" s="12"/>
       <c r="C443" s="12"/>
@@ -20420,7 +20420,7 @@
       <c r="AM443" s="6"/>
       <c r="AN443" s="6"/>
     </row>
-    <row r="444" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A444" s="12"/>
       <c r="B444" s="12"/>
       <c r="C444" s="12"/>
@@ -20462,7 +20462,7 @@
       <c r="AM444" s="6"/>
       <c r="AN444" s="6"/>
     </row>
-    <row r="445" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A445" s="12"/>
       <c r="B445" s="12"/>
       <c r="C445" s="12"/>
@@ -20504,7 +20504,7 @@
       <c r="AM445" s="6"/>
       <c r="AN445" s="6"/>
     </row>
-    <row r="446" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A446" s="12"/>
       <c r="B446" s="12"/>
       <c r="C446" s="12"/>
@@ -20546,7 +20546,7 @@
       <c r="AM446" s="6"/>
       <c r="AN446" s="6"/>
     </row>
-    <row r="447" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A447" s="12"/>
       <c r="B447" s="12"/>
       <c r="C447" s="12"/>
@@ -20588,7 +20588,7 @@
       <c r="AM447" s="6"/>
       <c r="AN447" s="6"/>
     </row>
-    <row r="448" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A448" s="12"/>
       <c r="B448" s="12"/>
       <c r="C448" s="12"/>
@@ -20630,7 +20630,7 @@
       <c r="AM448" s="6"/>
       <c r="AN448" s="6"/>
     </row>
-    <row r="449" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A449" s="12"/>
       <c r="B449" s="12"/>
       <c r="C449" s="12"/>
@@ -20672,7 +20672,7 @@
       <c r="AM449" s="6"/>
       <c r="AN449" s="6"/>
     </row>
-    <row r="450" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A450" s="12"/>
       <c r="B450" s="12"/>
       <c r="C450" s="12"/>
@@ -20714,7 +20714,7 @@
       <c r="AM450" s="6"/>
       <c r="AN450" s="6"/>
     </row>
-    <row r="451" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A451" s="12"/>
       <c r="B451" s="12"/>
       <c r="C451" s="12"/>
@@ -20756,7 +20756,7 @@
       <c r="AM451" s="6"/>
       <c r="AN451" s="6"/>
     </row>
-    <row r="452" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A452" s="12"/>
       <c r="B452" s="12"/>
       <c r="C452" s="12"/>
@@ -20798,7 +20798,7 @@
       <c r="AM452" s="6"/>
       <c r="AN452" s="6"/>
     </row>
-    <row r="453" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A453" s="12"/>
       <c r="B453" s="12"/>
       <c r="C453" s="12"/>
@@ -20840,7 +20840,7 @@
       <c r="AM453" s="6"/>
       <c r="AN453" s="6"/>
     </row>
-    <row r="454" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A454" s="12"/>
       <c r="B454" s="12"/>
       <c r="C454" s="12"/>
@@ -20882,7 +20882,7 @@
       <c r="AM454" s="6"/>
       <c r="AN454" s="6"/>
     </row>
-    <row r="455" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A455" s="12"/>
       <c r="B455" s="12"/>
       <c r="C455" s="12"/>
@@ -20924,7 +20924,7 @@
       <c r="AM455" s="6"/>
       <c r="AN455" s="6"/>
     </row>
-    <row r="456" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A456" s="12"/>
       <c r="B456" s="12"/>
       <c r="C456" s="12"/>
@@ -20966,7 +20966,7 @@
       <c r="AM456" s="6"/>
       <c r="AN456" s="6"/>
     </row>
-    <row r="457" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A457" s="12"/>
       <c r="B457" s="12"/>
       <c r="C457" s="12"/>
@@ -21008,7 +21008,7 @@
       <c r="AM457" s="6"/>
       <c r="AN457" s="6"/>
     </row>
-    <row r="458" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A458" s="12"/>
       <c r="B458" s="12"/>
       <c r="C458" s="12"/>
@@ -21050,7 +21050,7 @@
       <c r="AM458" s="6"/>
       <c r="AN458" s="6"/>
     </row>
-    <row r="459" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A459" s="12"/>
       <c r="B459" s="12"/>
       <c r="C459" s="12"/>
@@ -21092,7 +21092,7 @@
       <c r="AM459" s="6"/>
       <c r="AN459" s="6"/>
     </row>
-    <row r="460" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A460" s="12"/>
       <c r="B460" s="12"/>
       <c r="C460" s="12"/>
@@ -21134,7 +21134,7 @@
       <c r="AM460" s="6"/>
       <c r="AN460" s="6"/>
     </row>
-    <row r="461" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A461" s="12"/>
       <c r="B461" s="12"/>
       <c r="C461" s="12"/>
@@ -21176,7 +21176,7 @@
       <c r="AM461" s="6"/>
       <c r="AN461" s="6"/>
     </row>
-    <row r="462" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A462" s="12"/>
       <c r="B462" s="12"/>
       <c r="C462" s="12"/>
@@ -21218,7 +21218,7 @@
       <c r="AM462" s="6"/>
       <c r="AN462" s="6"/>
     </row>
-    <row r="463" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A463" s="12"/>
       <c r="B463" s="12"/>
       <c r="C463" s="12"/>
@@ -21260,7 +21260,7 @@
       <c r="AM463" s="6"/>
       <c r="AN463" s="6"/>
     </row>
-    <row r="464" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A464" s="12"/>
       <c r="B464" s="12"/>
       <c r="C464" s="12"/>
@@ -21302,7 +21302,7 @@
       <c r="AM464" s="6"/>
       <c r="AN464" s="6"/>
     </row>
-    <row r="465" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A465" s="12"/>
       <c r="B465" s="12"/>
       <c r="C465" s="12"/>
@@ -21344,7 +21344,7 @@
       <c r="AM465" s="6"/>
       <c r="AN465" s="6"/>
     </row>
-    <row r="466" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A466" s="12"/>
       <c r="B466" s="12"/>
       <c r="C466" s="12"/>
@@ -21386,7 +21386,7 @@
       <c r="AM466" s="6"/>
       <c r="AN466" s="6"/>
     </row>
-    <row r="467" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A467" s="12"/>
       <c r="B467" s="12"/>
       <c r="C467" s="12"/>
@@ -21428,7 +21428,7 @@
       <c r="AM467" s="6"/>
       <c r="AN467" s="6"/>
     </row>
-    <row r="468" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A468" s="12"/>
       <c r="B468" s="12"/>
       <c r="C468" s="12"/>
@@ -21470,7 +21470,7 @@
       <c r="AM468" s="6"/>
       <c r="AN468" s="6"/>
     </row>
-    <row r="469" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A469" s="12"/>
       <c r="B469" s="12"/>
       <c r="C469" s="12"/>
@@ -21512,7 +21512,7 @@
       <c r="AM469" s="6"/>
       <c r="AN469" s="6"/>
     </row>
-    <row r="470" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A470" s="12"/>
       <c r="B470" s="12"/>
       <c r="C470" s="12"/>
@@ -21554,7 +21554,7 @@
       <c r="AM470" s="6"/>
       <c r="AN470" s="6"/>
     </row>
-    <row r="471" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A471" s="12"/>
       <c r="B471" s="12"/>
       <c r="C471" s="12"/>
@@ -21596,7 +21596,7 @@
       <c r="AM471" s="6"/>
       <c r="AN471" s="6"/>
     </row>
-    <row r="472" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A472" s="12"/>
       <c r="B472" s="12"/>
       <c r="C472" s="12"/>
@@ -21638,7 +21638,7 @@
       <c r="AM472" s="6"/>
       <c r="AN472" s="6"/>
     </row>
-    <row r="473" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A473" s="12"/>
       <c r="B473" s="12"/>
       <c r="C473" s="12"/>
@@ -21680,7 +21680,7 @@
       <c r="AM473" s="6"/>
       <c r="AN473" s="6"/>
     </row>
-    <row r="474" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A474" s="12"/>
       <c r="B474" s="12"/>
       <c r="C474" s="12"/>
@@ -21722,7 +21722,7 @@
       <c r="AM474" s="6"/>
       <c r="AN474" s="6"/>
     </row>
-    <row r="475" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A475" s="12"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12"/>
@@ -21764,7 +21764,7 @@
       <c r="AM475" s="6"/>
       <c r="AN475" s="6"/>
     </row>
-    <row r="476" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A476" s="12"/>
       <c r="B476" s="12"/>
       <c r="C476" s="12"/>
@@ -21806,7 +21806,7 @@
       <c r="AM476" s="6"/>
       <c r="AN476" s="6"/>
     </row>
-    <row r="477" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A477" s="12"/>
       <c r="B477" s="12"/>
       <c r="C477" s="12"/>
@@ -21848,7 +21848,7 @@
       <c r="AM477" s="6"/>
       <c r="AN477" s="6"/>
     </row>
-    <row r="478" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A478" s="12"/>
       <c r="B478" s="12"/>
       <c r="C478" s="12"/>
@@ -21890,7 +21890,7 @@
       <c r="AM478" s="6"/>
       <c r="AN478" s="6"/>
     </row>
-    <row r="479" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A479" s="12"/>
       <c r="B479" s="12"/>
       <c r="C479" s="12"/>
@@ -21932,7 +21932,7 @@
       <c r="AM479" s="6"/>
       <c r="AN479" s="6"/>
     </row>
-    <row r="480" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A480" s="12"/>
       <c r="B480" s="12"/>
       <c r="C480" s="12"/>
@@ -21974,7 +21974,7 @@
       <c r="AM480" s="6"/>
       <c r="AN480" s="6"/>
     </row>
-    <row r="481" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A481" s="12"/>
       <c r="B481" s="12"/>
       <c r="C481" s="12"/>
@@ -22016,7 +22016,7 @@
       <c r="AM481" s="6"/>
       <c r="AN481" s="6"/>
     </row>
-    <row r="482" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A482" s="12"/>
       <c r="B482" s="12"/>
       <c r="C482" s="12"/>
@@ -22058,7 +22058,7 @@
       <c r="AM482" s="6"/>
       <c r="AN482" s="6"/>
     </row>
-    <row r="483" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A483" s="12"/>
       <c r="B483" s="12"/>
       <c r="C483" s="12"/>
@@ -22100,7 +22100,7 @@
       <c r="AM483" s="6"/>
       <c r="AN483" s="6"/>
     </row>
-    <row r="484" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A484" s="12"/>
       <c r="B484" s="12"/>
       <c r="C484" s="12"/>
@@ -22142,7 +22142,7 @@
       <c r="AM484" s="6"/>
       <c r="AN484" s="6"/>
     </row>
-    <row r="485" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A485" s="12"/>
       <c r="B485" s="12"/>
       <c r="C485" s="12"/>
@@ -22184,7 +22184,7 @@
       <c r="AM485" s="6"/>
       <c r="AN485" s="6"/>
     </row>
-    <row r="486" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A486" s="12"/>
       <c r="B486" s="12"/>
       <c r="C486" s="12"/>
@@ -22226,7 +22226,7 @@
       <c r="AM486" s="6"/>
       <c r="AN486" s="6"/>
     </row>
-    <row r="487" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A487" s="12"/>
       <c r="B487" s="12"/>
       <c r="C487" s="12"/>
@@ -22268,7 +22268,7 @@
       <c r="AM487" s="6"/>
       <c r="AN487" s="6"/>
     </row>
-    <row r="488" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A488" s="12"/>
       <c r="B488" s="12"/>
       <c r="C488" s="12"/>
@@ -22310,7 +22310,7 @@
       <c r="AM488" s="6"/>
       <c r="AN488" s="6"/>
     </row>
-    <row r="489" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A489" s="12"/>
       <c r="B489" s="12"/>
       <c r="C489" s="12"/>
@@ -22352,7 +22352,7 @@
       <c r="AM489" s="6"/>
       <c r="AN489" s="6"/>
     </row>
-    <row r="490" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A490" s="12"/>
       <c r="B490" s="12"/>
       <c r="C490" s="12"/>
@@ -22394,7 +22394,7 @@
       <c r="AM490" s="6"/>
       <c r="AN490" s="6"/>
     </row>
-    <row r="491" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -22436,7 +22436,7 @@
       <c r="AM491" s="6"/>
       <c r="AN491" s="6"/>
     </row>
-    <row r="492" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A492" s="12"/>
       <c r="B492" s="12"/>
       <c r="C492" s="12"/>
@@ -22478,7 +22478,7 @@
       <c r="AM492" s="6"/>
       <c r="AN492" s="6"/>
     </row>
-    <row r="493" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A493" s="12"/>
       <c r="B493" s="12"/>
       <c r="C493" s="12"/>
@@ -22520,7 +22520,7 @@
       <c r="AM493" s="6"/>
       <c r="AN493" s="6"/>
     </row>
-    <row r="494" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A494" s="12"/>
       <c r="B494" s="12"/>
       <c r="C494" s="12"/>
@@ -22562,7 +22562,7 @@
       <c r="AM494" s="6"/>
       <c r="AN494" s="6"/>
     </row>
-    <row r="495" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A495" s="12"/>
       <c r="B495" s="12"/>
       <c r="C495" s="12"/>
@@ -22604,7 +22604,7 @@
       <c r="AM495" s="6"/>
       <c r="AN495" s="6"/>
     </row>
-    <row r="496" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A496" s="12"/>
       <c r="B496" s="12"/>
       <c r="C496" s="12"/>
@@ -22646,7 +22646,7 @@
       <c r="AM496" s="6"/>
       <c r="AN496" s="6"/>
     </row>
-    <row r="497" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A497" s="12"/>
       <c r="B497" s="12"/>
       <c r="C497" s="12"/>
@@ -22688,7 +22688,7 @@
       <c r="AM497" s="6"/>
       <c r="AN497" s="6"/>
     </row>
-    <row r="498" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A498" s="12"/>
       <c r="B498" s="12"/>
       <c r="C498" s="12"/>
@@ -22730,7 +22730,7 @@
       <c r="AM498" s="6"/>
       <c r="AN498" s="6"/>
     </row>
-    <row r="499" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A499" s="12"/>
       <c r="B499" s="12"/>
       <c r="C499" s="12"/>
@@ -22772,7 +22772,7 @@
       <c r="AM499" s="6"/>
       <c r="AN499" s="6"/>
     </row>
-    <row r="500" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A500" s="12"/>
       <c r="B500" s="12"/>
       <c r="C500" s="12"/>
@@ -22814,7 +22814,7 @@
       <c r="AM500" s="6"/>
       <c r="AN500" s="6"/>
     </row>
-    <row r="501" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A501" s="12"/>
       <c r="B501" s="12"/>
       <c r="C501" s="12"/>
@@ -22856,7 +22856,7 @@
       <c r="AM501" s="6"/>
       <c r="AN501" s="6"/>
     </row>
-    <row r="502" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A502" s="12"/>
       <c r="B502" s="12"/>
       <c r="C502" s="12"/>
@@ -22898,7 +22898,7 @@
       <c r="AM502" s="6"/>
       <c r="AN502" s="6"/>
     </row>
-    <row r="503" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A503" s="12"/>
       <c r="B503" s="12"/>
       <c r="C503" s="12"/>
@@ -22940,7 +22940,7 @@
       <c r="AM503" s="6"/>
       <c r="AN503" s="6"/>
     </row>
-    <row r="504" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A504" s="12"/>
       <c r="B504" s="12"/>
       <c r="C504" s="12"/>
@@ -22982,7 +22982,7 @@
       <c r="AM504" s="6"/>
       <c r="AN504" s="6"/>
     </row>
-    <row r="505" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A505" s="12"/>
       <c r="B505" s="12"/>
       <c r="C505" s="12"/>
@@ -23024,7 +23024,7 @@
       <c r="AM505" s="6"/>
       <c r="AN505" s="6"/>
     </row>
-    <row r="506" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A506" s="12"/>
       <c r="B506" s="12"/>
       <c r="C506" s="12"/>
@@ -23066,7 +23066,7 @@
       <c r="AM506" s="6"/>
       <c r="AN506" s="6"/>
     </row>
-    <row r="507" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A507" s="12"/>
       <c r="B507" s="12"/>
       <c r="C507" s="12"/>
@@ -23108,7 +23108,7 @@
       <c r="AM507" s="6"/>
       <c r="AN507" s="6"/>
     </row>
-    <row r="508" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A508" s="12"/>
       <c r="B508" s="12"/>
       <c r="C508" s="12"/>
@@ -23150,7 +23150,7 @@
       <c r="AM508" s="6"/>
       <c r="AN508" s="6"/>
     </row>
-    <row r="509" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A509" s="12"/>
       <c r="B509" s="12"/>
       <c r="C509" s="12"/>
@@ -23192,7 +23192,7 @@
       <c r="AM509" s="6"/>
       <c r="AN509" s="6"/>
     </row>
-    <row r="510" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A510" s="12"/>
       <c r="B510" s="12"/>
       <c r="C510" s="12"/>
@@ -23234,7 +23234,7 @@
       <c r="AM510" s="6"/>
       <c r="AN510" s="6"/>
     </row>
-    <row r="511" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A511" s="12"/>
       <c r="B511" s="12"/>
       <c r="C511" s="12"/>
@@ -23276,7 +23276,7 @@
       <c r="AM511" s="6"/>
       <c r="AN511" s="6"/>
     </row>
-    <row r="512" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A512" s="12"/>
       <c r="B512" s="12"/>
       <c r="C512" s="12"/>
@@ -23318,7 +23318,7 @@
       <c r="AM512" s="6"/>
       <c r="AN512" s="6"/>
     </row>
-    <row r="513" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A513" s="12"/>
       <c r="B513" s="12"/>
       <c r="C513" s="12"/>
@@ -23360,7 +23360,7 @@
       <c r="AM513" s="6"/>
       <c r="AN513" s="6"/>
     </row>
-    <row r="514" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A514" s="12"/>
       <c r="B514" s="12"/>
       <c r="C514" s="12"/>
@@ -23402,7 +23402,7 @@
       <c r="AM514" s="6"/>
       <c r="AN514" s="6"/>
     </row>
-    <row r="515" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A515" s="12"/>
       <c r="B515" s="12"/>
       <c r="C515" s="12"/>
@@ -23444,7 +23444,7 @@
       <c r="AM515" s="6"/>
       <c r="AN515" s="6"/>
     </row>
-    <row r="516" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A516" s="12"/>
       <c r="B516" s="12"/>
       <c r="C516" s="12"/>
@@ -23486,7 +23486,7 @@
       <c r="AM516" s="6"/>
       <c r="AN516" s="6"/>
     </row>
-    <row r="517" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A517" s="12"/>
       <c r="B517" s="12"/>
       <c r="C517" s="12"/>
@@ -23528,7 +23528,7 @@
       <c r="AM517" s="6"/>
       <c r="AN517" s="6"/>
     </row>
-    <row r="518" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A518" s="12"/>
       <c r="B518" s="12"/>
       <c r="C518" s="12"/>
@@ -23570,7 +23570,7 @@
       <c r="AM518" s="6"/>
       <c r="AN518" s="6"/>
     </row>
-    <row r="519" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A519" s="12"/>
       <c r="B519" s="12"/>
       <c r="C519" s="12"/>
@@ -23612,7 +23612,7 @@
       <c r="AM519" s="6"/>
       <c r="AN519" s="6"/>
     </row>
-    <row r="520" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A520" s="12"/>
       <c r="B520" s="12"/>
       <c r="C520" s="12"/>
@@ -23654,7 +23654,7 @@
       <c r="AM520" s="6"/>
       <c r="AN520" s="6"/>
     </row>
-    <row r="521" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A521" s="12"/>
       <c r="B521" s="12"/>
       <c r="C521" s="12"/>
@@ -23696,7 +23696,7 @@
       <c r="AM521" s="6"/>
       <c r="AN521" s="6"/>
     </row>
-    <row r="522" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A522" s="12"/>
       <c r="B522" s="12"/>
       <c r="C522" s="12"/>
@@ -23738,7 +23738,7 @@
       <c r="AM522" s="6"/>
       <c r="AN522" s="6"/>
     </row>
-    <row r="523" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A523" s="12"/>
       <c r="B523" s="12"/>
       <c r="C523" s="12"/>
@@ -23780,7 +23780,7 @@
       <c r="AM523" s="6"/>
       <c r="AN523" s="6"/>
     </row>
-    <row r="524" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A524" s="12"/>
       <c r="B524" s="12"/>
       <c r="C524" s="12"/>
@@ -23822,7 +23822,7 @@
       <c r="AM524" s="6"/>
       <c r="AN524" s="6"/>
     </row>
-    <row r="525" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A525" s="12"/>
       <c r="B525" s="12"/>
       <c r="C525" s="12"/>
@@ -23864,7 +23864,7 @@
       <c r="AM525" s="6"/>
       <c r="AN525" s="6"/>
     </row>
-    <row r="526" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A526" s="12"/>
       <c r="B526" s="12"/>
       <c r="C526" s="12"/>
@@ -23906,7 +23906,7 @@
       <c r="AM526" s="6"/>
       <c r="AN526" s="6"/>
     </row>
-    <row r="527" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A527" s="12"/>
       <c r="B527" s="12"/>
       <c r="C527" s="12"/>
@@ -23948,7 +23948,7 @@
       <c r="AM527" s="6"/>
       <c r="AN527" s="6"/>
     </row>
-    <row r="528" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A528" s="12"/>
       <c r="B528" s="12"/>
       <c r="C528" s="12"/>
@@ -23990,7 +23990,7 @@
       <c r="AM528" s="6"/>
       <c r="AN528" s="6"/>
     </row>
-    <row r="529" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A529" s="12"/>
       <c r="B529" s="12"/>
       <c r="C529" s="12"/>
@@ -24032,7 +24032,7 @@
       <c r="AM529" s="6"/>
       <c r="AN529" s="6"/>
     </row>
-    <row r="530" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A530" s="12"/>
       <c r="B530" s="12"/>
       <c r="C530" s="12"/>
@@ -24074,7 +24074,7 @@
       <c r="AM530" s="6"/>
       <c r="AN530" s="6"/>
     </row>
-    <row r="531" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A531" s="12"/>
       <c r="B531" s="12"/>
       <c r="C531" s="12"/>
@@ -24116,7 +24116,7 @@
       <c r="AM531" s="6"/>
       <c r="AN531" s="6"/>
     </row>
-    <row r="532" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A532" s="12"/>
       <c r="B532" s="12"/>
       <c r="C532" s="12"/>
@@ -24158,7 +24158,7 @@
       <c r="AM532" s="6"/>
       <c r="AN532" s="6"/>
     </row>
-    <row r="533" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A533" s="12"/>
       <c r="B533" s="12"/>
       <c r="C533" s="12"/>
@@ -24200,7 +24200,7 @@
       <c r="AM533" s="6"/>
       <c r="AN533" s="6"/>
     </row>
-    <row r="534" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A534" s="12"/>
       <c r="B534" s="12"/>
       <c r="C534" s="12"/>
@@ -24242,7 +24242,7 @@
       <c r="AM534" s="6"/>
       <c r="AN534" s="6"/>
     </row>
-    <row r="535" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A535" s="12"/>
       <c r="B535" s="12"/>
       <c r="C535" s="12"/>
@@ -24284,7 +24284,7 @@
       <c r="AM535" s="6"/>
       <c r="AN535" s="6"/>
     </row>
-    <row r="536" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A536" s="12"/>
       <c r="B536" s="12"/>
       <c r="C536" s="12"/>
@@ -24326,7 +24326,7 @@
       <c r="AM536" s="6"/>
       <c r="AN536" s="6"/>
     </row>
-    <row r="537" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A537" s="12"/>
       <c r="B537" s="12"/>
       <c r="C537" s="12"/>
@@ -24368,7 +24368,7 @@
       <c r="AM537" s="6"/>
       <c r="AN537" s="6"/>
     </row>
-    <row r="538" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A538" s="12"/>
       <c r="B538" s="12"/>
       <c r="C538" s="12"/>
@@ -24410,7 +24410,7 @@
       <c r="AM538" s="6"/>
       <c r="AN538" s="6"/>
     </row>
-    <row r="539" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A539" s="12"/>
       <c r="B539" s="12"/>
       <c r="C539" s="12"/>
@@ -24452,7 +24452,7 @@
       <c r="AM539" s="6"/>
       <c r="AN539" s="6"/>
     </row>
-    <row r="540" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A540" s="12"/>
       <c r="B540" s="12"/>
       <c r="C540" s="12"/>
@@ -24494,7 +24494,7 @@
       <c r="AM540" s="6"/>
       <c r="AN540" s="6"/>
     </row>
-    <row r="541" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A541" s="12"/>
       <c r="B541" s="12"/>
       <c r="C541" s="12"/>
@@ -24536,7 +24536,7 @@
       <c r="AM541" s="6"/>
       <c r="AN541" s="6"/>
     </row>
-    <row r="542" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A542" s="12"/>
       <c r="B542" s="12"/>
       <c r="C542" s="12"/>
@@ -24578,7 +24578,7 @@
       <c r="AM542" s="6"/>
       <c r="AN542" s="6"/>
     </row>
-    <row r="543" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A543" s="12"/>
       <c r="B543" s="12"/>
       <c r="C543" s="12"/>
@@ -24620,7 +24620,7 @@
       <c r="AM543" s="6"/>
       <c r="AN543" s="6"/>
     </row>
-    <row r="544" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A544" s="12"/>
       <c r="B544" s="12"/>
       <c r="C544" s="12"/>
@@ -24662,7 +24662,7 @@
       <c r="AM544" s="6"/>
       <c r="AN544" s="6"/>
     </row>
-    <row r="545" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A545" s="12"/>
       <c r="B545" s="12"/>
       <c r="C545" s="12"/>
@@ -24704,7 +24704,7 @@
       <c r="AM545" s="6"/>
       <c r="AN545" s="6"/>
     </row>
-    <row r="546" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A546" s="12"/>
       <c r="B546" s="12"/>
       <c r="C546" s="12"/>
@@ -24746,7 +24746,7 @@
       <c r="AM546" s="6"/>
       <c r="AN546" s="6"/>
     </row>
-    <row r="547" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A547" s="12"/>
       <c r="B547" s="12"/>
       <c r="C547" s="12"/>
@@ -24788,7 +24788,7 @@
       <c r="AM547" s="6"/>
       <c r="AN547" s="6"/>
     </row>
-    <row r="548" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A548" s="12"/>
       <c r="B548" s="12"/>
       <c r="C548" s="12"/>
@@ -24830,7 +24830,7 @@
       <c r="AM548" s="6"/>
       <c r="AN548" s="6"/>
     </row>
-    <row r="549" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A549" s="12"/>
       <c r="B549" s="12"/>
       <c r="C549" s="12"/>
@@ -24872,7 +24872,7 @@
       <c r="AM549" s="6"/>
       <c r="AN549" s="6"/>
     </row>
-    <row r="550" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A550" s="12"/>
       <c r="B550" s="12"/>
       <c r="C550" s="12"/>
@@ -24914,7 +24914,7 @@
       <c r="AM550" s="6"/>
       <c r="AN550" s="6"/>
     </row>
-    <row r="551" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A551" s="12"/>
       <c r="B551" s="12"/>
       <c r="C551" s="12"/>
@@ -24956,7 +24956,7 @@
       <c r="AM551" s="6"/>
       <c r="AN551" s="6"/>
     </row>
-    <row r="552" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A552" s="12"/>
       <c r="B552" s="12"/>
       <c r="C552" s="12"/>
@@ -24998,7 +24998,7 @@
       <c r="AM552" s="6"/>
       <c r="AN552" s="6"/>
     </row>
-    <row r="553" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A553" s="12"/>
       <c r="B553" s="12"/>
       <c r="C553" s="12"/>
@@ -25040,7 +25040,7 @@
       <c r="AM553" s="6"/>
       <c r="AN553" s="6"/>
     </row>
-    <row r="554" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A554" s="12"/>
       <c r="B554" s="12"/>
       <c r="C554" s="12"/>
@@ -25082,7 +25082,7 @@
       <c r="AM554" s="6"/>
       <c r="AN554" s="6"/>
     </row>
-    <row r="555" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A555" s="12"/>
       <c r="B555" s="12"/>
       <c r="C555" s="12"/>
@@ -25124,7 +25124,7 @@
       <c r="AM555" s="6"/>
       <c r="AN555" s="6"/>
     </row>
-    <row r="556" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A556" s="12"/>
       <c r="B556" s="12"/>
       <c r="C556" s="12"/>
@@ -25166,7 +25166,7 @@
       <c r="AM556" s="6"/>
       <c r="AN556" s="6"/>
     </row>
-    <row r="557" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A557" s="12"/>
       <c r="B557" s="12"/>
       <c r="C557" s="12"/>
@@ -25208,7 +25208,7 @@
       <c r="AM557" s="6"/>
       <c r="AN557" s="6"/>
     </row>
-    <row r="558" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A558" s="12"/>
       <c r="B558" s="12"/>
       <c r="C558" s="12"/>
@@ -25250,7 +25250,7 @@
       <c r="AM558" s="6"/>
       <c r="AN558" s="6"/>
     </row>
-    <row r="559" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A559" s="12"/>
       <c r="B559" s="12"/>
       <c r="C559" s="12"/>
@@ -25292,7 +25292,7 @@
       <c r="AM559" s="6"/>
       <c r="AN559" s="6"/>
     </row>
-    <row r="560" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A560" s="12"/>
       <c r="B560" s="12"/>
       <c r="C560" s="12"/>
@@ -25334,7 +25334,7 @@
       <c r="AM560" s="6"/>
       <c r="AN560" s="6"/>
     </row>
-    <row r="561" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A561" s="12"/>
       <c r="B561" s="12"/>
       <c r="C561" s="12"/>
@@ -25376,7 +25376,7 @@
       <c r="AM561" s="6"/>
       <c r="AN561" s="6"/>
     </row>
-    <row r="562" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A562" s="12"/>
       <c r="B562" s="12"/>
       <c r="C562" s="12"/>
@@ -25418,7 +25418,7 @@
       <c r="AM562" s="6"/>
       <c r="AN562" s="6"/>
     </row>
-    <row r="563" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A563" s="12"/>
       <c r="B563" s="12"/>
       <c r="C563" s="12"/>
@@ -25460,7 +25460,7 @@
       <c r="AM563" s="6"/>
       <c r="AN563" s="6"/>
     </row>
-    <row r="564" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A564" s="12"/>
       <c r="B564" s="12"/>
       <c r="C564" s="12"/>
@@ -25502,7 +25502,7 @@
       <c r="AM564" s="6"/>
       <c r="AN564" s="6"/>
     </row>
-    <row r="565" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A565" s="12"/>
       <c r="B565" s="12"/>
       <c r="C565" s="12"/>
@@ -25544,7 +25544,7 @@
       <c r="AM565" s="6"/>
       <c r="AN565" s="6"/>
     </row>
-    <row r="566" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A566" s="12"/>
       <c r="B566" s="12"/>
       <c r="C566" s="12"/>
@@ -25586,7 +25586,7 @@
       <c r="AM566" s="6"/>
       <c r="AN566" s="6"/>
     </row>
-    <row r="567" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A567" s="12"/>
       <c r="B567" s="12"/>
       <c r="C567" s="12"/>
@@ -25628,7 +25628,7 @@
       <c r="AM567" s="6"/>
       <c r="AN567" s="6"/>
     </row>
-    <row r="568" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A568" s="12"/>
       <c r="B568" s="12"/>
       <c r="C568" s="12"/>
@@ -25670,7 +25670,7 @@
       <c r="AM568" s="6"/>
       <c r="AN568" s="6"/>
     </row>
-    <row r="569" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A569" s="12"/>
       <c r="B569" s="12"/>
       <c r="C569" s="12"/>
@@ -25712,7 +25712,7 @@
       <c r="AM569" s="6"/>
       <c r="AN569" s="6"/>
     </row>
-    <row r="570" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A570" s="12"/>
       <c r="B570" s="12"/>
       <c r="C570" s="12"/>
@@ -25754,7 +25754,7 @@
       <c r="AM570" s="6"/>
       <c r="AN570" s="6"/>
     </row>
-    <row r="571" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A571" s="12"/>
       <c r="B571" s="12"/>
       <c r="C571" s="12"/>
@@ -25796,7 +25796,7 @@
       <c r="AM571" s="6"/>
       <c r="AN571" s="6"/>
     </row>
-    <row r="572" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A572" s="12"/>
       <c r="B572" s="12"/>
       <c r="C572" s="12"/>
@@ -25838,7 +25838,7 @@
       <c r="AM572" s="6"/>
       <c r="AN572" s="6"/>
     </row>
-    <row r="573" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A573" s="12"/>
       <c r="B573" s="12"/>
       <c r="C573" s="12"/>
@@ -25880,7 +25880,7 @@
       <c r="AM573" s="6"/>
       <c r="AN573" s="6"/>
     </row>
-    <row r="574" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A574" s="12"/>
       <c r="B574" s="12"/>
       <c r="C574" s="12"/>
@@ -25922,7 +25922,7 @@
       <c r="AM574" s="6"/>
       <c r="AN574" s="6"/>
     </row>
-    <row r="575" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A575" s="12"/>
       <c r="B575" s="12"/>
       <c r="C575" s="12"/>
@@ -25964,7 +25964,7 @@
       <c r="AM575" s="6"/>
       <c r="AN575" s="6"/>
     </row>
-    <row r="576" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A576" s="12"/>
       <c r="B576" s="12"/>
       <c r="C576" s="12"/>
@@ -26006,7 +26006,7 @@
       <c r="AM576" s="6"/>
       <c r="AN576" s="6"/>
     </row>
-    <row r="577" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A577" s="12"/>
       <c r="B577" s="12"/>
       <c r="C577" s="12"/>
@@ -26048,7 +26048,7 @@
       <c r="AM577" s="6"/>
       <c r="AN577" s="6"/>
     </row>
-    <row r="578" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A578" s="12"/>
       <c r="B578" s="12"/>
       <c r="C578" s="12"/>
@@ -26090,7 +26090,7 @@
       <c r="AM578" s="6"/>
       <c r="AN578" s="6"/>
     </row>
-    <row r="579" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A579" s="12"/>
       <c r="B579" s="12"/>
       <c r="C579" s="12"/>
@@ -26132,7 +26132,7 @@
       <c r="AM579" s="6"/>
       <c r="AN579" s="6"/>
     </row>
-    <row r="580" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A580" s="12"/>
       <c r="B580" s="12"/>
       <c r="C580" s="12"/>
@@ -26174,7 +26174,7 @@
       <c r="AM580" s="6"/>
       <c r="AN580" s="6"/>
     </row>
-    <row r="581" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A581" s="12"/>
       <c r="B581" s="12"/>
       <c r="C581" s="12"/>
@@ -26216,7 +26216,7 @@
       <c r="AM581" s="6"/>
       <c r="AN581" s="6"/>
     </row>
-    <row r="582" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A582" s="12"/>
       <c r="B582" s="12"/>
       <c r="C582" s="12"/>
@@ -26258,7 +26258,7 @@
       <c r="AM582" s="6"/>
       <c r="AN582" s="6"/>
     </row>
-    <row r="583" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A583" s="12"/>
       <c r="B583" s="12"/>
       <c r="C583" s="12"/>
@@ -26300,7 +26300,7 @@
       <c r="AM583" s="6"/>
       <c r="AN583" s="6"/>
     </row>
-    <row r="584" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A584" s="12"/>
       <c r="B584" s="12"/>
       <c r="C584" s="12"/>
@@ -26342,7 +26342,7 @@
       <c r="AM584" s="6"/>
       <c r="AN584" s="6"/>
     </row>
-    <row r="585" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A585" s="12"/>
       <c r="B585" s="12"/>
       <c r="C585" s="12"/>
@@ -26384,7 +26384,7 @@
       <c r="AM585" s="6"/>
       <c r="AN585" s="6"/>
     </row>
-    <row r="586" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A586" s="12"/>
       <c r="B586" s="12"/>
       <c r="C586" s="12"/>
@@ -26426,7 +26426,7 @@
       <c r="AM586" s="6"/>
       <c r="AN586" s="6"/>
     </row>
-    <row r="587" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A587" s="12"/>
       <c r="B587" s="12"/>
       <c r="C587" s="12"/>
@@ -26468,7 +26468,7 @@
       <c r="AM587" s="6"/>
       <c r="AN587" s="6"/>
     </row>
-    <row r="588" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A588" s="12"/>
       <c r="B588" s="12"/>
       <c r="C588" s="12"/>
@@ -26510,7 +26510,7 @@
       <c r="AM588" s="6"/>
       <c r="AN588" s="6"/>
     </row>
-    <row r="589" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A589" s="12"/>
       <c r="B589" s="12"/>
       <c r="C589" s="12"/>
@@ -26552,7 +26552,7 @@
       <c r="AM589" s="6"/>
       <c r="AN589" s="6"/>
     </row>
-    <row r="590" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A590" s="12"/>
       <c r="B590" s="12"/>
       <c r="C590" s="12"/>
@@ -26594,7 +26594,7 @@
       <c r="AM590" s="6"/>
       <c r="AN590" s="6"/>
     </row>
-    <row r="591" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A591" s="12"/>
       <c r="B591" s="12"/>
       <c r="C591" s="12"/>
@@ -26636,7 +26636,7 @@
       <c r="AM591" s="6"/>
       <c r="AN591" s="6"/>
     </row>
-    <row r="592" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A592" s="12"/>
       <c r="B592" s="12"/>
       <c r="C592" s="12"/>
@@ -26678,7 +26678,7 @@
       <c r="AM592" s="6"/>
       <c r="AN592" s="6"/>
     </row>
-    <row r="593" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A593" s="12"/>
       <c r="B593" s="12"/>
       <c r="C593" s="12"/>
@@ -26720,7 +26720,7 @@
       <c r="AM593" s="6"/>
       <c r="AN593" s="6"/>
     </row>
-    <row r="594" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A594" s="12"/>
       <c r="B594" s="12"/>
       <c r="C594" s="12"/>
@@ -26762,7 +26762,7 @@
       <c r="AM594" s="6"/>
       <c r="AN594" s="6"/>
     </row>
-    <row r="595" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A595" s="12"/>
       <c r="B595" s="12"/>
       <c r="C595" s="12"/>
@@ -26804,7 +26804,7 @@
       <c r="AM595" s="6"/>
       <c r="AN595" s="6"/>
     </row>
-    <row r="596" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A596" s="12"/>
       <c r="B596" s="12"/>
       <c r="C596" s="12"/>
@@ -26846,7 +26846,7 @@
       <c r="AM596" s="6"/>
       <c r="AN596" s="6"/>
     </row>
-    <row r="597" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A597" s="12"/>
       <c r="B597" s="12"/>
       <c r="C597" s="12"/>
@@ -26888,7 +26888,7 @@
       <c r="AM597" s="6"/>
       <c r="AN597" s="6"/>
     </row>
-    <row r="598" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A598" s="12"/>
       <c r="B598" s="12"/>
       <c r="C598" s="12"/>
@@ -26930,7 +26930,7 @@
       <c r="AM598" s="6"/>
       <c r="AN598" s="6"/>
     </row>
-    <row r="599" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A599" s="12"/>
       <c r="B599" s="12"/>
       <c r="C599" s="12"/>
@@ -26972,7 +26972,7 @@
       <c r="AM599" s="6"/>
       <c r="AN599" s="6"/>
     </row>
-    <row r="600" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A600" s="12"/>
       <c r="B600" s="12"/>
       <c r="C600" s="12"/>
@@ -27014,7 +27014,7 @@
       <c r="AM600" s="6"/>
       <c r="AN600" s="6"/>
     </row>
-    <row r="601" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A601" s="12"/>
       <c r="B601" s="12"/>
       <c r="C601" s="12"/>
@@ -27056,7 +27056,7 @@
       <c r="AM601" s="6"/>
       <c r="AN601" s="6"/>
     </row>
-    <row r="602" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A602" s="12"/>
       <c r="B602" s="12"/>
       <c r="C602" s="12"/>
@@ -27098,7 +27098,7 @@
       <c r="AM602" s="6"/>
       <c r="AN602" s="6"/>
     </row>
-    <row r="603" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A603" s="12"/>
       <c r="B603" s="12"/>
       <c r="C603" s="12"/>
@@ -27140,7 +27140,7 @@
       <c r="AM603" s="6"/>
       <c r="AN603" s="6"/>
     </row>
-    <row r="604" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A604" s="12"/>
       <c r="B604" s="12"/>
       <c r="C604" s="12"/>
@@ -27182,7 +27182,7 @@
       <c r="AM604" s="6"/>
       <c r="AN604" s="6"/>
     </row>
-    <row r="605" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A605" s="12"/>
       <c r="B605" s="12"/>
       <c r="C605" s="12"/>
@@ -27224,7 +27224,7 @@
       <c r="AM605" s="6"/>
       <c r="AN605" s="6"/>
     </row>
-    <row r="606" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A606" s="12"/>
       <c r="B606" s="12"/>
       <c r="C606" s="12"/>
@@ -27266,7 +27266,7 @@
       <c r="AM606" s="6"/>
       <c r="AN606" s="6"/>
     </row>
-    <row r="607" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A607" s="12"/>
       <c r="B607" s="12"/>
       <c r="C607" s="12"/>
@@ -27308,7 +27308,7 @@
       <c r="AM607" s="6"/>
       <c r="AN607" s="6"/>
     </row>
-    <row r="608" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A608" s="12"/>
       <c r="B608" s="12"/>
       <c r="C608" s="12"/>
@@ -27350,7 +27350,7 @@
       <c r="AM608" s="6"/>
       <c r="AN608" s="6"/>
     </row>
-    <row r="609" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A609" s="12"/>
       <c r="B609" s="12"/>
       <c r="C609" s="12"/>
@@ -27392,7 +27392,7 @@
       <c r="AM609" s="6"/>
       <c r="AN609" s="6"/>
     </row>
-    <row r="610" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A610" s="12"/>
       <c r="B610" s="12"/>
       <c r="C610" s="12"/>
@@ -27434,7 +27434,7 @@
       <c r="AM610" s="6"/>
       <c r="AN610" s="6"/>
     </row>
-    <row r="611" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A611" s="12"/>
       <c r="B611" s="12"/>
       <c r="C611" s="12"/>
@@ -27476,7 +27476,7 @@
       <c r="AM611" s="6"/>
       <c r="AN611" s="6"/>
     </row>
-    <row r="612" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A612" s="12"/>
       <c r="B612" s="12"/>
       <c r="C612" s="12"/>
@@ -27518,7 +27518,7 @@
       <c r="AM612" s="6"/>
       <c r="AN612" s="6"/>
     </row>
-    <row r="613" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A613" s="12"/>
       <c r="B613" s="12"/>
       <c r="C613" s="12"/>
@@ -27560,7 +27560,7 @@
       <c r="AM613" s="6"/>
       <c r="AN613" s="6"/>
     </row>
-    <row r="614" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A614" s="12"/>
       <c r="B614" s="12"/>
       <c r="C614" s="12"/>
@@ -27602,7 +27602,7 @@
       <c r="AM614" s="6"/>
       <c r="AN614" s="6"/>
     </row>
-    <row r="615" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A615" s="12"/>
       <c r="B615" s="12"/>
       <c r="C615" s="12"/>
@@ -27644,7 +27644,7 @@
       <c r="AM615" s="6"/>
       <c r="AN615" s="6"/>
     </row>
-    <row r="616" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A616" s="12"/>
       <c r="B616" s="12"/>
       <c r="C616" s="12"/>
@@ -27686,7 +27686,7 @@
       <c r="AM616" s="6"/>
       <c r="AN616" s="6"/>
     </row>
-    <row r="617" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A617" s="12"/>
       <c r="B617" s="12"/>
       <c r="C617" s="12"/>
@@ -27728,7 +27728,7 @@
       <c r="AM617" s="6"/>
       <c r="AN617" s="6"/>
     </row>
-    <row r="618" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A618" s="12"/>
       <c r="B618" s="12"/>
       <c r="C618" s="12"/>
@@ -27770,7 +27770,7 @@
       <c r="AM618" s="6"/>
       <c r="AN618" s="6"/>
     </row>
-    <row r="619" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A619" s="12"/>
       <c r="B619" s="12"/>
       <c r="C619" s="12"/>
@@ -27812,7 +27812,7 @@
       <c r="AM619" s="6"/>
       <c r="AN619" s="6"/>
     </row>
-    <row r="620" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A620" s="12"/>
       <c r="B620" s="12"/>
       <c r="C620" s="12"/>
@@ -27854,7 +27854,7 @@
       <c r="AM620" s="6"/>
       <c r="AN620" s="6"/>
     </row>
-    <row r="621" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A621" s="12"/>
       <c r="B621" s="12"/>
       <c r="C621" s="12"/>
@@ -27896,7 +27896,7 @@
       <c r="AM621" s="6"/>
       <c r="AN621" s="6"/>
     </row>
-    <row r="622" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A622" s="12"/>
       <c r="B622" s="12"/>
       <c r="C622" s="12"/>
@@ -27938,7 +27938,7 @@
       <c r="AM622" s="6"/>
       <c r="AN622" s="6"/>
     </row>
-    <row r="623" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A623" s="12"/>
       <c r="B623" s="12"/>
       <c r="C623" s="12"/>
@@ -27980,7 +27980,7 @@
       <c r="AM623" s="6"/>
       <c r="AN623" s="6"/>
     </row>
-    <row r="624" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A624" s="12"/>
       <c r="B624" s="12"/>
       <c r="C624" s="12"/>
@@ -28022,7 +28022,7 @@
       <c r="AM624" s="6"/>
       <c r="AN624" s="6"/>
     </row>
-    <row r="625" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A625" s="12"/>
       <c r="B625" s="12"/>
       <c r="C625" s="12"/>
@@ -28064,7 +28064,7 @@
       <c r="AM625" s="6"/>
       <c r="AN625" s="6"/>
     </row>
-    <row r="626" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A626" s="12"/>
       <c r="B626" s="12"/>
       <c r="C626" s="12"/>
@@ -28106,7 +28106,7 @@
       <c r="AM626" s="6"/>
       <c r="AN626" s="6"/>
     </row>
-    <row r="627" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A627" s="12"/>
       <c r="B627" s="12"/>
       <c r="C627" s="12"/>
@@ -28148,7 +28148,7 @@
       <c r="AM627" s="6"/>
       <c r="AN627" s="6"/>
     </row>
-    <row r="628" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A628" s="12"/>
       <c r="B628" s="12"/>
       <c r="C628" s="12"/>
@@ -28190,7 +28190,7 @@
       <c r="AM628" s="6"/>
       <c r="AN628" s="6"/>
     </row>
-    <row r="629" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A629" s="12"/>
       <c r="B629" s="12"/>
       <c r="C629" s="12"/>
@@ -28232,7 +28232,7 @@
       <c r="AM629" s="6"/>
       <c r="AN629" s="6"/>
     </row>
-    <row r="630" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A630" s="12"/>
       <c r="B630" s="12"/>
       <c r="C630" s="12"/>
@@ -28274,7 +28274,7 @@
       <c r="AM630" s="6"/>
       <c r="AN630" s="6"/>
     </row>
-    <row r="631" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A631" s="12"/>
       <c r="B631" s="12"/>
       <c r="C631" s="12"/>
@@ -28316,7 +28316,7 @@
       <c r="AM631" s="6"/>
       <c r="AN631" s="6"/>
     </row>
-    <row r="632" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A632" s="12"/>
       <c r="B632" s="12"/>
       <c r="C632" s="12"/>
@@ -28358,7 +28358,7 @@
       <c r="AM632" s="6"/>
       <c r="AN632" s="6"/>
     </row>
-    <row r="633" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A633" s="12"/>
       <c r="B633" s="12"/>
       <c r="C633" s="12"/>
@@ -28400,7 +28400,7 @@
       <c r="AM633" s="6"/>
       <c r="AN633" s="6"/>
     </row>
-    <row r="634" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A634" s="12"/>
       <c r="B634" s="12"/>
       <c r="C634" s="12"/>
@@ -28442,7 +28442,7 @@
       <c r="AM634" s="6"/>
       <c r="AN634" s="6"/>
     </row>
-    <row r="635" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A635" s="12"/>
       <c r="B635" s="12"/>
       <c r="C635" s="12"/>
@@ -28484,7 +28484,7 @@
       <c r="AM635" s="6"/>
       <c r="AN635" s="6"/>
     </row>
-    <row r="636" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A636" s="12"/>
       <c r="B636" s="12"/>
       <c r="C636" s="12"/>
@@ -28526,7 +28526,7 @@
       <c r="AM636" s="6"/>
       <c r="AN636" s="6"/>
     </row>
-    <row r="637" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A637" s="12"/>
       <c r="B637" s="12"/>
       <c r="C637" s="12"/>
@@ -28568,7 +28568,7 @@
       <c r="AM637" s="6"/>
       <c r="AN637" s="6"/>
     </row>
-    <row r="638" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A638" s="12"/>
       <c r="B638" s="12"/>
       <c r="C638" s="12"/>
@@ -28610,7 +28610,7 @@
       <c r="AM638" s="6"/>
       <c r="AN638" s="6"/>
     </row>
-    <row r="639" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A639" s="12"/>
       <c r="B639" s="12"/>
       <c r="C639" s="12"/>
@@ -28652,7 +28652,7 @@
       <c r="AM639" s="6"/>
       <c r="AN639" s="6"/>
     </row>
-    <row r="640" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A640" s="12"/>
       <c r="B640" s="12"/>
       <c r="C640" s="12"/>
@@ -28694,7 +28694,7 @@
       <c r="AM640" s="6"/>
       <c r="AN640" s="6"/>
     </row>
-    <row r="641" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A641" s="12"/>
       <c r="B641" s="12"/>
       <c r="C641" s="12"/>
@@ -28736,7 +28736,7 @@
       <c r="AM641" s="6"/>
       <c r="AN641" s="6"/>
     </row>
-    <row r="642" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A642" s="12"/>
       <c r="B642" s="12"/>
       <c r="C642" s="12"/>
@@ -28778,7 +28778,7 @@
       <c r="AM642" s="6"/>
       <c r="AN642" s="6"/>
     </row>
-    <row r="643" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A643" s="12"/>
       <c r="B643" s="12"/>
       <c r="C643" s="12"/>
@@ -28820,7 +28820,7 @@
       <c r="AM643" s="6"/>
       <c r="AN643" s="6"/>
     </row>
-    <row r="644" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A644" s="12"/>
       <c r="B644" s="12"/>
       <c r="C644" s="12"/>
@@ -28862,7 +28862,7 @@
       <c r="AM644" s="6"/>
       <c r="AN644" s="6"/>
     </row>
-    <row r="645" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A645" s="12"/>
       <c r="B645" s="12"/>
       <c r="C645" s="12"/>
@@ -28904,7 +28904,7 @@
       <c r="AM645" s="6"/>
       <c r="AN645" s="6"/>
     </row>
-    <row r="646" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A646" s="12"/>
       <c r="B646" s="12"/>
       <c r="C646" s="12"/>
@@ -28946,7 +28946,7 @@
       <c r="AM646" s="6"/>
       <c r="AN646" s="6"/>
     </row>
-    <row r="647" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A647" s="12"/>
       <c r="B647" s="12"/>
       <c r="C647" s="12"/>
@@ -28988,7 +28988,7 @@
       <c r="AM647" s="6"/>
       <c r="AN647" s="6"/>
     </row>
-    <row r="648" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A648" s="12"/>
       <c r="B648" s="12"/>
       <c r="C648" s="12"/>
@@ -29030,7 +29030,7 @@
       <c r="AM648" s="6"/>
       <c r="AN648" s="6"/>
     </row>
-    <row r="649" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A649" s="12"/>
       <c r="B649" s="12"/>
       <c r="C649" s="12"/>
@@ -29072,7 +29072,7 @@
       <c r="AM649" s="6"/>
       <c r="AN649" s="6"/>
     </row>
-    <row r="650" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A650" s="12"/>
       <c r="B650" s="12"/>
       <c r="C650" s="12"/>
@@ -29114,7 +29114,7 @@
       <c r="AM650" s="6"/>
       <c r="AN650" s="6"/>
     </row>
-    <row r="651" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A651" s="12"/>
       <c r="B651" s="12"/>
       <c r="C651" s="12"/>
@@ -29156,7 +29156,7 @@
       <c r="AM651" s="6"/>
       <c r="AN651" s="6"/>
     </row>
-    <row r="652" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A652" s="12"/>
       <c r="B652" s="12"/>
       <c r="C652" s="12"/>
@@ -29198,7 +29198,7 @@
       <c r="AM652" s="6"/>
       <c r="AN652" s="6"/>
     </row>
-    <row r="653" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A653" s="12"/>
       <c r="B653" s="12"/>
       <c r="C653" s="12"/>
@@ -29240,7 +29240,7 @@
       <c r="AM653" s="6"/>
       <c r="AN653" s="6"/>
     </row>
-    <row r="654" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A654" s="12"/>
       <c r="B654" s="12"/>
       <c r="C654" s="12"/>
@@ -29282,7 +29282,7 @@
       <c r="AM654" s="6"/>
       <c r="AN654" s="6"/>
     </row>
-    <row r="655" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A655" s="12"/>
       <c r="B655" s="12"/>
       <c r="C655" s="12"/>
@@ -29324,7 +29324,7 @@
       <c r="AM655" s="6"/>
       <c r="AN655" s="6"/>
     </row>
-    <row r="656" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A656" s="12"/>
       <c r="B656" s="12"/>
       <c r="C656" s="12"/>
@@ -29366,7 +29366,7 @@
       <c r="AM656" s="6"/>
       <c r="AN656" s="6"/>
     </row>
-    <row r="657" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A657" s="12"/>
       <c r="B657" s="12"/>
       <c r="C657" s="12"/>
@@ -29408,7 +29408,7 @@
       <c r="AM657" s="6"/>
       <c r="AN657" s="6"/>
     </row>
-    <row r="658" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A658" s="12"/>
       <c r="B658" s="12"/>
       <c r="C658" s="12"/>
@@ -29450,7 +29450,7 @@
       <c r="AM658" s="6"/>
       <c r="AN658" s="6"/>
     </row>
-    <row r="659" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A659" s="12"/>
       <c r="B659" s="12"/>
       <c r="C659" s="12"/>
@@ -29492,7 +29492,7 @@
       <c r="AM659" s="6"/>
       <c r="AN659" s="6"/>
     </row>
-    <row r="660" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A660" s="12"/>
       <c r="B660" s="12"/>
       <c r="C660" s="12"/>
@@ -29534,7 +29534,7 @@
       <c r="AM660" s="6"/>
       <c r="AN660" s="6"/>
     </row>
-    <row r="661" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A661" s="12"/>
       <c r="B661" s="12"/>
       <c r="C661" s="12"/>
@@ -29576,7 +29576,7 @@
       <c r="AM661" s="6"/>
       <c r="AN661" s="6"/>
     </row>
-    <row r="662" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A662" s="12"/>
       <c r="B662" s="12"/>
       <c r="C662" s="12"/>
@@ -29618,7 +29618,7 @@
       <c r="AM662" s="6"/>
       <c r="AN662" s="6"/>
     </row>
-    <row r="663" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A663" s="12"/>
       <c r="B663" s="12"/>
       <c r="C663" s="12"/>
@@ -29660,7 +29660,7 @@
       <c r="AM663" s="6"/>
       <c r="AN663" s="6"/>
     </row>
-    <row r="664" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A664" s="12"/>
       <c r="B664" s="12"/>
       <c r="C664" s="12"/>
@@ -29702,7 +29702,7 @@
       <c r="AM664" s="6"/>
       <c r="AN664" s="6"/>
     </row>
-    <row r="665" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A665" s="12"/>
       <c r="B665" s="12"/>
       <c r="C665" s="12"/>
@@ -29744,7 +29744,7 @@
       <c r="AM665" s="6"/>
       <c r="AN665" s="6"/>
     </row>
-    <row r="666" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A666" s="12"/>
       <c r="B666" s="12"/>
       <c r="C666" s="12"/>
@@ -29786,7 +29786,7 @@
       <c r="AM666" s="6"/>
       <c r="AN666" s="6"/>
     </row>
-    <row r="667" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A667" s="12"/>
       <c r="B667" s="12"/>
       <c r="C667" s="12"/>
@@ -29828,7 +29828,7 @@
       <c r="AM667" s="6"/>
       <c r="AN667" s="6"/>
     </row>
-    <row r="668" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A668" s="12"/>
       <c r="B668" s="12"/>
       <c r="C668" s="12"/>
@@ -29870,7 +29870,7 @@
       <c r="AM668" s="6"/>
       <c r="AN668" s="6"/>
     </row>
-    <row r="669" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A669" s="12"/>
       <c r="B669" s="12"/>
       <c r="C669" s="12"/>
@@ -29912,7 +29912,7 @@
       <c r="AM669" s="6"/>
       <c r="AN669" s="6"/>
     </row>
-    <row r="670" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A670" s="12"/>
       <c r="B670" s="12"/>
       <c r="C670" s="12"/>
@@ -29954,7 +29954,7 @@
       <c r="AM670" s="6"/>
       <c r="AN670" s="6"/>
     </row>
-    <row r="671" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A671" s="12"/>
       <c r="B671" s="12"/>
       <c r="C671" s="12"/>
@@ -29996,7 +29996,7 @@
       <c r="AM671" s="6"/>
       <c r="AN671" s="6"/>
     </row>
-    <row r="672" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A672" s="12"/>
       <c r="B672" s="12"/>
       <c r="C672" s="12"/>
@@ -30038,7 +30038,7 @@
       <c r="AM672" s="6"/>
       <c r="AN672" s="6"/>
     </row>
-    <row r="673" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A673" s="12"/>
       <c r="B673" s="12"/>
       <c r="C673" s="12"/>
@@ -30080,7 +30080,7 @@
       <c r="AM673" s="6"/>
       <c r="AN673" s="6"/>
     </row>
-    <row r="674" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A674" s="12"/>
       <c r="B674" s="12"/>
       <c r="C674" s="12"/>
@@ -30122,7 +30122,7 @@
       <c r="AM674" s="6"/>
       <c r="AN674" s="6"/>
     </row>
-    <row r="675" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A675" s="12"/>
       <c r="B675" s="12"/>
       <c r="C675" s="12"/>
@@ -30164,7 +30164,7 @@
       <c r="AM675" s="6"/>
       <c r="AN675" s="6"/>
     </row>
-    <row r="676" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A676" s="12"/>
       <c r="B676" s="12"/>
       <c r="C676" s="12"/>
@@ -30206,7 +30206,7 @@
       <c r="AM676" s="6"/>
       <c r="AN676" s="6"/>
     </row>
-    <row r="677" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A677" s="12"/>
       <c r="B677" s="12"/>
       <c r="C677" s="12"/>
@@ -30248,7 +30248,7 @@
       <c r="AM677" s="6"/>
       <c r="AN677" s="6"/>
     </row>
-    <row r="678" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A678" s="12"/>
       <c r="B678" s="12"/>
       <c r="C678" s="12"/>
@@ -30290,7 +30290,7 @@
       <c r="AM678" s="6"/>
       <c r="AN678" s="6"/>
     </row>
-    <row r="679" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A679" s="12"/>
       <c r="B679" s="12"/>
       <c r="C679" s="12"/>
@@ -30332,7 +30332,7 @@
       <c r="AM679" s="6"/>
       <c r="AN679" s="6"/>
     </row>
-    <row r="680" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A680" s="12"/>
       <c r="B680" s="12"/>
       <c r="C680" s="12"/>
@@ -30374,7 +30374,7 @@
       <c r="AM680" s="6"/>
       <c r="AN680" s="6"/>
     </row>
-    <row r="681" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A681" s="12"/>
       <c r="B681" s="12"/>
       <c r="C681" s="12"/>
@@ -30416,7 +30416,7 @@
       <c r="AM681" s="6"/>
       <c r="AN681" s="6"/>
     </row>
-    <row r="682" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A682" s="12"/>
       <c r="B682" s="12"/>
       <c r="C682" s="12"/>
@@ -30458,7 +30458,7 @@
       <c r="AM682" s="6"/>
       <c r="AN682" s="6"/>
     </row>
-    <row r="683" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A683" s="12"/>
       <c r="B683" s="12"/>
       <c r="C683" s="12"/>
@@ -30500,7 +30500,7 @@
       <c r="AM683" s="6"/>
       <c r="AN683" s="6"/>
     </row>
-    <row r="684" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A684" s="12"/>
       <c r="B684" s="12"/>
       <c r="C684" s="12"/>
@@ -30542,7 +30542,7 @@
       <c r="AM684" s="6"/>
       <c r="AN684" s="6"/>
     </row>
-    <row r="685" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A685" s="12"/>
       <c r="B685" s="12"/>
       <c r="C685" s="12"/>
@@ -30584,7 +30584,7 @@
       <c r="AM685" s="6"/>
       <c r="AN685" s="6"/>
     </row>
-    <row r="686" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A686" s="12"/>
       <c r="B686" s="12"/>
       <c r="C686" s="12"/>
@@ -30626,7 +30626,7 @@
       <c r="AM686" s="6"/>
       <c r="AN686" s="6"/>
     </row>
-    <row r="687" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A687" s="12"/>
       <c r="B687" s="12"/>
       <c r="C687" s="12"/>
@@ -30668,7 +30668,7 @@
       <c r="AM687" s="6"/>
       <c r="AN687" s="6"/>
     </row>
-    <row r="688" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A688" s="12"/>
       <c r="B688" s="12"/>
       <c r="C688" s="12"/>
@@ -30710,7 +30710,7 @@
       <c r="AM688" s="6"/>
       <c r="AN688" s="6"/>
     </row>
-    <row r="689" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A689" s="12"/>
       <c r="B689" s="12"/>
       <c r="C689" s="12"/>
@@ -30752,7 +30752,7 @@
       <c r="AM689" s="6"/>
       <c r="AN689" s="6"/>
     </row>
-    <row r="690" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A690" s="12"/>
       <c r="B690" s="12"/>
       <c r="C690" s="12"/>
@@ -30794,7 +30794,7 @@
       <c r="AM690" s="6"/>
       <c r="AN690" s="6"/>
     </row>
-    <row r="691" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A691" s="12"/>
       <c r="B691" s="12"/>
       <c r="C691" s="12"/>
@@ -30836,7 +30836,7 @@
       <c r="AM691" s="6"/>
       <c r="AN691" s="6"/>
     </row>
-    <row r="692" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A692" s="12"/>
       <c r="B692" s="12"/>
       <c r="C692" s="12"/>
@@ -30878,7 +30878,7 @@
       <c r="AM692" s="6"/>
       <c r="AN692" s="6"/>
     </row>
-    <row r="693" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A693" s="12"/>
       <c r="B693" s="12"/>
       <c r="C693" s="12"/>
@@ -30920,7 +30920,7 @@
       <c r="AM693" s="6"/>
       <c r="AN693" s="6"/>
     </row>
-    <row r="694" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A694" s="12"/>
       <c r="B694" s="12"/>
       <c r="C694" s="12"/>
@@ -30962,7 +30962,7 @@
       <c r="AM694" s="6"/>
       <c r="AN694" s="6"/>
     </row>
-    <row r="695" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A695" s="12"/>
       <c r="B695" s="12"/>
       <c r="C695" s="12"/>
@@ -31004,7 +31004,7 @@
       <c r="AM695" s="6"/>
       <c r="AN695" s="6"/>
     </row>
-    <row r="696" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A696" s="12"/>
       <c r="B696" s="12"/>
       <c r="C696" s="12"/>
@@ -31046,7 +31046,7 @@
       <c r="AM696" s="6"/>
       <c r="AN696" s="6"/>
     </row>
-    <row r="697" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A697" s="12"/>
       <c r="B697" s="12"/>
       <c r="C697" s="12"/>
@@ -31088,7 +31088,7 @@
       <c r="AM697" s="6"/>
       <c r="AN697" s="6"/>
     </row>
-    <row r="698" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A698" s="12"/>
       <c r="B698" s="12"/>
       <c r="C698" s="12"/>
@@ -31130,7 +31130,7 @@
       <c r="AM698" s="6"/>
       <c r="AN698" s="6"/>
     </row>
-    <row r="699" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A699" s="12"/>
       <c r="B699" s="12"/>
       <c r="C699" s="12"/>
@@ -31172,7 +31172,7 @@
       <c r="AM699" s="6"/>
       <c r="AN699" s="6"/>
     </row>
-    <row r="700" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A700" s="12"/>
       <c r="B700" s="12"/>
       <c r="C700" s="12"/>
@@ -31214,7 +31214,7 @@
       <c r="AM700" s="6"/>
       <c r="AN700" s="6"/>
     </row>
-    <row r="701" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A701" s="12"/>
       <c r="B701" s="12"/>
       <c r="C701" s="12"/>
@@ -31256,7 +31256,7 @@
       <c r="AM701" s="6"/>
       <c r="AN701" s="6"/>
     </row>
-    <row r="702" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A702" s="12"/>
       <c r="B702" s="12"/>
       <c r="C702" s="12"/>
@@ -31298,7 +31298,7 @@
       <c r="AM702" s="6"/>
       <c r="AN702" s="6"/>
     </row>
-    <row r="703" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A703" s="12"/>
       <c r="B703" s="12"/>
       <c r="C703" s="12"/>
@@ -31340,7 +31340,7 @@
       <c r="AM703" s="6"/>
       <c r="AN703" s="6"/>
     </row>
-    <row r="704" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A704" s="12"/>
       <c r="B704" s="12"/>
       <c r="C704" s="12"/>
@@ -31382,7 +31382,7 @@
       <c r="AM704" s="6"/>
       <c r="AN704" s="6"/>
     </row>
-    <row r="705" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A705" s="12"/>
       <c r="B705" s="12"/>
       <c r="C705" s="12"/>
@@ -31424,7 +31424,7 @@
       <c r="AM705" s="6"/>
       <c r="AN705" s="6"/>
     </row>
-    <row r="706" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A706" s="12"/>
       <c r="B706" s="12"/>
       <c r="C706" s="12"/>
@@ -31466,7 +31466,7 @@
       <c r="AM706" s="6"/>
       <c r="AN706" s="6"/>
     </row>
-    <row r="707" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A707" s="12"/>
       <c r="B707" s="12"/>
       <c r="C707" s="12"/>
@@ -31508,7 +31508,7 @@
       <c r="AM707" s="6"/>
       <c r="AN707" s="6"/>
     </row>
-    <row r="708" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A708" s="12"/>
       <c r="B708" s="12"/>
       <c r="C708" s="12"/>
@@ -31550,7 +31550,7 @@
       <c r="AM708" s="6"/>
       <c r="AN708" s="6"/>
     </row>
-    <row r="709" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A709" s="12"/>
       <c r="B709" s="12"/>
       <c r="C709" s="12"/>
@@ -31592,7 +31592,7 @@
       <c r="AM709" s="6"/>
       <c r="AN709" s="6"/>
     </row>
-    <row r="710" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A710" s="12"/>
       <c r="B710" s="12"/>
       <c r="C710" s="12"/>
@@ -31634,7 +31634,7 @@
       <c r="AM710" s="6"/>
       <c r="AN710" s="6"/>
     </row>
-    <row r="711" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A711" s="12"/>
       <c r="B711" s="12"/>
       <c r="C711" s="12"/>
@@ -31676,7 +31676,7 @@
       <c r="AM711" s="6"/>
       <c r="AN711" s="6"/>
     </row>
-    <row r="712" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A712" s="12"/>
       <c r="B712" s="12"/>
       <c r="C712" s="12"/>
@@ -31718,7 +31718,7 @@
       <c r="AM712" s="6"/>
       <c r="AN712" s="6"/>
     </row>
-    <row r="713" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A713" s="12"/>
       <c r="B713" s="12"/>
       <c r="C713" s="12"/>
@@ -31760,7 +31760,7 @@
       <c r="AM713" s="6"/>
       <c r="AN713" s="6"/>
     </row>
-    <row r="714" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A714" s="12"/>
       <c r="B714" s="12"/>
       <c r="C714" s="12"/>
@@ -31802,7 +31802,7 @@
       <c r="AM714" s="6"/>
       <c r="AN714" s="6"/>
     </row>
-    <row r="715" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A715" s="12"/>
       <c r="B715" s="12"/>
       <c r="C715" s="12"/>
@@ -31844,7 +31844,7 @@
       <c r="AM715" s="6"/>
       <c r="AN715" s="6"/>
     </row>
-    <row r="716" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A716" s="12"/>
       <c r="B716" s="12"/>
       <c r="C716" s="12"/>
@@ -31886,7 +31886,7 @@
       <c r="AM716" s="6"/>
       <c r="AN716" s="6"/>
     </row>
-    <row r="717" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A717" s="12"/>
       <c r="B717" s="12"/>
       <c r="C717" s="12"/>
@@ -31928,7 +31928,7 @@
       <c r="AM717" s="6"/>
       <c r="AN717" s="6"/>
     </row>
-    <row r="718" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A718" s="12"/>
       <c r="B718" s="12"/>
       <c r="C718" s="12"/>
@@ -31970,7 +31970,7 @@
       <c r="AM718" s="6"/>
       <c r="AN718" s="6"/>
     </row>
-    <row r="719" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A719" s="12"/>
       <c r="B719" s="12"/>
       <c r="C719" s="12"/>
@@ -32012,7 +32012,7 @@
       <c r="AM719" s="6"/>
       <c r="AN719" s="6"/>
     </row>
-    <row r="720" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A720" s="12"/>
       <c r="B720" s="12"/>
       <c r="C720" s="12"/>
@@ -32054,7 +32054,7 @@
       <c r="AM720" s="6"/>
       <c r="AN720" s="6"/>
     </row>
-    <row r="721" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A721" s="12"/>
       <c r="B721" s="12"/>
       <c r="C721" s="12"/>
@@ -32096,7 +32096,7 @@
       <c r="AM721" s="6"/>
       <c r="AN721" s="6"/>
     </row>
-    <row r="722" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A722" s="12"/>
       <c r="B722" s="12"/>
       <c r="C722" s="12"/>
@@ -32138,7 +32138,7 @@
       <c r="AM722" s="6"/>
       <c r="AN722" s="6"/>
     </row>
-    <row r="723" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A723" s="12"/>
       <c r="B723" s="12"/>
       <c r="C723" s="12"/>
@@ -32180,7 +32180,7 @@
       <c r="AM723" s="6"/>
       <c r="AN723" s="6"/>
     </row>
-    <row r="724" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A724" s="12"/>
       <c r="B724" s="12"/>
       <c r="C724" s="12"/>
@@ -32222,7 +32222,7 @@
       <c r="AM724" s="6"/>
       <c r="AN724" s="6"/>
     </row>
-    <row r="725" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A725" s="12"/>
       <c r="B725" s="12"/>
       <c r="C725" s="12"/>
@@ -32264,7 +32264,7 @@
       <c r="AM725" s="6"/>
       <c r="AN725" s="6"/>
     </row>
-    <row r="726" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A726" s="12"/>
       <c r="B726" s="12"/>
       <c r="C726" s="12"/>
@@ -32306,7 +32306,7 @@
       <c r="AM726" s="6"/>
       <c r="AN726" s="6"/>
     </row>
-    <row r="727" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A727" s="12"/>
       <c r="B727" s="12"/>
       <c r="C727" s="12"/>
@@ -32348,7 +32348,7 @@
       <c r="AM727" s="6"/>
       <c r="AN727" s="6"/>
     </row>
-    <row r="728" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A728" s="12"/>
       <c r="B728" s="12"/>
       <c r="C728" s="12"/>
@@ -32390,7 +32390,7 @@
       <c r="AM728" s="6"/>
       <c r="AN728" s="6"/>
     </row>
-    <row r="729" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A729" s="12"/>
       <c r="B729" s="12"/>
       <c r="C729" s="12"/>
@@ -32432,7 +32432,7 @@
       <c r="AM729" s="6"/>
       <c r="AN729" s="6"/>
     </row>
-    <row r="730" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A730" s="12"/>
       <c r="B730" s="12"/>
       <c r="C730" s="12"/>
@@ -32474,7 +32474,7 @@
       <c r="AM730" s="6"/>
       <c r="AN730" s="6"/>
     </row>
-    <row r="731" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A731" s="12"/>
       <c r="B731" s="12"/>
       <c r="C731" s="12"/>
@@ -32516,7 +32516,7 @@
       <c r="AM731" s="6"/>
       <c r="AN731" s="6"/>
     </row>
-    <row r="732" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A732" s="12"/>
       <c r="B732" s="12"/>
       <c r="C732" s="12"/>
@@ -32558,7 +32558,7 @@
       <c r="AM732" s="6"/>
       <c r="AN732" s="6"/>
     </row>
-    <row r="733" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A733" s="12"/>
       <c r="B733" s="12"/>
       <c r="C733" s="12"/>
@@ -32600,7 +32600,7 @@
       <c r="AM733" s="6"/>
       <c r="AN733" s="6"/>
     </row>
-    <row r="734" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A734" s="12"/>
       <c r="B734" s="12"/>
       <c r="C734" s="12"/>
@@ -32642,7 +32642,7 @@
       <c r="AM734" s="6"/>
       <c r="AN734" s="6"/>
     </row>
-    <row r="735" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A735" s="12"/>
       <c r="B735" s="12"/>
       <c r="C735" s="12"/>
@@ -32684,7 +32684,7 @@
       <c r="AM735" s="6"/>
       <c r="AN735" s="6"/>
     </row>
-    <row r="736" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A736" s="12"/>
       <c r="B736" s="12"/>
       <c r="C736" s="12"/>
@@ -32726,7 +32726,7 @@
       <c r="AM736" s="6"/>
       <c r="AN736" s="6"/>
     </row>
-    <row r="737" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A737" s="12"/>
       <c r="B737" s="12"/>
       <c r="C737" s="12"/>
@@ -32768,7 +32768,7 @@
       <c r="AM737" s="6"/>
       <c r="AN737" s="6"/>
     </row>
-    <row r="738" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A738" s="12"/>
       <c r="B738" s="12"/>
       <c r="C738" s="12"/>
@@ -32810,7 +32810,7 @@
       <c r="AM738" s="6"/>
       <c r="AN738" s="6"/>
     </row>
-    <row r="739" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A739" s="12"/>
       <c r="B739" s="12"/>
       <c r="C739" s="12"/>
@@ -32852,7 +32852,7 @@
       <c r="AM739" s="6"/>
       <c r="AN739" s="6"/>
     </row>
-    <row r="740" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A740" s="12"/>
       <c r="B740" s="12"/>
       <c r="C740" s="12"/>
@@ -32894,7 +32894,7 @@
       <c r="AM740" s="6"/>
       <c r="AN740" s="6"/>
     </row>
-    <row r="741" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A741" s="12"/>
       <c r="B741" s="12"/>
       <c r="C741" s="12"/>
@@ -32936,7 +32936,7 @@
       <c r="AM741" s="6"/>
       <c r="AN741" s="6"/>
     </row>
-    <row r="742" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A742" s="12"/>
       <c r="B742" s="12"/>
       <c r="C742" s="12"/>
@@ -32978,7 +32978,7 @@
       <c r="AM742" s="6"/>
       <c r="AN742" s="6"/>
     </row>
-    <row r="743" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A743" s="12"/>
       <c r="B743" s="12"/>
       <c r="C743" s="12"/>
@@ -33020,7 +33020,7 @@
       <c r="AM743" s="6"/>
       <c r="AN743" s="6"/>
     </row>
-    <row r="744" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A744" s="12"/>
       <c r="B744" s="12"/>
       <c r="C744" s="12"/>
@@ -33062,7 +33062,7 @@
       <c r="AM744" s="6"/>
       <c r="AN744" s="6"/>
     </row>
-    <row r="745" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A745" s="12"/>
       <c r="B745" s="12"/>
       <c r="C745" s="12"/>
@@ -33104,7 +33104,7 @@
       <c r="AM745" s="6"/>
       <c r="AN745" s="6"/>
     </row>
-    <row r="746" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A746" s="12"/>
       <c r="B746" s="12"/>
       <c r="C746" s="12"/>
@@ -33146,7 +33146,7 @@
       <c r="AM746" s="6"/>
       <c r="AN746" s="6"/>
     </row>
-    <row r="747" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A747" s="12"/>
       <c r="B747" s="12"/>
       <c r="C747" s="12"/>
@@ -33188,7 +33188,7 @@
       <c r="AM747" s="6"/>
       <c r="AN747" s="6"/>
     </row>
-    <row r="748" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A748" s="12"/>
       <c r="B748" s="12"/>
       <c r="C748" s="12"/>
@@ -33230,7 +33230,7 @@
       <c r="AM748" s="6"/>
       <c r="AN748" s="6"/>
     </row>
-    <row r="749" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A749" s="12"/>
       <c r="B749" s="12"/>
       <c r="C749" s="12"/>
@@ -33272,7 +33272,7 @@
       <c r="AM749" s="6"/>
       <c r="AN749" s="6"/>
     </row>
-    <row r="750" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A750" s="12"/>
       <c r="B750" s="12"/>
       <c r="C750" s="12"/>
@@ -33314,7 +33314,7 @@
       <c r="AM750" s="6"/>
       <c r="AN750" s="6"/>
     </row>
-    <row r="751" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A751" s="12"/>
       <c r="B751" s="12"/>
       <c r="C751" s="12"/>
@@ -33356,7 +33356,7 @@
       <c r="AM751" s="6"/>
       <c r="AN751" s="6"/>
     </row>
-    <row r="752" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A752" s="12"/>
       <c r="B752" s="12"/>
       <c r="C752" s="12"/>
@@ -33398,7 +33398,7 @@
       <c r="AM752" s="6"/>
       <c r="AN752" s="6"/>
     </row>
-    <row r="753" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A753" s="12"/>
       <c r="B753" s="12"/>
       <c r="C753" s="12"/>
@@ -33440,7 +33440,7 @@
       <c r="AM753" s="6"/>
       <c r="AN753" s="6"/>
     </row>
-    <row r="754" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A754" s="12"/>
       <c r="B754" s="12"/>
       <c r="C754" s="12"/>
@@ -33482,7 +33482,7 @@
       <c r="AM754" s="6"/>
       <c r="AN754" s="6"/>
     </row>
-    <row r="755" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A755" s="12"/>
       <c r="B755" s="12"/>
       <c r="C755" s="12"/>
@@ -33526,14 +33526,22 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="O1:T1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -33546,22 +33554,14 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI4:AI755" xr:uid="{046B03D6-210C-4F88-AB83-B1FB7A0C74BF}">
@@ -33591,23 +33591,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C179FE-D1C9-4048-A0D3-B569542EE019}">
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="13"/>
-    <col min="2" max="2" width="23.26953125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="13"/>
+    <col min="2" max="2" width="23.28515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="13" customWidth="1"/>
     <col min="4" max="5" width="19" style="13" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" style="13" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="19.26953125" style="13" customWidth="1"/>
-    <col min="9" max="9" width="20.1796875" style="13" customWidth="1"/>
-    <col min="10" max="10" width="29.26953125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" style="13" customWidth="1"/>
     <col min="11" max="11" width="27" style="13" customWidth="1"/>
-    <col min="12" max="12" width="25.453125" style="13" customWidth="1"/>
-    <col min="13" max="13" width="25.1796875" style="13" customWidth="1"/>
+    <col min="12" max="12" width="25.42578125" style="13" customWidth="1"/>
+    <col min="13" max="13" width="25.140625" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -33648,64 +33648,69 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="24" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="A2:A3"/>
@@ -33714,11 +33719,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -33728,14 +33728,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3406010B-37DA-462B-8DC6-B4E80ECF9E33}">
   <dimension ref="A1:AD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.1796875" style="13"/>
-    <col min="3" max="3" width="8.7265625" style="13"/>
-    <col min="4" max="30" width="9.1796875" style="13"/>
+    <col min="1" max="2" width="9.140625" style="13"/>
+    <col min="3" max="3" width="8.7109375" style="13"/>
+    <col min="4" max="30" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -33827,77 +33827,77 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="P2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="17" t="s">
+      <c r="T2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="U2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="V2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="17" t="s">
+      <c r="W2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="X2" s="17" t="s">
+      <c r="X2" s="24" t="s">
         <v>15</v>
       </c>
       <c r="Y2" s="29" t="s">
@@ -33906,61 +33906,62 @@
       <c r="Z2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="17" t="s">
+      <c r="AA2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AB2" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AC2" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AD2" s="25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="95.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
       <c r="Y3" s="29"/>
       <c r="Z3" s="29"/>
-      <c r="AA3" s="17"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="P2:P3"/>
@@ -33974,15 +33975,14 @@
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="U2:U3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/wwwroot/template/TemplateExportHistoryNew.xlsx
+++ b/wwwroot/template/TemplateExportHistoryNew.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3961455E-40F1-4A28-93C8-7F09ADA2929E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99E87B9-757D-492C-8DC2-9D6FEAFC762F}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{D99E87B9-757D-492C-8DC2-9D6FEAFC762F}"/>
   </bookViews>
   <sheets>
     <sheet name="Lịch sử yêu cầu" sheetId="1" r:id="rId1"/>
@@ -1248,17 +1248,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1278,17 +1284,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1685,15 +1685,15 @@
       <c r="N1" s="1">
         <v>12</v>
       </c>
-      <c r="O1" s="18">
+      <c r="O1" s="20">
         <f>N1+1</f>
         <v>13</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="20"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="22"/>
       <c r="U1" s="2">
         <v>14</v>
       </c>
@@ -1775,132 +1775,132 @@
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="14" t="s">
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="X2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="Y2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AA2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AB2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AC2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AD2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AE2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="AF2" s="14" t="s">
+      <c r="AF2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AG2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="AH2" s="24" t="s">
+      <c r="AH2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="AI2" s="26" t="s">
+      <c r="AI2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="26" t="s">
+      <c r="AJ2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AK2" s="24" t="s">
+      <c r="AK2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AL2" s="25" t="s">
+      <c r="AL2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AM2" s="25" t="s">
+      <c r="AM2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AN2" s="25" t="s">
+      <c r="AN2" s="14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="132" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
       <c r="O3" s="5" t="s">
         <v>19</v>
       </c>
@@ -1919,26 +1919,26 @@
       <c r="T3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="24"/>
-      <c r="AH3" s="24"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="24"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="16"/>
+      <c r="AJ3" s="16"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
@@ -33526,22 +33526,14 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
-    <mergeCell ref="AN2:AN3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
     <mergeCell ref="O1:T1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -33554,14 +33546,22 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI4:AI755" xr:uid="{046B03D6-210C-4F88-AB83-B1FB7A0C74BF}">
@@ -33652,65 +33652,60 @@
       <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="A2:A3"/>
@@ -33719,6 +33714,11 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -33831,73 +33831,73 @@
       <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="N2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="24" t="s">
+      <c r="R2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="S2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="24" t="s">
+      <c r="T2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="U2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="24" t="s">
+      <c r="V2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="W2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="X2" s="17" t="s">
         <v>15</v>
       </c>
       <c r="Y2" s="29" t="s">
@@ -33906,62 +33906,61 @@
       <c r="Z2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="24" t="s">
+      <c r="AA2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="25" t="s">
+      <c r="AB2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AC2" s="25" t="s">
+      <c r="AC2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AD2" s="25" t="s">
+      <c r="AD2" s="14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
       <c r="Y3" s="29"/>
       <c r="Z3" s="29"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="P2:P3"/>
@@ -33975,14 +33974,15 @@
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="U2:U3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
